--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55A004C-1888-4D12-8C82-DFD861D458A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31140A0E-D40A-4D9D-87A1-A5142F25E4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TalentProto" sheetId="1" r:id="rId1"/>
@@ -238,9 +238,6 @@
     <t>SkillPropertyAdd;61011102,61011103,61011104,61011105,61011106;2;0.75@SkillPropertyAdd;61012102,61012103,61012104,61012105,61012106;2;0.75</t>
   </si>
   <si>
-    <t>技能刷新</t>
-  </si>
-  <si>
     <t>每次攻击有10%的概率自动触发裂地击技能,且不影响主技能的冷却时间</t>
   </si>
   <si>
@@ -379,24 +376,12 @@
     <t>轰击</t>
   </si>
   <si>
-    <t>SkillIdAdd;62000101</t>
-  </si>
-  <si>
     <t>减速之术</t>
   </si>
   <si>
-    <t>普通攻击附带20%减速效果,持续3秒</t>
-  </si>
-  <si>
-    <t>BuffIdAdd;60000301,60000302,60000401,60000402;90000301</t>
-  </si>
-  <si>
     <t>龙卷增强</t>
   </si>
   <si>
-    <t>攻击有5%概率对目标释放龙卷雨击</t>
-  </si>
-  <si>
     <t>SkillIdAdd;62000102</t>
   </si>
   <si>
@@ -548,12 +533,6 @@
   </si>
   <si>
     <t>爆炸种子</t>
-  </si>
-  <si>
-    <t>每次攻击会又概率在目标种下一颗爆炸种子,1.5秒后发生爆炸对范围内的敌人造成250%伤害</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;62000033</t>
   </si>
   <si>
     <t>野兽强壮</t>
@@ -769,9 +748,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>新增技能：猛击\n立即对目标造成300%伤害+1000点固定伤害,如果目标生命低于50%,伤害提升50%</t>
-  </si>
-  <si>
     <t>SkillIdAdd;62000008</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -788,10 +764,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>SkillPropertyAdd;62021302,62021303,62021304,62021305,62021306;2;0.25@SkillPropertyAdd;62022202,62022203,62022204,62022205,62022206;4;3@SkillPropertyAdd;62023302,62023303,62023304,62023305,62023306;4;3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>冰封陷阱: 冷却时间降低2秒;灼热之箭:伤害提升75%;野兽之力:爆发状态延长3秒</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -816,14 +788,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>新增强击技能,立即对目标造成400%伤害</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>新增技能:轰击 立即对目标及其范围造成350%伤害</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>跳跃斩和冲锋斩会对目标区域伤害提升75%</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -841,10 +805,6 @@
   </si>
   <si>
     <t>每次闪避目标攻击将对目标造成100%攻击伤害</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通攻击有20%概率回复自身最大生命的4%</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -1120,6 +1080,54 @@
   </si>
   <si>
     <t>新增技能:冰冻击 蓄力1秒,立即对前方矩形范围的目标造成350%伤害,并使目标禁锢2秒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增强击技能,立即对目标造成400%+1000点伤害</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能刷新</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增技能：猛击\n立即对目标造成350%伤害+1500点固定伤害,如果目标生命低于50%,伤害提升50%</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通攻击有20%概率回复自身最大生命的5%</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增技能:轰击 立即对目标及其范围造成350%+1000点伤害</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000101</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击有10%概率对目标释放龙卷雨击</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通攻击附带30%减速效果,持续3秒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffIdAdd;60000301,60000302,60000401,60000402;90000301</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;62021302,62021303,62021304,62021305,62021306;2;0.4@SkillPropertyAdd;62022202,62022203,62022204,62022205,62022206;4;3@SkillPropertyAdd;62023302,62023303,62023304,62023305,62023306;4;3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000033</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次攻击会又概率在目标种下一颗爆炸种子,1.5秒后发生爆炸对范围内的敌人造成300%+1000点伤害</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -12321,7 +12329,7 @@
         <v>8</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12358,10 +12366,10 @@
         <v>15</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12378,10 +12386,10 @@
         <v>15</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>204</v>
+        <v>266</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12409,7 +12417,7 @@
         <v>10011</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>16</v>
+        <v>267</v>
       </c>
       <c r="E9" s="9">
         <v>10011</v>
@@ -12418,10 +12426,10 @@
         <v>22</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12429,7 +12437,7 @@
         <v>10012</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="9">
         <v>10012</v>
@@ -12438,10 +12446,10 @@
         <v>22</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12449,7 +12457,7 @@
         <v>10013</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11" s="9">
         <v>10013</v>
@@ -12458,10 +12466,10 @@
         <v>22</v>
       </c>
       <c r="G11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="12" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12469,7 +12477,7 @@
         <v>10021</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" s="9">
         <v>10021</v>
@@ -12478,10 +12486,10 @@
         <v>28</v>
       </c>
       <c r="G12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="12" t="s">
         <v>24</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="13" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12489,7 +12497,7 @@
         <v>10022</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="9">
         <v>10022</v>
@@ -12498,10 +12506,10 @@
         <v>28</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="12" t="s">
         <v>27</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="14" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12509,7 +12517,7 @@
         <v>10023</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" s="9">
         <v>10023</v>
@@ -12518,10 +12526,10 @@
         <v>28</v>
       </c>
       <c r="G14" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="12" t="s">
         <v>30</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="15" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12529,7 +12537,7 @@
         <v>10031</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" s="9">
         <v>10031</v>
@@ -12538,10 +12546,10 @@
         <v>32</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="16" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12549,7 +12557,7 @@
         <v>10032</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" s="9">
         <v>10032</v>
@@ -12558,10 +12566,10 @@
         <v>32</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>192</v>
+        <v>268</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12569,7 +12577,7 @@
         <v>10033</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17" s="9">
         <v>10033</v>
@@ -12578,10 +12586,10 @@
         <v>32</v>
       </c>
       <c r="G17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="18" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12589,7 +12597,7 @@
         <v>10041</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" s="9">
         <v>10041</v>
@@ -12598,10 +12606,10 @@
         <v>38</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>211</v>
+        <v>269</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12609,7 +12617,7 @@
         <v>10042</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E19" s="9">
         <v>10042</v>
@@ -12618,10 +12626,10 @@
         <v>38</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12629,7 +12637,7 @@
         <v>10043</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E20" s="9">
         <v>10043</v>
@@ -12638,10 +12646,10 @@
         <v>38</v>
       </c>
       <c r="G20" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="12" t="s">
         <v>44</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="21" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12649,7 +12657,7 @@
         <v>10051</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E21" s="9">
         <v>10051</v>
@@ -12658,10 +12666,10 @@
         <v>42</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12669,7 +12677,7 @@
         <v>10052</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E22" s="9">
         <v>10052</v>
@@ -12678,10 +12686,10 @@
         <v>42</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12689,7 +12697,7 @@
         <v>10053</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E23" s="9">
         <v>10053</v>
@@ -12698,10 +12706,10 @@
         <v>42</v>
       </c>
       <c r="G23" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H23" s="12" t="s">
         <v>51</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="24" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12709,7 +12717,7 @@
         <v>10061</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E24" s="14">
         <v>10061</v>
@@ -12718,10 +12726,10 @@
         <v>52</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12729,7 +12737,7 @@
         <v>10062</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" s="14">
         <v>10062</v>
@@ -12738,10 +12746,10 @@
         <v>52</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12749,7 +12757,7 @@
         <v>10063</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E26" s="14">
         <v>10063</v>
@@ -12758,10 +12766,10 @@
         <v>52</v>
       </c>
       <c r="G26" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26" s="17" t="s">
         <v>57</v>
-      </c>
-      <c r="H26" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="27" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12769,7 +12777,7 @@
         <v>20001</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27" s="9">
         <v>20001</v>
@@ -12778,10 +12786,10 @@
         <v>15</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="12" t="s">
         <v>60</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="28" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12789,7 +12797,7 @@
         <v>20002</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E28" s="9">
         <v>20002</v>
@@ -12798,10 +12806,10 @@
         <v>15</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>205</v>
+        <v>270</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>63</v>
+        <v>271</v>
       </c>
     </row>
     <row r="29" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12809,7 +12817,7 @@
         <v>20003</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E29" s="9">
         <v>20003</v>
@@ -12818,10 +12826,10 @@
         <v>15</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>65</v>
+        <v>273</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>66</v>
+        <v>274</v>
       </c>
     </row>
     <row r="30" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12829,7 +12837,7 @@
         <v>20011</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E30" s="9">
         <v>20011</v>
@@ -12838,10 +12846,10 @@
         <v>22</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>68</v>
+        <v>272</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12849,7 +12857,7 @@
         <v>20012</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E31" s="9">
         <v>20012</v>
@@ -12858,10 +12866,10 @@
         <v>22</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12869,7 +12877,7 @@
         <v>20013</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E32" s="9">
         <v>20013</v>
@@ -12878,10 +12886,10 @@
         <v>22</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12889,7 +12897,7 @@
         <v>20021</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E33" s="9">
         <v>20021</v>
@@ -12898,10 +12906,10 @@
         <v>28</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12909,7 +12917,7 @@
         <v>20022</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E34" s="9">
         <v>20022</v>
@@ -12918,10 +12926,10 @@
         <v>28</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12929,7 +12937,7 @@
         <v>20023</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E35" s="9">
         <v>20023</v>
@@ -12938,10 +12946,10 @@
         <v>28</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12949,7 +12957,7 @@
         <v>20031</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E36" s="9">
         <v>20031</v>
@@ -12958,10 +12966,10 @@
         <v>32</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12969,7 +12977,7 @@
         <v>20032</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E37" s="9">
         <v>20032</v>
@@ -12978,10 +12986,10 @@
         <v>32</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12989,7 +12997,7 @@
         <v>20033</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E38" s="9">
         <v>20033</v>
@@ -12998,10 +13006,10 @@
         <v>32</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13009,7 +13017,7 @@
         <v>20041</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E39" s="9">
         <v>20041</v>
@@ -13018,10 +13026,10 @@
         <v>38</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13029,7 +13037,7 @@
         <v>20042</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E40" s="9">
         <v>20042</v>
@@ -13038,10 +13046,10 @@
         <v>38</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13049,7 +13057,7 @@
         <v>20043</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E41" s="9">
         <v>20043</v>
@@ -13058,10 +13066,10 @@
         <v>38</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13069,7 +13077,7 @@
         <v>20051</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E42" s="9">
         <v>20051</v>
@@ -13078,10 +13086,10 @@
         <v>42</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13089,7 +13097,7 @@
         <v>20052</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E43" s="9">
         <v>20052</v>
@@ -13098,10 +13106,10 @@
         <v>42</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>197</v>
+        <v>275</v>
       </c>
     </row>
     <row r="44" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13109,7 +13117,7 @@
         <v>20053</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E44" s="9">
         <v>20053</v>
@@ -13118,10 +13126,10 @@
         <v>42</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13129,7 +13137,7 @@
         <v>20061</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E45" s="9">
         <v>20061</v>
@@ -13138,10 +13146,10 @@
         <v>52</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13149,7 +13157,7 @@
         <v>20062</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E46" s="9">
         <v>20062</v>
@@ -13158,10 +13166,10 @@
         <v>52</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13169,7 +13177,7 @@
         <v>20063</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E47" s="9">
         <v>20063</v>
@@ -13178,10 +13186,10 @@
         <v>52</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13198,10 +13206,10 @@
         <v>15</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13209,7 +13217,7 @@
         <v>30002</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E49" s="9">
         <v>30002</v>
@@ -13218,10 +13226,10 @@
         <v>15</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13238,10 +13246,10 @@
         <v>15</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13249,7 +13257,7 @@
         <v>30011</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E51" s="9">
         <v>30011</v>
@@ -13258,10 +13266,10 @@
         <v>22</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>120</v>
+        <v>277</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>121</v>
+        <v>276</v>
       </c>
     </row>
     <row r="52" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13269,7 +13277,7 @@
         <v>30012</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E52" s="9">
         <v>30012</v>
@@ -13278,10 +13286,10 @@
         <v>22</v>
       </c>
       <c r="G52" s="22" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13289,7 +13297,7 @@
         <v>30013</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E53" s="9">
         <v>30013</v>
@@ -13298,10 +13306,10 @@
         <v>22</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13309,7 +13317,7 @@
         <v>30021</v>
       </c>
       <c r="D54" s="20" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E54" s="9">
         <v>30021</v>
@@ -13318,10 +13326,10 @@
         <v>28</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13329,7 +13337,7 @@
         <v>30022</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E55" s="9">
         <v>30022</v>
@@ -13338,10 +13346,10 @@
         <v>28</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13349,7 +13357,7 @@
         <v>30023</v>
       </c>
       <c r="D56" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E56" s="9">
         <v>30023</v>
@@ -13358,10 +13366,10 @@
         <v>28</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13369,7 +13377,7 @@
         <v>30031</v>
       </c>
       <c r="D57" s="20" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E57" s="9">
         <v>30031</v>
@@ -13378,10 +13386,10 @@
         <v>32</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="H57" s="16" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13389,7 +13397,7 @@
         <v>30032</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E58" s="9">
         <v>30032</v>
@@ -13398,10 +13406,10 @@
         <v>32</v>
       </c>
       <c r="G58" s="24" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13409,7 +13417,7 @@
         <v>30033</v>
       </c>
       <c r="D59" s="20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E59" s="9">
         <v>30033</v>
@@ -13418,10 +13426,10 @@
         <v>32</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13429,7 +13437,7 @@
         <v>30041</v>
       </c>
       <c r="D60" s="20" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E60" s="9">
         <v>30041</v>
@@ -13438,10 +13446,10 @@
         <v>38</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="61" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13449,7 +13457,7 @@
         <v>30042</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E61" s="9">
         <v>30042</v>
@@ -13458,10 +13466,10 @@
         <v>38</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13469,7 +13477,7 @@
         <v>30043</v>
       </c>
       <c r="D62" s="20" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E62" s="9">
         <v>30043</v>
@@ -13478,10 +13486,10 @@
         <v>38</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13489,7 +13497,7 @@
         <v>30051</v>
       </c>
       <c r="D63" s="20" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E63" s="9">
         <v>30051</v>
@@ -13498,10 +13506,10 @@
         <v>42</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
     </row>
     <row r="64" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13509,7 +13517,7 @@
         <v>30052</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E64" s="9">
         <v>30052</v>
@@ -13518,10 +13526,10 @@
         <v>42</v>
       </c>
       <c r="G64" s="25" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
     </row>
     <row r="65" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13529,7 +13537,7 @@
         <v>30053</v>
       </c>
       <c r="D65" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E65" s="9">
         <v>30053</v>
@@ -13538,10 +13546,10 @@
         <v>42</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13549,7 +13557,7 @@
         <v>30061</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E66" s="9">
         <v>30061</v>
@@ -13558,10 +13566,10 @@
         <v>52</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13569,7 +13577,7 @@
         <v>30062</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E67" s="9">
         <v>30062</v>
@@ -13578,10 +13586,10 @@
         <v>52</v>
       </c>
       <c r="G67" s="27" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="H67" s="17" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="68" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13589,7 +13597,7 @@
         <v>30063</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E68" s="9">
         <v>30063</v>
@@ -13598,10 +13606,10 @@
         <v>52</v>
       </c>
       <c r="G68" s="29" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H68" s="16" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13609,7 +13617,7 @@
         <v>40001</v>
       </c>
       <c r="D69" s="31" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="E69" s="14">
         <v>40001</v>
@@ -13618,10 +13626,10 @@
         <v>15</v>
       </c>
       <c r="G69" s="32" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H69" s="16" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="70" spans="3:8" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -13629,7 +13637,7 @@
         <v>40002</v>
       </c>
       <c r="D70" s="31" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="E70" s="14">
         <v>40002</v>
@@ -13638,10 +13646,10 @@
         <v>15</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13649,7 +13657,7 @@
         <v>40003</v>
       </c>
       <c r="D71" s="34" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="E71" s="33">
         <v>40003</v>
@@ -13658,10 +13666,10 @@
         <v>15</v>
       </c>
       <c r="G71" s="35" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="H71" s="16" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
     </row>
     <row r="72" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13669,7 +13677,7 @@
         <v>40011</v>
       </c>
       <c r="D72" s="31" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E72" s="14">
         <v>40011</v>
@@ -13678,10 +13686,10 @@
         <v>22</v>
       </c>
       <c r="G72" s="32" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="H72" s="16" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
     </row>
     <row r="73" spans="3:8" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -13689,7 +13697,7 @@
         <v>40012</v>
       </c>
       <c r="D73" s="31" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E73" s="14">
         <v>40012</v>
@@ -13698,10 +13706,10 @@
         <v>22</v>
       </c>
       <c r="G73" s="32" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="H73" s="16" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13709,7 +13717,7 @@
         <v>40013</v>
       </c>
       <c r="D74" s="34" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E74" s="33">
         <v>40013</v>
@@ -13718,10 +13726,10 @@
         <v>22</v>
       </c>
       <c r="G74" s="35" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="H74" s="40" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
     </row>
     <row r="75" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13729,7 +13737,7 @@
         <v>40021</v>
       </c>
       <c r="D75" s="31" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="E75" s="14">
         <v>40021</v>
@@ -13738,10 +13746,10 @@
         <v>28</v>
       </c>
       <c r="G75" s="32" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="76" spans="3:8" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -13749,7 +13757,7 @@
         <v>40022</v>
       </c>
       <c r="D76" s="31" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E76" s="14">
         <v>40022</v>
@@ -13758,10 +13766,10 @@
         <v>28</v>
       </c>
       <c r="G76" s="32" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
     </row>
     <row r="77" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13769,7 +13777,7 @@
         <v>40023</v>
       </c>
       <c r="D77" s="34" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="E77" s="33">
         <v>40023</v>
@@ -13778,10 +13786,10 @@
         <v>28</v>
       </c>
       <c r="G77" s="35" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
     </row>
     <row r="78" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13789,7 +13797,7 @@
         <v>40031</v>
       </c>
       <c r="D78" s="37" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="E78" s="33">
         <v>40031</v>
@@ -13798,10 +13806,10 @@
         <v>32</v>
       </c>
       <c r="G78" s="38" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="H78" s="39" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
     </row>
     <row r="79" spans="3:8" s="36" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -13809,7 +13817,7 @@
         <v>40032</v>
       </c>
       <c r="D79" s="37" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E79" s="33">
         <v>40032</v>
@@ -13818,10 +13826,10 @@
         <v>32</v>
       </c>
       <c r="G79" s="38" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13829,7 +13837,7 @@
         <v>40033</v>
       </c>
       <c r="D80" s="34" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="E80" s="33">
         <v>40033</v>
@@ -13838,10 +13846,10 @@
         <v>32</v>
       </c>
       <c r="G80" s="35" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="81" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13849,7 +13857,7 @@
         <v>40041</v>
       </c>
       <c r="D81" s="37" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E81" s="33">
         <v>40041</v>
@@ -13858,10 +13866,10 @@
         <v>38</v>
       </c>
       <c r="G81" s="38" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="82" spans="3:8" s="36" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -13869,7 +13877,7 @@
         <v>40042</v>
       </c>
       <c r="D82" s="37" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E82" s="33">
         <v>40042</v>
@@ -13878,10 +13886,10 @@
         <v>38</v>
       </c>
       <c r="G82" s="38" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="H82" s="39" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
     </row>
     <row r="83" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13889,7 +13897,7 @@
         <v>40043</v>
       </c>
       <c r="D83" s="34" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E83" s="33">
         <v>40043</v>
@@ -13898,10 +13906,10 @@
         <v>38</v>
       </c>
       <c r="G83" s="35" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
     </row>
     <row r="84" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13909,7 +13917,7 @@
         <v>40051</v>
       </c>
       <c r="D84" s="37" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="E84" s="33">
         <v>40051</v>
@@ -13918,10 +13926,10 @@
         <v>42</v>
       </c>
       <c r="G84" s="38" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H84" s="39" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="85" spans="3:8" s="36" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -13929,7 +13937,7 @@
         <v>40052</v>
       </c>
       <c r="D85" s="37" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="E85" s="33">
         <v>40052</v>
@@ -13938,10 +13946,10 @@
         <v>42</v>
       </c>
       <c r="G85" s="38" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
     </row>
     <row r="86" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13949,7 +13957,7 @@
         <v>40053</v>
       </c>
       <c r="D86" s="34" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E86" s="33">
         <v>40053</v>
@@ -13958,10 +13966,10 @@
         <v>42</v>
       </c>
       <c r="G86" s="35" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="H86" s="17" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13969,7 +13977,7 @@
         <v>40061</v>
       </c>
       <c r="D87" s="37" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="E87" s="33">
         <v>40061</v>
@@ -13978,10 +13986,10 @@
         <v>52</v>
       </c>
       <c r="G87" s="38" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="H87" s="39" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
     </row>
     <row r="88" spans="3:8" s="36" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -13989,7 +13997,7 @@
         <v>40062</v>
       </c>
       <c r="D88" s="37" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="E88" s="33">
         <v>40062</v>
@@ -13998,10 +14006,10 @@
         <v>52</v>
       </c>
       <c r="G88" s="38" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="H88" s="16" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="89" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14009,7 +14017,7 @@
         <v>40063</v>
       </c>
       <c r="D89" s="34" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="E89" s="33">
         <v>40063</v>
@@ -14018,10 +14026,10 @@
         <v>52</v>
       </c>
       <c r="G89" s="35" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="H89" s="17" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="90" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14029,7 +14037,7 @@
         <v>90001</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E90" s="9">
         <v>60010100</v>
@@ -14038,10 +14046,10 @@
         <v>1</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="H90" s="12" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="91" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14049,7 +14057,7 @@
         <v>90002</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E91" s="9">
         <v>60010200</v>
@@ -14058,10 +14066,10 @@
         <v>1</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="92" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14069,7 +14077,7 @@
         <v>90003</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E92" s="9">
         <v>60010300</v>
@@ -14078,10 +14086,10 @@
         <v>1</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="93" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14089,7 +14097,7 @@
         <v>90004</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E93" s="9">
         <v>60010400</v>
@@ -14098,10 +14106,10 @@
         <v>2</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H93" s="12" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14109,7 +14117,7 @@
         <v>90005</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E94" s="9">
         <v>60010500</v>
@@ -14118,10 +14126,10 @@
         <v>2</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="95" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14129,7 +14137,7 @@
         <v>90006</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E95" s="9">
         <v>60010600</v>
@@ -14138,10 +14146,10 @@
         <v>2</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="H95" s="12" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="96" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14155,7 +14163,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="30" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="97" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14169,7 +14177,7 @@
         <v>1</v>
       </c>
       <c r="H97" s="30" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="98" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14183,7 +14191,7 @@
         <v>1</v>
       </c>
       <c r="H98" s="30" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="99" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14197,7 +14205,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="30" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="100" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14211,7 +14219,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="101" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14225,7 +14233,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="30" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="102" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14239,7 +14247,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="30" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="103" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14253,7 +14261,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="30" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="104" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14267,7 +14275,7 @@
         <v>1</v>
       </c>
       <c r="H104" s="30" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="105" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14281,7 +14289,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="106" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14295,7 +14303,7 @@
         <v>1</v>
       </c>
       <c r="H106" s="30" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="O106" s="9"/>
     </row>
@@ -14310,7 +14318,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="30" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="O107" s="9"/>
     </row>
@@ -14325,7 +14333,7 @@
         <v>1</v>
       </c>
       <c r="H108" s="30" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="O108" s="9"/>
     </row>
@@ -14340,7 +14348,7 @@
         <v>1</v>
       </c>
       <c r="H109" s="30" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="O109" s="9"/>
     </row>
@@ -14355,7 +14363,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="30" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="O110" s="9"/>
     </row>
@@ -14370,7 +14378,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="30" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="O111" s="9"/>
     </row>
@@ -14385,7 +14393,7 @@
         <v>1</v>
       </c>
       <c r="H112" s="30" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O112" s="9"/>
     </row>
@@ -14400,7 +14408,7 @@
         <v>1</v>
       </c>
       <c r="H113" s="30" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O113" s="9"/>
     </row>
@@ -14415,7 +14423,7 @@
         <v>1</v>
       </c>
       <c r="H114" s="30" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="O114" s="9"/>
     </row>
@@ -14430,7 +14438,7 @@
         <v>1</v>
       </c>
       <c r="H115" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="O115" s="9"/>
     </row>
@@ -14445,7 +14453,7 @@
         <v>1</v>
       </c>
       <c r="H116" s="30" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="O116" s="9"/>
     </row>
@@ -14460,7 +14468,7 @@
         <v>1</v>
       </c>
       <c r="H117" s="30" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="O117" s="9"/>
     </row>
@@ -14475,7 +14483,7 @@
         <v>1</v>
       </c>
       <c r="H118" s="30" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="O118" s="9"/>
     </row>
@@ -14490,7 +14498,7 @@
         <v>1</v>
       </c>
       <c r="H119" s="30" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="O119" s="9"/>
     </row>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31140A0E-D40A-4D9D-87A1-A5142F25E4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6884395D-A909-4C60-B10E-A02635AEE8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -188,7 +188,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="438">
   <si>
     <t>Id</t>
   </si>
@@ -1129,6 +1129,489 @@
   <si>
     <t>每次攻击会又概率在目标种下一颗爆炸种子,1.5秒后发生爆炸对范围内的敌人造成300%+1000点伤害</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Life Restoration</t>
+  </si>
+  <si>
+    <t>Striking</t>
+  </si>
+  <si>
+    <t>Damage increases.</t>
+  </si>
+  <si>
+    <t>Skill refresh</t>
+  </si>
+  <si>
+    <t>Free movement</t>
+  </si>
+  <si>
+    <t>Holy Light Speed</t>
+  </si>
+  <si>
+    <t>Critical Hit Rate Increase</t>
+  </si>
+  <si>
+    <t>Dodge specialization</t>
+  </si>
+  <si>
+    <t>Skill Specialization</t>
+  </si>
+  <si>
+    <t>Defense Shield</t>
+  </si>
+  <si>
+    <t>Punch</t>
+  </si>
+  <si>
+    <t>Skill upgrade</t>
+  </si>
+  <si>
+    <t>Attack recovery</t>
+  </si>
+  <si>
+    <t>Ultimate Counterattack</t>
+  </si>
+  <si>
+    <t>Profession Specialization</t>
+  </si>
+  <si>
+    <t>Victory Hope</t>
+  </si>
+  <si>
+    <t>Explosive Bombardment</t>
+  </si>
+  <si>
+    <t>Class Advancement</t>
+  </si>
+  <si>
+    <t>Eye for eye</t>
+  </si>
+  <si>
+    <t>Control of Time</t>
+  </si>
+  <si>
+    <t>Damage Increase</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Slow Technique</t>
+  </si>
+  <si>
+    <t>Tornado Enhancement</t>
+  </si>
+  <si>
+    <t>Freezing Strike</t>
+  </si>
+  <si>
+    <t>Brave Guardianship</t>
+  </si>
+  <si>
+    <t>Willpower of the Spirit</t>
+  </si>
+  <si>
+    <t>Attack Enhancement</t>
+  </si>
+  <si>
+    <t>Strong Hand</t>
+  </si>
+  <si>
+    <t>Defensive Strike</t>
+  </si>
+  <si>
+    <t>Movement Enhancement</t>
+  </si>
+  <si>
+    <t>Critical Hit Recovery</t>
+  </si>
+  <si>
+    <t>Movement Orb</t>
+  </si>
+  <si>
+    <t>Spell Combo</t>
+  </si>
+  <si>
+    <t>Excellent Counterattack</t>
+  </si>
+  <si>
+    <t>Fierce</t>
+  </si>
+  <si>
+    <t>Explosion Seed</t>
+  </si>
+  <si>
+    <t>Wild Beast Strength</t>
+  </si>
+  <si>
+    <t>Scattering Stun</t>
+  </si>
+  <si>
+    <t>Heavy Strike Power</t>
+  </si>
+  <si>
+    <t>Frozen Arrow</t>
+  </si>
+  <si>
+    <t>Critical Strike Power</t>
+  </si>
+  <si>
+    <t>Anger</t>
+  </si>
+  <si>
+    <t>Specialization in shooting</t>
+  </si>
+  <si>
+    <t>Life Shield</t>
+  </si>
+  <si>
+    <t>Shooting penetration</t>
+  </si>
+  <si>
+    <t>怒气 Recovery</t>
+  </si>
+  <si>
+    <t>Attack Power</t>
+  </si>
+  <si>
+    <t>Explosion attack</t>
+  </si>
+  <si>
+    <t>Multiple Shots</t>
+  </si>
+  <si>
+    <t>Magic Strike</t>
+  </si>
+  <si>
+    <t>Resting Hand</t>
+  </si>
+  <si>
+    <t>Magic Mark</t>
+  </si>
+  <si>
+    <t>Bravery Power</t>
+  </si>
+  <si>
+    <t>Swift Aura</t>
+  </si>
+  <si>
+    <t>Magic Power</t>
+  </si>
+  <si>
+    <t>Summoning Power</t>
+  </si>
+  <si>
+    <t>Thunder Power</t>
+  </si>
+  <si>
+    <t>Swift Movement</t>
+  </si>
+  <si>
+    <t>Summoning Ritual</t>
+  </si>
+  <si>
+    <t>Defense Guardian</t>
+  </si>
+  <si>
+    <t>Skill Ability</t>
+  </si>
+  <si>
+    <t>Health increase</t>
+  </si>
+  <si>
+    <t>Auras Skill Range</t>
+  </si>
+  <si>
+    <t>Elemental Ball attaches health to itself and stuns enemies</t>
+  </si>
+  <si>
+    <t>Change Skill Elemental Blast Ice to Elemental Ball</t>
+  </si>
+  <si>
+    <t>New skill aura</t>
+  </si>
+  <si>
+    <t>Extended speed reduction duration</t>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>New passive skill: Life Recovery. There is a certain probability of restoring 5% of one's maximum health upon taking damage.</t>
+  </si>
+  <si>
+    <t>New powerful strike skill: Immediately deals 400% + 1000 damage to the target.</t>
+  </si>
+  <si>
+    <t>Damage of Split Ground and Split Wave increases by 75%</t>
+  </si>
+  <si>
+    <t>Each attack has a 10% chance to automatically trigger the Earth-Shattering Strike skill, and this does not affect the cooldown time of the main skill.</t>
+  </si>
+  <si>
+    <t>Jumpsword and Charge Sword will increase damage to the target area by 75%</t>
+  </si>
+  <si>
+    <t>Holy Light Speed: Significantly increases the movement speed of the character, and boosts the evasion rate by 10%. Duration: 6 seconds.</t>
+  </si>
+  <si>
+    <t>Permanent increase of critical hit rate by 5%</t>
+  </si>
+  <si>
+    <t>Permanent Increase of 5% to the Limit of Dexterity Defense</t>
+  </si>
+  <si>
+    <t>Elemental Flame: Damage increased by 75%; Light Strike: Damage increased by 120%; Energy Absorption: Damage increased by 75%</t>
+  </si>
+  <si>
+    <t>When damaged, there is a chance to release a shield for yourself. The shield can resist 30% of the damage and 20% of the maximum life, lasting for 20 seconds.</t>
+  </si>
+  <si>
+    <t>New skill： Slam\nImmediately deal 350% damage + 1500 fixed damage to the target. If the target's health is below 50%， the damage is increased by 50%</t>
+  </si>
+  <si>
+    <t>Elemental ball: Skill damage increased by 75%; Lightsaber attack: Duration extended by 10 seconds; Burst state: Additional damage of 1000 points</t>
+  </si>
+  <si>
+    <t>Normal attack has a 20% chance to restore 5% of one's maximum health.</t>
+  </si>
+  <si>
+    <t>When life is below 30%, one's own life value is reduced by 50% and attacks will restore a certain amount of life value to oneself, lasting for 6 seconds.</t>
+  </si>
+  <si>
+    <t>Elemental Gravitational Wave: Skill damage increased by 75%; Light Energy: Damage range expanded, damage increased by 30%; Energy Ball: Damage increased to 30%</t>
+  </si>
+  <si>
+    <t>When health drops below 10%, immediately restore 20% of maximum health and increase damage by 25% for 6 seconds, with a 120-second cooldown.</t>
+  </si>
+  <si>
+    <t>New Skill: Burst Bombing\nCauses 150% damage to the area around the user every second for a duration of 6 seconds.</t>
+  </si>
+  <si>
+    <t>Elemental Flame: Skill damage increased by 75%; Light Strike: Skill damage increased by 75%; Energy Field: Skill damage effect increased to 20%</t>
+  </si>
+  <si>
+    <t>Each time you dodge an attack from the target, you will deal 100% attack damage to the target</t>
+  </si>
+  <si>
+    <t>The cooldown time of the Elemental Gravitational Wave skill is reduced by 4 seconds; the cooldown time of Light Strike is reduced by 5 seconds; the attack effect of Energy Field is enhanced by 10%.</t>
+  </si>
+  <si>
+    <t>Skill cooldown time reduced by 10%</t>
+  </si>
+  <si>
+    <t>Damage from Magic Strike and Dragon Cyclone Strike increases by 75%</t>
+  </si>
+  <si>
+    <t>New skill: Blast Deal 350% + 1000 points of damage to the target and its range immediately.</t>
+  </si>
+  <si>
+    <t>The normal attack comes with a 30% slowdown effect that lasts for 3 seconds.</t>
+  </si>
+  <si>
+    <t>The attack has a 10% chance to release Dragon Whirlwind Strike on the target</t>
+  </si>
+  <si>
+    <t>New Skill: Freezing Strike. It requires 1 second of charging time. Immediately, it deals 350% damage to the targets within a rectangular area in front of you, and also immobilizes the targets for 2 seconds.</t>
+  </si>
+  <si>
+    <t>The damage caused by Guardian Strike and Ice Spike Strike increases by 75%.</t>
+  </si>
+  <si>
+    <t>Being injured has a 15% chance to trigger the Guardian Strike.</t>
+  </si>
+  <si>
+    <t>Shockwave: Skill damage effect increased by 75%; Spirit Strike: Skill damage effect increased by 75%; Healing Field: Skill damage effect increased by 25%</t>
+  </si>
+  <si>
+    <t>The attack has a 10% chance to grant a 30% damage bonus to itself for 10 seconds.</t>
+  </si>
+  <si>
+    <t>Attack permanently increases by 5%</t>
+  </si>
+  <si>
+    <t>Magic Field: Skill damage effect increases by 75%; Blaze Burning: Duration of effect increases by 4 seconds; Healing Realm: Recovery effect is additionally enhanced by 3%</t>
+  </si>
+  <si>
+    <t>When the health value drops to 30%, the damage received is reduced by 75% for 6 seconds. It can only be triggered once within 45 seconds.</t>
+  </si>
+  <si>
+    <t>New Skill: Defense Strike Immediately deals 250% damage to nearby enemy targets, and causes nearby units to suffer silence and slowdown effects as well as a 50% increase in your own movement speed, lasting for 3 seconds.</t>
+  </si>
+  <si>
+    <t>Shockwave: Stuns the target unit in place for 3 seconds and prevents movement; Burning Blast: Duration is increased by 4 seconds; Psychic Strike: Damage is increased by 50%</t>
+  </si>
+  <si>
+    <t>Movement speed permanently increases by 10%</t>
+  </si>
+  <si>
+    <t>After each critical hit, immediately restore 4% of the maximum health of the friendly units.</t>
+  </si>
+  <si>
+    <t>Lava World: Damage increased by 25%; Burst Burning cooldown time reduced by 3 seconds; Psychic Strike: Cooldown time shortened by 3 seconds</t>
+  </si>
+  <si>
+    <t>New Skill: Magic Orb, releases a moving light ball in the front area. It deals 350% + 2500 damage to the units it touches. It also reduces the movement speed of the touched target by 50% for 3 seconds.</t>
+  </si>
+  <si>
+    <t>The cooldown time of the Great Mage's Shadow has been reduced by 20 seconds; the spell of the Spirit Blast has been changed from requiring a chant to being cast immediately; the cooldown time of the Mind Heal has been shortened by 5 seconds.</t>
+  </si>
+  <si>
+    <t>There is a 15% chance to continuously release 2 skills when using a skill</t>
+  </si>
+  <si>
+    <t>There is a 20% chance of causing the target to be stunned for 2 seconds upon being attacked. This effect triggers once every 20 seconds.</t>
+  </si>
+  <si>
+    <t>There is a 20% chance to restore 2% of one's maximum health upon using an arrow for an ordinary attack.</t>
+  </si>
+  <si>
+    <t>Immediately increase the attack speed of both the player and the summoned beast by 100%, lasting for 6 seconds.</t>
+  </si>
+  <si>
+    <t>The damage of Shock Shot is increased by 75%</t>
+  </si>
+  <si>
+    <t>Each attack has a probability of planting an explosive seed on the target. After 1.5 seconds, an explosion occurs, dealing 300% + 1000 points of damage to enemies within the range.</t>
+  </si>
+  <si>
+    <t>Summoned Beast Attack and Life Increase 20%</t>
+  </si>
+  <si>
+    <t>The skill damage of scattering is increased by 75%</t>
+  </si>
+  <si>
+    <t>Permanent increase in critical hit probability by 5%</t>
+  </si>
+  <si>
+    <t>Each attack has a probability of reducing the target's movement speed by 30%, lasting for 5 seconds</t>
+  </si>
+  <si>
+    <t>Frozen Trap: Cooldown time reduced by 2 seconds; Scorching Arrow: Damage increased by 75%; Beast Power: Duration of burst state extended by 3 seconds</t>
+  </si>
+  <si>
+    <t>When the normal attack hits, it will increase the damage of itself by 20% for 6 seconds</t>
+  </si>
+  <si>
+    <t>Each attack has a certain probability of restoring 10 points of rage to the character.</t>
+  </si>
+  <si>
+    <t>Explosion Trap: Inflicts damage and causes the target to be stunned for 1 second.  Burning Cyclone: Skill damage is increased by 75%.  Hunting Mark: Damage is increased by 10%.</t>
+  </si>
+  <si>
+    <t>Normal attack with bow and arrow increases damage to target by 20%</t>
+  </si>
+  <si>
+    <t>Has a chance to give itself a shield upon taking damage. The shield can resist 50% damage and 30% of the maximum life, lasting for 20 seconds</t>
+  </si>
+  <si>
+    <t>Frozen Land: Damage increased by 25%  Cooldown Strike: Damage increased by 75%  Beast Blaze: Damage increased to 75%</t>
+  </si>
+  <si>
+    <t>The damage bonus is increased by 5%.</t>
+  </si>
+  <si>
+    <t>The rage limit is increased to 150, and rage recovery now adds an extra 3 points per second.</t>
+  </si>
+  <si>
+    <t>Flame Guard: Cooling time reduced by 5 seconds; Gale Arrow Field: The skill will reduce the target's movement speed by 30%; Beast Call: All summoned monsters' attributes of the self will be increased by 25%</t>
+  </si>
+  <si>
+    <t>Each attack on the target has a certain probability to reduce all its defenses to 0, lasting for 5 seconds</t>
+  </si>
+  <si>
+    <t>Launch a scattering attack on the target. After the scattering attack hits the target, it will cause 100% area damage to nearby units.</t>
+  </si>
+  <si>
+    <t>The attack will target both the target and nearby units simultaneously.</t>
+  </si>
+  <si>
+    <t>Added the Magic Strike skill, which deals 400% damage to the target immediately</t>
+  </si>
+  <si>
+    <t>Magic baptism and magic bombardment damage increase by 75%</t>
+  </si>
+  <si>
+    <t>Each time a skill is used, there is a certain probability of restoring a certain amount of one's own life points.</t>
+  </si>
+  <si>
+    <t>There is a chance for normal attacks to add 1 layer of magic mark to the target.</t>
+  </si>
+  <si>
+    <t>New defensive strike skill: Immediately restore 10% of one's health. When taking damage, there is a certain probability to immediately deal 350% attack damage + 2000 to monsters within one's range, and cause a 2-second stun.</t>
+  </si>
+  <si>
+    <t>Self basic attack damage increased by 25%</t>
+  </si>
+  <si>
+    <t>Each normal attack increases attack speed and movement speed by 5%, and can stack up to 5 layers.</t>
+  </si>
+  <si>
+    <t>The cooldown time of the Magic Flash Strike is reduced by 1 second. The damage of the Burning Magic Ball is increased by 75%, and the damage of the Contracted Land is increased by 25%.</t>
+  </si>
+  <si>
+    <t>Damage dealt increases by 5%</t>
+  </si>
+  <si>
+    <t>Each layer of magic mark increases damage by 10%</t>
+  </si>
+  <si>
+    <t>The cooldown time for Shadow Throw is reduced by 1 second; the cooldown time for Burning Magic Ball is reduced by 1 second; the cooldown time for Thunderous Power is reduced by 3 seconds.</t>
+  </si>
+  <si>
+    <t>The speed-bombing skill's damage is increased by 75%; the cooldown time of the Gale Flame skill is reduced by 2 seconds; the damage of Dark Magic Blast is increased by 75%.</t>
+  </si>
+  <si>
+    <t>Active Skill: Thunderous Power, immediately deals 350% lightning damage to the 6 areas within the surrounding range of the caster, and causes a 1-second stun</t>
+  </si>
+  <si>
+    <t>Movement speed increased by 15%</t>
+  </si>
+  <si>
+    <t>After causing a critical hit, it will additionally increase its own attack by 15% for 10 seconds</t>
+  </si>
+  <si>
+    <t>Flame Cyclone skill damage +75%; Windmaiden's basic attack damage +50%; Demon Pact cooldown -5s.</t>
+  </si>
+  <si>
+    <t>Skill cooldown time reduced by 5%</t>
+  </si>
+  <si>
+    <t>Each time the skill is used, there is a probability to summon an additional ritual monster to assist in the battle.</t>
+  </si>
+  <si>
+    <t>New defensive guardian skill. When damaged, there is a certain probability to immediately inflict 350% attack damage + 2000 damage on the monsters within your own range, and push back nearby enemy targets.</t>
+  </si>
+  <si>
+    <t>The release skill has a 10% chance to cause double damage from the skill's effect.</t>
+  </si>
+  <si>
+    <t>Attack +10; Attack +20; Attack +30</t>
+  </si>
+  <si>
+    <t>The skill damage range of Whirlwind Slash increases by 1; The skill damage range of Whirlwind Slash increases by 2</t>
+  </si>
+  <si>
+    <t>Forward movement distance extended by 3 yards</t>
+  </si>
+  <si>
+    <t>When using Judgment, you can slow the target by 30% for 3 seconds; when using Judgment, you can slow the target by 30% for 5 seconds.</t>
+  </si>
+  <si>
+    <t>Kill monsters and gain 1% of gold; Kill monsters and gain 2% of gold; Kill monsters and gain 3% of gold; Kill monsters and gain 4% of gold; Kill monsters and gain 5% of gold</t>
+  </si>
+  <si>
+    <t>Base movement speed + 4%; Base movement speed + 8%; Base movement speed + 12%; Base movement speed + 16%; Base movement speed + 20%</t>
   </si>
 </sst>
 </file>
@@ -9230,7 +9713,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -9348,6 +9831,7 @@
     <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2603">
     <cellStyle name="20% - 强调文字颜色 1 10" xfId="98" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
@@ -12280,19 +12764,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:O119"/>
+  <dimension ref="C1:Q119"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="8.5" customWidth="1"/>
-    <col min="4" max="4" width="39" customWidth="1"/>
-    <col min="5" max="5" width="11.375" customWidth="1"/>
-    <col min="6" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="7" width="108.25" customWidth="1"/>
-    <col min="8" max="8" width="43.75" customWidth="1"/>
+    <col min="4" max="5" width="39" customWidth="1"/>
+    <col min="6" max="6" width="11.375" customWidth="1"/>
+    <col min="7" max="7" width="12.75" customWidth="1"/>
+    <col min="8" max="9" width="108.25" customWidth="1"/>
+    <col min="10" max="10" width="43.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:10" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:10" x14ac:dyDescent="0.15">
+      <c r="E2" s="41" t="s">
+        <v>348</v>
+      </c>
+      <c r="I2" s="41" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -12300,2207 +12792,2765 @@
         <v>1</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="5" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>10</v>
+        <v>279</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>9</v>
+        <v>279</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="J5" s="7" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="6" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="9">
         <v>10001</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="F6" s="9">
         <v>10001</v>
       </c>
-      <c r="F6" s="9">
+      <c r="G6" s="9">
         <v>15</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="H6" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="I6" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="7" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="9">
         <v>10002</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="F7" s="9">
         <v>10002</v>
       </c>
-      <c r="F7" s="9">
+      <c r="G7" s="9">
         <v>15</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="H7" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="I7" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="8" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="9">
         <v>10003</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="F8" s="9">
         <v>10003</v>
       </c>
-      <c r="F8" s="9">
+      <c r="G8" s="9">
         <v>15</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="H8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="I8" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="J8" s="12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C9" s="9">
         <v>10011</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="F9" s="9">
         <v>10011</v>
       </c>
-      <c r="F9" s="9">
+      <c r="G9" s="9">
         <v>22</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="H9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="I9" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="10" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C10" s="9">
         <v>10012</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="F10" s="9">
         <v>10012</v>
       </c>
-      <c r="F10" s="9">
+      <c r="G10" s="9">
         <v>22</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="H10" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="I10" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="J10" s="12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C11" s="9">
         <v>10013</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="F11" s="9">
         <v>10013</v>
       </c>
-      <c r="F11" s="9">
+      <c r="G11" s="9">
         <v>22</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="I11" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="J11" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="9">
         <v>10021</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F12" s="9">
         <v>10021</v>
       </c>
-      <c r="F12" s="9">
+      <c r="G12" s="9">
         <v>28</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="H12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="I12" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="J12" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="9">
         <v>10022</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="F13" s="9">
         <v>10022</v>
       </c>
-      <c r="F13" s="9">
+      <c r="G13" s="9">
         <v>28</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="H13" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="I13" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="J13" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C14" s="9">
         <v>10023</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="F14" s="9">
         <v>10023</v>
       </c>
-      <c r="F14" s="9">
+      <c r="G14" s="9">
         <v>28</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="H14" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="I14" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="J14" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C15" s="9">
         <v>10031</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="F15" s="9">
         <v>10031</v>
       </c>
-      <c r="F15" s="9">
+      <c r="G15" s="9">
         <v>32</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="H15" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="I15" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="J15" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C16" s="9">
         <v>10032</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="F16" s="9">
         <v>10032</v>
       </c>
-      <c r="F16" s="9">
+      <c r="G16" s="9">
         <v>32</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="H16" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="I16" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="J16" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="9">
         <v>10033</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="F17" s="9">
         <v>10033</v>
       </c>
-      <c r="F17" s="9">
+      <c r="G17" s="9">
         <v>32</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="H17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="I17" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="J17" s="12" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="9">
         <v>10041</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="F18" s="9">
         <v>10041</v>
       </c>
-      <c r="F18" s="9">
+      <c r="G18" s="9">
         <v>38</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="H18" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="I18" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="J18" s="11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="9">
         <v>10042</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="F19" s="9">
         <v>10042</v>
       </c>
-      <c r="F19" s="9">
+      <c r="G19" s="9">
         <v>38</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="H19" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="I19" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="J19" s="11" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="20" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C20" s="9">
         <v>10043</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="F20" s="9">
         <v>10043</v>
       </c>
-      <c r="F20" s="9">
+      <c r="G20" s="9">
         <v>38</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="H20" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="I20" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="J20" s="12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="9">
         <v>10051</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="F21" s="9">
         <v>10051</v>
       </c>
-      <c r="F21" s="9">
+      <c r="G21" s="9">
         <v>42</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="H21" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="I21" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="J21" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C22" s="9">
         <v>10052</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="F22" s="9">
         <v>10052</v>
       </c>
-      <c r="F22" s="9">
+      <c r="G22" s="9">
         <v>42</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="H22" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="I22" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="J22" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C23" s="9">
         <v>10053</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="F23" s="9">
         <v>10053</v>
       </c>
-      <c r="F23" s="9">
+      <c r="G23" s="9">
         <v>42</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="H23" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="I23" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="J23" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="14">
         <v>10061</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="F24" s="14">
         <v>10061</v>
       </c>
-      <c r="F24" s="14">
+      <c r="G24" s="14">
         <v>52</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="H24" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="H24" s="16" t="s">
+      <c r="I24" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="J24" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="14">
         <v>10062</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="F25" s="14">
         <v>10062</v>
       </c>
-      <c r="F25" s="14">
+      <c r="G25" s="14">
         <v>52</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="H25" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="H25" s="16" t="s">
+      <c r="I25" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="J25" s="16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C26" s="14">
         <v>10063</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="F26" s="14">
         <v>10063</v>
       </c>
-      <c r="F26" s="14">
+      <c r="G26" s="14">
         <v>52</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="H26" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="H26" s="17" t="s">
+      <c r="I26" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="J26" s="17" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C27" s="9">
         <v>20001</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F27" s="9">
         <v>20001</v>
       </c>
-      <c r="F27" s="9">
+      <c r="G27" s="9">
         <v>15</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="H27" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H27" s="12" t="s">
+      <c r="I27" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="J27" s="12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C28" s="9">
         <v>20002</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F28" s="9">
         <v>20002</v>
       </c>
-      <c r="F28" s="9">
+      <c r="G28" s="9">
         <v>15</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="H28" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="I28" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="J28" s="11" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="29" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C29" s="9">
         <v>20003</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F29" s="9">
         <v>20003</v>
       </c>
-      <c r="F29" s="9">
+      <c r="G29" s="9">
         <v>15</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="H29" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="H29" s="12" t="s">
+      <c r="I29" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="J29" s="12" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="30" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C30" s="9">
         <v>20011</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="F30" s="9">
         <v>20011</v>
       </c>
-      <c r="F30" s="9">
+      <c r="G30" s="9">
         <v>22</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="H30" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="I30" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="J30" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C31" s="9">
         <v>20012</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="F31" s="9">
         <v>20012</v>
       </c>
-      <c r="F31" s="9">
+      <c r="G31" s="9">
         <v>22</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="H31" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="I31" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="J31" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C32" s="9">
         <v>20013</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F32" s="9">
         <v>20013</v>
       </c>
-      <c r="F32" s="9">
+      <c r="G32" s="9">
         <v>22</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="H32" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="I32" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="J32" s="12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C33" s="9">
         <v>20021</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="F33" s="9">
         <v>20021</v>
       </c>
-      <c r="F33" s="9">
+      <c r="G33" s="9">
         <v>28</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="H33" s="12" t="s">
+      <c r="I33" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="J33" s="12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C34" s="9">
         <v>20022</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="F34" s="9">
         <v>20022</v>
       </c>
-      <c r="F34" s="9">
+      <c r="G34" s="9">
         <v>28</v>
       </c>
-      <c r="G34" s="10" t="s">
+      <c r="H34" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="I34" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="J34" s="12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C35" s="9">
         <v>20023</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="F35" s="9">
         <v>20023</v>
       </c>
-      <c r="F35" s="9">
+      <c r="G35" s="9">
         <v>28</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="I35" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="J35" s="12" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="36" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C36" s="9">
         <v>20031</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="F36" s="9">
         <v>20031</v>
       </c>
-      <c r="F36" s="9">
+      <c r="G36" s="9">
         <v>32</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="H36" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="I36" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="J36" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C37" s="9">
         <v>20032</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="F37" s="9">
         <v>20032</v>
       </c>
-      <c r="F37" s="9">
+      <c r="G37" s="9">
         <v>32</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="H37" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="I37" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="J37" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C38" s="9">
         <v>20033</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="F38" s="9">
         <v>20033</v>
       </c>
-      <c r="F38" s="9">
+      <c r="G38" s="9">
         <v>32</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="H38" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="H38" s="12" t="s">
+      <c r="I38" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="J38" s="12" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C39" s="9">
         <v>20041</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="F39" s="9">
         <v>20041</v>
       </c>
-      <c r="F39" s="9">
+      <c r="G39" s="9">
         <v>38</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="H39" s="11" t="s">
+      <c r="I39" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="J39" s="11" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="40" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C40" s="9">
         <v>20042</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="F40" s="9">
         <v>20042</v>
       </c>
-      <c r="F40" s="9">
+      <c r="G40" s="9">
         <v>38</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="H40" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="H40" s="12" t="s">
+      <c r="I40" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="J40" s="12" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C41" s="9">
         <v>20043</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="F41" s="9">
         <v>20043</v>
       </c>
-      <c r="F41" s="9">
+      <c r="G41" s="9">
         <v>38</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="H41" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="H41" s="12" t="s">
+      <c r="I41" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="J41" s="12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C42" s="9">
         <v>20051</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="F42" s="9">
         <v>20051</v>
       </c>
-      <c r="F42" s="9">
+      <c r="G42" s="9">
         <v>42</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="H42" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="H42" s="11" t="s">
+      <c r="I42" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="J42" s="11" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="9">
         <v>20052</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="F43" s="9">
         <v>20052</v>
       </c>
-      <c r="F43" s="9">
+      <c r="G43" s="9">
         <v>42</v>
       </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="H43" s="11" t="s">
+      <c r="I43" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="J43" s="11" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="44" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="9">
         <v>20053</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="F44" s="9">
         <v>20053</v>
       </c>
-      <c r="F44" s="9">
+      <c r="G44" s="9">
         <v>42</v>
       </c>
-      <c r="G44" s="10" t="s">
+      <c r="H44" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="H44" s="11" t="s">
+      <c r="I44" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="J44" s="11" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="9">
         <v>20061</v>
       </c>
       <c r="D45" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="F45" s="9">
         <v>20061</v>
       </c>
-      <c r="F45" s="14">
+      <c r="G45" s="14">
         <v>52</v>
       </c>
-      <c r="G45" s="13" t="s">
+      <c r="H45" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="I45" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="J45" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="9">
         <v>20062</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="F46" s="9">
         <v>20062</v>
       </c>
-      <c r="F46" s="14">
+      <c r="G46" s="14">
         <v>52</v>
       </c>
-      <c r="G46" s="13" t="s">
+      <c r="H46" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="H46" s="17" t="s">
+      <c r="I46" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="J46" s="17" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="47" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="9">
         <v>20063</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="F47" s="9">
         <v>20063</v>
       </c>
-      <c r="F47" s="14">
+      <c r="G47" s="14">
         <v>52</v>
       </c>
-      <c r="G47" s="13" t="s">
+      <c r="H47" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="H47" s="16" t="s">
+      <c r="I47" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="J47" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C48" s="9">
         <v>30001</v>
       </c>
       <c r="D48" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="F48" s="9">
         <v>30001</v>
       </c>
-      <c r="F48" s="9">
+      <c r="G48" s="9">
         <v>15</v>
       </c>
-      <c r="G48" s="19" t="s">
+      <c r="H48" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="H48" s="16" t="s">
+      <c r="I48" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="J48" s="16" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C49" s="9">
         <v>30002</v>
       </c>
       <c r="D49" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E49" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="F49" s="9">
         <v>30002</v>
       </c>
-      <c r="F49" s="9">
+      <c r="G49" s="9">
         <v>15</v>
       </c>
-      <c r="G49" s="19" t="s">
+      <c r="H49" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="H49" s="16" t="s">
+      <c r="I49" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="J49" s="16" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C50" s="9">
         <v>30003</v>
       </c>
       <c r="D50" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="F50" s="9">
         <v>30003</v>
       </c>
-      <c r="F50" s="9">
+      <c r="G50" s="9">
         <v>15</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="H50" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="H50" s="12" t="s">
+      <c r="I50" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="J50" s="12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C51" s="9">
         <v>30011</v>
       </c>
       <c r="D51" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="F51" s="9">
         <v>30011</v>
       </c>
-      <c r="F51" s="9">
+      <c r="G51" s="9">
         <v>22</v>
       </c>
-      <c r="G51" s="19" t="s">
+      <c r="H51" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="H51" s="16" t="s">
+      <c r="I51" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="J51" s="16" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="52" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C52" s="9">
         <v>30012</v>
       </c>
       <c r="D52" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="F52" s="9">
         <v>30012</v>
       </c>
-      <c r="F52" s="9">
+      <c r="G52" s="9">
         <v>22</v>
       </c>
-      <c r="G52" s="22" t="s">
+      <c r="H52" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="H52" s="12" t="s">
+      <c r="I52" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="J52" s="12" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C53" s="9">
         <v>30013</v>
       </c>
       <c r="D53" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="F53" s="9">
         <v>30013</v>
       </c>
-      <c r="F53" s="9">
+      <c r="G53" s="9">
         <v>22</v>
       </c>
-      <c r="G53" s="10" t="s">
+      <c r="H53" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="H53" s="12" t="s">
+      <c r="I53" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="J53" s="12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="54" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C54" s="9">
         <v>30021</v>
       </c>
       <c r="D54" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="F54" s="9">
         <v>30021</v>
       </c>
-      <c r="F54" s="9">
+      <c r="G54" s="9">
         <v>28</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="H54" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H54" s="12" t="s">
+      <c r="I54" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="J54" s="12" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="55" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C55" s="9">
         <v>30022</v>
       </c>
       <c r="D55" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E55" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="F55" s="9">
         <v>30022</v>
       </c>
-      <c r="F55" s="9">
+      <c r="G55" s="9">
         <v>28</v>
       </c>
-      <c r="G55" s="10" t="s">
+      <c r="H55" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="H55" s="16" t="s">
+      <c r="I55" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="J55" s="16" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="56" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C56" s="9">
         <v>30023</v>
       </c>
       <c r="D56" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="E56" s="9">
+      <c r="E56" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="F56" s="9">
         <v>30023</v>
       </c>
-      <c r="F56" s="9">
+      <c r="G56" s="9">
         <v>28</v>
       </c>
-      <c r="G56" s="10" t="s">
+      <c r="H56" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="H56" s="12" t="s">
+      <c r="I56" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="J56" s="12" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C57" s="9">
         <v>30031</v>
       </c>
       <c r="D57" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E57" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="F57" s="9">
         <v>30031</v>
       </c>
-      <c r="F57" s="9">
+      <c r="G57" s="9">
         <v>32</v>
       </c>
-      <c r="G57" s="10" t="s">
+      <c r="H57" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="H57" s="16" t="s">
+      <c r="I57" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="J57" s="16" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="58" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="9">
         <v>30032</v>
       </c>
       <c r="D58" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E58" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="F58" s="9">
         <v>30032</v>
       </c>
-      <c r="F58" s="9">
+      <c r="G58" s="9">
         <v>32</v>
       </c>
-      <c r="G58" s="24" t="s">
+      <c r="H58" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="H58" s="16" t="s">
+      <c r="I58" s="24" t="s">
+        <v>401</v>
+      </c>
+      <c r="J58" s="16" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="59" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C59" s="9">
         <v>30033</v>
       </c>
       <c r="D59" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E59" s="9">
+      <c r="E59" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="F59" s="9">
         <v>30033</v>
       </c>
-      <c r="F59" s="9">
+      <c r="G59" s="9">
         <v>32</v>
       </c>
-      <c r="G59" s="10" t="s">
+      <c r="H59" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="H59" s="12" t="s">
+      <c r="I59" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="J59" s="12" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="60" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C60" s="9">
         <v>30041</v>
       </c>
       <c r="D60" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="F60" s="9">
         <v>30041</v>
       </c>
-      <c r="F60" s="9">
+      <c r="G60" s="9">
         <v>38</v>
       </c>
-      <c r="G60" s="10" t="s">
+      <c r="H60" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="H60" s="12" t="s">
+      <c r="I60" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="J60" s="12" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="61" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C61" s="9">
         <v>30042</v>
       </c>
       <c r="D61" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="E61" s="9">
+      <c r="E61" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="F61" s="9">
         <v>30042</v>
       </c>
-      <c r="F61" s="9">
+      <c r="G61" s="9">
         <v>38</v>
       </c>
-      <c r="G61" s="10" t="s">
+      <c r="H61" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="H61" s="11" t="s">
+      <c r="I61" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="J61" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C62" s="9">
         <v>30043</v>
       </c>
       <c r="D62" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="E62" s="9">
+      <c r="E62" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="F62" s="9">
         <v>30043</v>
       </c>
-      <c r="F62" s="9">
+      <c r="G62" s="9">
         <v>38</v>
       </c>
-      <c r="G62" s="10" t="s">
+      <c r="H62" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="H62" s="12" t="s">
+      <c r="I62" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="J62" s="12" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C63" s="9">
         <v>30051</v>
       </c>
       <c r="D63" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="E63" s="9">
+      <c r="E63" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="F63" s="9">
         <v>30051</v>
       </c>
-      <c r="F63" s="9">
+      <c r="G63" s="9">
         <v>42</v>
       </c>
-      <c r="G63" s="10" t="s">
+      <c r="H63" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="H63" s="12" t="s">
+      <c r="I63" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="J63" s="12" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="64" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C64" s="9">
         <v>30052</v>
       </c>
       <c r="D64" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="E64" s="9">
+      <c r="E64" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="F64" s="9">
         <v>30052</v>
       </c>
-      <c r="F64" s="9">
+      <c r="G64" s="9">
         <v>42</v>
       </c>
-      <c r="G64" s="25" t="s">
+      <c r="H64" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="H64" s="11" t="s">
+      <c r="I64" s="25" t="s">
+        <v>407</v>
+      </c>
+      <c r="J64" s="11" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="65" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C65" s="9">
         <v>30053</v>
       </c>
       <c r="D65" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E65" s="9">
+      <c r="E65" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="F65" s="9">
         <v>30053</v>
       </c>
-      <c r="F65" s="9">
+      <c r="G65" s="9">
         <v>42</v>
       </c>
-      <c r="G65" s="10" t="s">
+      <c r="H65" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H65" s="12" t="s">
+      <c r="I65" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="J65" s="12" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="66" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C66" s="9">
         <v>30061</v>
       </c>
       <c r="D66" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="E66" s="9">
+      <c r="E66" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="F66" s="9">
         <v>30061</v>
       </c>
-      <c r="F66" s="14">
+      <c r="G66" s="14">
         <v>52</v>
       </c>
-      <c r="G66" s="13" t="s">
+      <c r="H66" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="H66" s="16" t="s">
+      <c r="I66" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="J66" s="16" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="67" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C67" s="9">
         <v>30062</v>
       </c>
       <c r="D67" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="E67" s="9">
+      <c r="E67" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="F67" s="9">
         <v>30062</v>
       </c>
-      <c r="F67" s="14">
+      <c r="G67" s="14">
         <v>52</v>
       </c>
-      <c r="G67" s="27" t="s">
+      <c r="H67" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="H67" s="17" t="s">
+      <c r="I67" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="J67" s="17" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="68" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C68" s="9">
         <v>30063</v>
       </c>
       <c r="D68" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="E68" s="9">
+      <c r="E68" s="28" t="s">
+        <v>329</v>
+      </c>
+      <c r="F68" s="9">
         <v>30063</v>
       </c>
-      <c r="F68" s="14">
+      <c r="G68" s="14">
         <v>52</v>
       </c>
-      <c r="G68" s="29" t="s">
+      <c r="H68" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="H68" s="16" t="s">
+      <c r="I68" s="29" t="s">
+        <v>411</v>
+      </c>
+      <c r="J68" s="16" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="69" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C69" s="14">
         <v>40001</v>
       </c>
       <c r="D69" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="E69" s="14">
+      <c r="E69" s="31" t="s">
+        <v>330</v>
+      </c>
+      <c r="F69" s="14">
         <v>40001</v>
       </c>
-      <c r="F69" s="9">
+      <c r="G69" s="9">
         <v>15</v>
       </c>
-      <c r="G69" s="32" t="s">
+      <c r="H69" s="32" t="s">
         <v>209</v>
       </c>
-      <c r="H69" s="16" t="s">
+      <c r="I69" s="32" t="s">
+        <v>412</v>
+      </c>
+      <c r="J69" s="16" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="70" spans="3:8" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C70" s="14">
         <v>40002</v>
       </c>
       <c r="D70" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="E70" s="14">
+      <c r="E70" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="F70" s="14">
         <v>40002</v>
       </c>
-      <c r="F70" s="9">
+      <c r="G70" s="9">
         <v>15</v>
       </c>
-      <c r="G70" s="10" t="s">
+      <c r="H70" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="H70" s="12" t="s">
+      <c r="I70" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="J70" s="12" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="71" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="3:10" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C71" s="33">
         <v>40003</v>
       </c>
       <c r="D71" s="34" t="s">
         <v>241</v>
       </c>
-      <c r="E71" s="33">
+      <c r="E71" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="F71" s="33">
         <v>40003</v>
       </c>
-      <c r="F71" s="9">
+      <c r="G71" s="9">
         <v>15</v>
       </c>
-      <c r="G71" s="35" t="s">
+      <c r="H71" s="35" t="s">
         <v>212</v>
       </c>
-      <c r="H71" s="16" t="s">
+      <c r="I71" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="J71" s="16" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="72" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C72" s="14">
         <v>40011</v>
       </c>
       <c r="D72" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="E72" s="14">
+      <c r="E72" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="F72" s="14">
         <v>40011</v>
       </c>
-      <c r="F72" s="9">
+      <c r="G72" s="9">
         <v>22</v>
       </c>
-      <c r="G72" s="32" t="s">
+      <c r="H72" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="H72" s="16" t="s">
+      <c r="I72" s="32" t="s">
+        <v>415</v>
+      </c>
+      <c r="J72" s="16" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="73" spans="3:8" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C73" s="14">
         <v>40012</v>
       </c>
       <c r="D73" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="E73" s="14">
+      <c r="E73" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="F73" s="14">
         <v>40012</v>
       </c>
-      <c r="F73" s="9">
+      <c r="G73" s="9">
         <v>22</v>
       </c>
-      <c r="G73" s="32" t="s">
+      <c r="H73" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="H73" s="16" t="s">
+      <c r="I73" s="32" t="s">
+        <v>416</v>
+      </c>
+      <c r="J73" s="16" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="74" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="3:10" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C74" s="33">
         <v>40013</v>
       </c>
       <c r="D74" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="E74" s="33">
+      <c r="E74" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="F74" s="33">
         <v>40013</v>
       </c>
-      <c r="F74" s="9">
+      <c r="G74" s="9">
         <v>22</v>
       </c>
-      <c r="G74" s="35" t="s">
+      <c r="H74" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="H74" s="40" t="s">
+      <c r="I74" s="35" t="s">
+        <v>417</v>
+      </c>
+      <c r="J74" s="40" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="75" spans="3:8" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C75" s="14">
         <v>40021</v>
       </c>
       <c r="D75" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="E75" s="14">
+      <c r="E75" s="31" t="s">
+        <v>334</v>
+      </c>
+      <c r="F75" s="14">
         <v>40021</v>
       </c>
-      <c r="F75" s="9">
+      <c r="G75" s="9">
         <v>28</v>
       </c>
-      <c r="G75" s="32" t="s">
+      <c r="H75" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="H75" s="16" t="s">
+      <c r="I75" s="32" t="s">
+        <v>418</v>
+      </c>
+      <c r="J75" s="16" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="76" spans="3:8" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C76" s="14">
         <v>40022</v>
       </c>
       <c r="D76" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="E76" s="14">
+      <c r="E76" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="F76" s="14">
         <v>40022</v>
       </c>
-      <c r="F76" s="9">
+      <c r="G76" s="9">
         <v>28</v>
       </c>
-      <c r="G76" s="32" t="s">
+      <c r="H76" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="H76" s="12" t="s">
+      <c r="I76" s="32" t="s">
+        <v>419</v>
+      </c>
+      <c r="J76" s="12" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="77" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="3:10" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C77" s="33">
         <v>40023</v>
       </c>
       <c r="D77" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="E77" s="33">
+      <c r="E77" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="F77" s="33">
         <v>40023</v>
       </c>
-      <c r="F77" s="9">
+      <c r="G77" s="9">
         <v>28</v>
       </c>
-      <c r="G77" s="35" t="s">
+      <c r="H77" s="35" t="s">
         <v>223</v>
       </c>
-      <c r="H77" s="12" t="s">
+      <c r="I77" s="35" t="s">
+        <v>420</v>
+      </c>
+      <c r="J77" s="12" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="78" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="3:10" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C78" s="33">
         <v>40031</v>
       </c>
       <c r="D78" s="37" t="s">
         <v>247</v>
       </c>
-      <c r="E78" s="33">
+      <c r="E78" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="F78" s="33">
         <v>40031</v>
       </c>
-      <c r="F78" s="9">
+      <c r="G78" s="9">
         <v>32</v>
       </c>
-      <c r="G78" s="38" t="s">
+      <c r="H78" s="38" t="s">
         <v>246</v>
       </c>
-      <c r="H78" s="39" t="s">
+      <c r="I78" s="38" t="s">
+        <v>421</v>
+      </c>
+      <c r="J78" s="39" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="79" spans="3:8" s="36" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="3:10" s="36" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C79" s="33">
         <v>40032</v>
       </c>
       <c r="D79" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="E79" s="33">
+      <c r="E79" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="F79" s="33">
         <v>40032</v>
       </c>
-      <c r="F79" s="9">
+      <c r="G79" s="9">
         <v>32</v>
       </c>
-      <c r="G79" s="38" t="s">
+      <c r="H79" s="38" t="s">
         <v>257</v>
       </c>
-      <c r="H79" s="12" t="s">
+      <c r="I79" s="38" t="s">
+        <v>422</v>
+      </c>
+      <c r="J79" s="12" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="80" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="3:10" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C80" s="33">
         <v>40033</v>
       </c>
       <c r="D80" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="E80" s="33">
+      <c r="E80" s="34" t="s">
+        <v>336</v>
+      </c>
+      <c r="F80" s="33">
         <v>40033</v>
       </c>
-      <c r="F80" s="9">
+      <c r="G80" s="9">
         <v>32</v>
       </c>
-      <c r="G80" s="35" t="s">
+      <c r="H80" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="H80" s="12" t="s">
+      <c r="I80" s="35" t="s">
+        <v>395</v>
+      </c>
+      <c r="J80" s="12" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:10" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C81" s="33">
         <v>40041</v>
       </c>
       <c r="D81" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="E81" s="33">
+      <c r="E81" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="F81" s="33">
         <v>40041</v>
       </c>
-      <c r="F81" s="9">
+      <c r="G81" s="9">
         <v>38</v>
       </c>
-      <c r="G81" s="38" t="s">
+      <c r="H81" s="38" t="s">
         <v>258</v>
       </c>
-      <c r="H81" s="12" t="s">
+      <c r="I81" s="38" t="s">
+        <v>423</v>
+      </c>
+      <c r="J81" s="12" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="82" spans="3:8" s="36" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:10" s="36" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C82" s="33">
         <v>40042</v>
       </c>
       <c r="D82" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="E82" s="33">
+      <c r="E82" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="F82" s="33">
         <v>40042</v>
       </c>
-      <c r="F82" s="9">
+      <c r="G82" s="9">
         <v>38</v>
       </c>
-      <c r="G82" s="38" t="s">
+      <c r="H82" s="38" t="s">
         <v>238</v>
       </c>
-      <c r="H82" s="39" t="s">
+      <c r="I82" s="38" t="s">
+        <v>424</v>
+      </c>
+      <c r="J82" s="39" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="83" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="3:10" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C83" s="33">
         <v>40043</v>
       </c>
       <c r="D83" s="34" t="s">
         <v>250</v>
       </c>
-      <c r="E83" s="33">
+      <c r="E83" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="F83" s="33">
         <v>40043</v>
       </c>
-      <c r="F83" s="9">
+      <c r="G83" s="9">
         <v>38</v>
       </c>
-      <c r="G83" s="35" t="s">
+      <c r="H83" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="H83" s="12" t="s">
+      <c r="I83" s="35" t="s">
+        <v>425</v>
+      </c>
+      <c r="J83" s="12" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="84" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="3:10" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C84" s="33">
         <v>40051</v>
       </c>
       <c r="D84" s="37" t="s">
         <v>252</v>
       </c>
-      <c r="E84" s="33">
+      <c r="E84" s="37" t="s">
+        <v>321</v>
+      </c>
+      <c r="F84" s="33">
         <v>40051</v>
       </c>
-      <c r="F84" s="9">
+      <c r="G84" s="9">
         <v>42</v>
       </c>
-      <c r="G84" s="38" t="s">
+      <c r="H84" s="38" t="s">
         <v>251</v>
       </c>
-      <c r="H84" s="39" t="s">
+      <c r="I84" s="38" t="s">
+        <v>426</v>
+      </c>
+      <c r="J84" s="39" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="85" spans="3:8" s="36" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="3:10" s="36" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C85" s="33">
         <v>40052</v>
       </c>
       <c r="D85" s="37" t="s">
         <v>240</v>
       </c>
-      <c r="E85" s="33">
+      <c r="E85" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="F85" s="33">
         <v>40052</v>
       </c>
-      <c r="F85" s="9">
+      <c r="G85" s="9">
         <v>42</v>
       </c>
-      <c r="G85" s="38" t="s">
+      <c r="H85" s="38" t="s">
         <v>261</v>
       </c>
-      <c r="H85" s="12" t="s">
+      <c r="I85" s="38" t="s">
+        <v>427</v>
+      </c>
+      <c r="J85" s="12" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="86" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="3:10" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C86" s="33">
         <v>40053</v>
       </c>
       <c r="D86" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="E86" s="33">
+      <c r="E86" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="F86" s="33">
         <v>40053</v>
       </c>
-      <c r="F86" s="9">
+      <c r="G86" s="9">
         <v>42</v>
       </c>
-      <c r="G86" s="35" t="s">
+      <c r="H86" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="H86" s="17" t="s">
+      <c r="I86" s="35" t="s">
+        <v>428</v>
+      </c>
+      <c r="J86" s="17" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="87" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:10" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C87" s="33">
         <v>40061</v>
       </c>
       <c r="D87" s="37" t="s">
         <v>254</v>
       </c>
-      <c r="E87" s="33">
+      <c r="E87" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="F87" s="33">
         <v>40061</v>
       </c>
-      <c r="F87" s="14">
+      <c r="G87" s="14">
         <v>52</v>
       </c>
-      <c r="G87" s="38" t="s">
+      <c r="H87" s="38" t="s">
         <v>235</v>
       </c>
-      <c r="H87" s="39" t="s">
+      <c r="I87" s="38" t="s">
+        <v>429</v>
+      </c>
+      <c r="J87" s="39" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="88" spans="3:8" s="36" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:10" s="36" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C88" s="33">
         <v>40062</v>
       </c>
       <c r="D88" s="37" t="s">
         <v>255</v>
       </c>
-      <c r="E88" s="33">
+      <c r="E88" s="37" t="s">
+        <v>340</v>
+      </c>
+      <c r="F88" s="33">
         <v>40062</v>
       </c>
-      <c r="F88" s="14">
+      <c r="G88" s="14">
         <v>52</v>
       </c>
-      <c r="G88" s="38" t="s">
+      <c r="H88" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="H88" s="16" t="s">
+      <c r="I88" s="38" t="s">
+        <v>430</v>
+      </c>
+      <c r="J88" s="16" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="89" spans="3:8" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:10" s="36" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C89" s="33">
         <v>40063</v>
       </c>
       <c r="D89" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="E89" s="33">
+      <c r="E89" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="F89" s="33">
         <v>40063</v>
       </c>
-      <c r="F89" s="14">
+      <c r="G89" s="14">
         <v>52</v>
       </c>
-      <c r="G89" s="35" t="s">
+      <c r="H89" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="H89" s="17" t="s">
+      <c r="I89" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="J89" s="17" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="90" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C90" s="9">
         <v>90001</v>
       </c>
       <c r="D90" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E90" s="9">
+      <c r="E90" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="F90" s="9">
         <v>60010100</v>
       </c>
-      <c r="F90" s="9">
+      <c r="G90" s="9">
         <v>1</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="H90" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="H90" s="12" t="s">
+      <c r="I90" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="J90" s="12" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="91" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C91" s="9">
         <v>90002</v>
       </c>
       <c r="D91" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E91" s="9">
+      <c r="E91" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="F91" s="9">
         <v>60010200</v>
       </c>
-      <c r="F91" s="9">
+      <c r="G91" s="9">
         <v>1</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="H91" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H91" s="12" t="s">
+      <c r="I91" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="J91" s="12" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="92" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C92" s="9">
         <v>90003</v>
       </c>
       <c r="D92" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="E92" s="9">
+      <c r="E92" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="F92" s="9">
         <v>60010300</v>
       </c>
-      <c r="F92" s="9">
+      <c r="G92" s="9">
         <v>1</v>
       </c>
-      <c r="G92" s="3" t="s">
+      <c r="H92" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="H92" s="12" t="s">
+      <c r="I92" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="J92" s="12" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="93" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C93" s="9">
         <v>90004</v>
       </c>
       <c r="D93" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="E93" s="9">
+      <c r="E93" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="F93" s="9">
         <v>60010400</v>
       </c>
-      <c r="F93" s="9">
+      <c r="G93" s="9">
         <v>2</v>
       </c>
-      <c r="G93" s="3" t="s">
+      <c r="H93" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H93" s="12" t="s">
+      <c r="I93" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="J93" s="12" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="94" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C94" s="9">
         <v>90005</v>
       </c>
       <c r="D94" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E94" s="9">
+      <c r="E94" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="F94" s="9">
         <v>60010500</v>
       </c>
-      <c r="F94" s="9">
+      <c r="G94" s="9">
         <v>2</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="H94" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H94" s="12" t="s">
+      <c r="I94" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="J94" s="12" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="95" spans="3:8" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C95" s="9">
         <v>90006</v>
       </c>
       <c r="D95" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E95" s="9">
+      <c r="E95" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="F95" s="9">
         <v>60010600</v>
       </c>
-      <c r="F95" s="9">
+      <c r="G95" s="9">
         <v>2</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="H95" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="H95" s="12" t="s">
+      <c r="I95" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="J95" s="12" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="96" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C96" s="9">
         <v>100001</v>
       </c>
-      <c r="E96" s="9">
+      <c r="F96" s="9">
         <v>0</v>
       </c>
-      <c r="F96" s="9">
+      <c r="G96" s="9">
         <v>1</v>
       </c>
-      <c r="H96" s="30" t="s">
+      <c r="J96" s="30" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="97" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C97" s="9">
         <v>100002</v>
       </c>
-      <c r="E97" s="9">
+      <c r="F97" s="9">
         <v>0</v>
       </c>
-      <c r="F97" s="9">
+      <c r="G97" s="9">
         <v>1</v>
       </c>
-      <c r="H97" s="30" t="s">
+      <c r="J97" s="30" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="98" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C98" s="9">
         <v>100003</v>
       </c>
-      <c r="E98" s="9">
+      <c r="F98" s="9">
         <v>0</v>
       </c>
-      <c r="F98" s="9">
+      <c r="G98" s="9">
         <v>1</v>
       </c>
-      <c r="H98" s="30" t="s">
+      <c r="J98" s="30" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="99" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C99" s="9">
         <v>100004</v>
       </c>
-      <c r="E99" s="9">
+      <c r="F99" s="9">
         <v>0</v>
       </c>
-      <c r="F99" s="9">
+      <c r="G99" s="9">
         <v>1</v>
       </c>
-      <c r="H99" s="30" t="s">
+      <c r="J99" s="30" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="100" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C100" s="9">
         <v>100005</v>
       </c>
-      <c r="E100" s="9">
+      <c r="F100" s="9">
         <v>0</v>
       </c>
-      <c r="F100" s="9">
+      <c r="G100" s="9">
         <v>1</v>
       </c>
-      <c r="H100" s="30" t="s">
+      <c r="J100" s="30" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="101" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C101" s="9">
         <v>100006</v>
       </c>
-      <c r="E101" s="9">
+      <c r="F101" s="9">
         <v>0</v>
       </c>
-      <c r="F101" s="9">
+      <c r="G101" s="9">
         <v>1</v>
       </c>
-      <c r="H101" s="30" t="s">
+      <c r="J101" s="30" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="102" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C102" s="9">
         <v>100007</v>
       </c>
-      <c r="E102" s="9">
+      <c r="F102" s="9">
         <v>0</v>
       </c>
-      <c r="F102" s="9">
+      <c r="G102" s="9">
         <v>1</v>
       </c>
-      <c r="H102" s="30" t="s">
+      <c r="J102" s="30" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="103" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C103" s="9">
         <v>100008</v>
       </c>
-      <c r="E103" s="9">
+      <c r="F103" s="9">
         <v>0</v>
       </c>
-      <c r="F103" s="9">
+      <c r="G103" s="9">
         <v>1</v>
       </c>
-      <c r="H103" s="30" t="s">
+      <c r="J103" s="30" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="104" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C104" s="9">
         <v>100009</v>
       </c>
-      <c r="E104" s="9">
+      <c r="F104" s="9">
         <v>0</v>
       </c>
-      <c r="F104" s="9">
+      <c r="G104" s="9">
         <v>1</v>
       </c>
-      <c r="H104" s="30" t="s">
+      <c r="J104" s="30" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="105" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C105" s="9">
         <v>100010</v>
       </c>
-      <c r="E105" s="9">
+      <c r="F105" s="9">
         <v>0</v>
       </c>
-      <c r="F105" s="9">
+      <c r="G105" s="9">
         <v>1</v>
       </c>
-      <c r="H105" s="30" t="s">
+      <c r="J105" s="30" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="106" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C106" s="9">
         <v>200001</v>
       </c>
-      <c r="E106" s="9">
+      <c r="F106" s="9">
         <v>0</v>
       </c>
-      <c r="F106" s="9">
+      <c r="G106" s="9">
         <v>1</v>
       </c>
-      <c r="H106" s="30" t="s">
+      <c r="J106" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="O106" s="9"/>
+      <c r="Q106" s="9"/>
     </row>
-    <row r="107" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C107" s="9">
         <v>200002</v>
       </c>
-      <c r="E107" s="9">
+      <c r="F107" s="9">
         <v>0</v>
       </c>
-      <c r="F107" s="9">
+      <c r="G107" s="9">
         <v>1</v>
       </c>
-      <c r="H107" s="30" t="s">
+      <c r="J107" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="O107" s="9"/>
+      <c r="Q107" s="9"/>
     </row>
-    <row r="108" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C108" s="9">
         <v>200003</v>
       </c>
-      <c r="E108" s="9">
+      <c r="F108" s="9">
         <v>0</v>
       </c>
-      <c r="F108" s="9">
+      <c r="G108" s="9">
         <v>1</v>
       </c>
-      <c r="H108" s="30" t="s">
+      <c r="J108" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="O108" s="9"/>
+      <c r="Q108" s="9"/>
     </row>
-    <row r="109" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C109" s="9">
         <v>200004</v>
       </c>
-      <c r="E109" s="9">
+      <c r="F109" s="9">
         <v>0</v>
       </c>
-      <c r="F109" s="9">
+      <c r="G109" s="9">
         <v>1</v>
       </c>
-      <c r="H109" s="30" t="s">
+      <c r="J109" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="O109" s="9"/>
+      <c r="Q109" s="9"/>
     </row>
-    <row r="110" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C110" s="9">
         <v>200005</v>
       </c>
-      <c r="E110" s="9">
+      <c r="F110" s="9">
         <v>0</v>
       </c>
-      <c r="F110" s="9">
+      <c r="G110" s="9">
         <v>1</v>
       </c>
-      <c r="H110" s="30" t="s">
+      <c r="J110" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="O110" s="9"/>
+      <c r="Q110" s="9"/>
     </row>
-    <row r="111" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C111" s="9">
         <v>200006</v>
       </c>
-      <c r="E111" s="9">
+      <c r="F111" s="9">
         <v>0</v>
       </c>
-      <c r="F111" s="9">
+      <c r="G111" s="9">
         <v>1</v>
       </c>
-      <c r="H111" s="30" t="s">
+      <c r="J111" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="O111" s="9"/>
+      <c r="Q111" s="9"/>
     </row>
-    <row r="112" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C112" s="9">
         <v>200007</v>
       </c>
-      <c r="E112" s="9">
+      <c r="F112" s="9">
         <v>0</v>
       </c>
-      <c r="F112" s="9">
+      <c r="G112" s="9">
         <v>1</v>
       </c>
-      <c r="H112" s="30" t="s">
+      <c r="J112" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="O112" s="9"/>
+      <c r="Q112" s="9"/>
     </row>
-    <row r="113" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C113" s="9">
         <v>200008</v>
       </c>
-      <c r="E113" s="9">
+      <c r="F113" s="9">
         <v>0</v>
       </c>
-      <c r="F113" s="9">
+      <c r="G113" s="9">
         <v>1</v>
       </c>
-      <c r="H113" s="30" t="s">
+      <c r="J113" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="O113" s="9"/>
+      <c r="Q113" s="9"/>
     </row>
-    <row r="114" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C114" s="9">
         <v>200009</v>
       </c>
-      <c r="E114" s="9">
+      <c r="F114" s="9">
         <v>0</v>
       </c>
-      <c r="F114" s="9">
+      <c r="G114" s="9">
         <v>1</v>
       </c>
-      <c r="H114" s="30" t="s">
+      <c r="J114" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="O114" s="9"/>
+      <c r="Q114" s="9"/>
     </row>
-    <row r="115" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C115" s="9">
         <v>200010</v>
       </c>
-      <c r="E115" s="9">
+      <c r="F115" s="9">
         <v>0</v>
       </c>
-      <c r="F115" s="9">
+      <c r="G115" s="9">
         <v>1</v>
       </c>
-      <c r="H115" s="30" t="s">
+      <c r="J115" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="O115" s="9"/>
+      <c r="Q115" s="9"/>
     </row>
-    <row r="116" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C116" s="9">
         <v>200011</v>
       </c>
-      <c r="E116" s="9">
+      <c r="F116" s="9">
         <v>0</v>
       </c>
-      <c r="F116" s="9">
+      <c r="G116" s="9">
         <v>1</v>
       </c>
-      <c r="H116" s="30" t="s">
+      <c r="J116" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="O116" s="9"/>
+      <c r="Q116" s="9"/>
     </row>
-    <row r="117" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C117" s="9">
         <v>200012</v>
       </c>
-      <c r="E117" s="9">
+      <c r="F117" s="9">
         <v>0</v>
       </c>
-      <c r="F117" s="9">
+      <c r="G117" s="9">
         <v>1</v>
       </c>
-      <c r="H117" s="30" t="s">
+      <c r="J117" s="30" t="s">
         <v>181</v>
       </c>
-      <c r="O117" s="9"/>
+      <c r="Q117" s="9"/>
     </row>
-    <row r="118" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C118" s="9">
         <v>200013</v>
       </c>
-      <c r="E118" s="9">
+      <c r="F118" s="9">
         <v>0</v>
       </c>
-      <c r="F118" s="9">
+      <c r="G118" s="9">
         <v>1</v>
       </c>
-      <c r="H118" s="30" t="s">
+      <c r="J118" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="O118" s="9"/>
+      <c r="Q118" s="9"/>
     </row>
-    <row r="119" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C119" s="9">
         <v>200014</v>
       </c>
-      <c r="E119" s="9">
+      <c r="F119" s="9">
         <v>0</v>
       </c>
-      <c r="F119" s="9">
+      <c r="G119" s="9">
         <v>1</v>
       </c>
-      <c r="H119" s="30" t="s">
+      <c r="J119" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="O119" s="9"/>
+      <c r="Q119" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293F2D47-E773-4348-A0BF-1C91ECCAA22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6409D7-3525-42F7-B866-D387ED99BF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TalentProto" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="478">
   <si>
     <t>c</t>
   </si>
@@ -306,9 +306,6 @@
     <t>轰击</t>
   </si>
   <si>
-    <t>新增技能:轰击 立即对目标及其范围造成350%+1000点伤害</t>
-  </si>
-  <si>
     <t>SkillIdAdd;62000101</t>
   </si>
   <si>
@@ -355,9 +352,6 @@
   </si>
   <si>
     <t>英勇守护</t>
-  </si>
-  <si>
-    <t>受到伤害有15%概率触发守护之击</t>
   </si>
   <si>
     <t>SkillIdAdd;62000104</t>
@@ -679,703 +673,894 @@
     <t>SkillIdAdd;62000061</t>
   </si>
   <si>
+    <t>SkillPropertyAdd;64011202,64011203,64011204,64011205,64011206;2;0.75@SkillPropertyAdd;64012202,64012203,64012204,64012205,64012206;2;0.75</t>
+  </si>
+  <si>
+    <t>恢复之手</t>
+  </si>
+  <si>
+    <t>每次使用技能有一定概率恢复自身的一定生命值</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000062</t>
+  </si>
+  <si>
+    <t>魔法印记</t>
+  </si>
+  <si>
+    <t>Magic Mark</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000063</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000065</t>
+  </si>
+  <si>
+    <t>勇猛之力</t>
+  </si>
+  <si>
+    <t>自身普攻伤害提升25%</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;60000601,60000602,60000701,60000702;2;0.25</t>
+  </si>
+  <si>
+    <t>疾风光环</t>
+  </si>
+  <si>
+    <t>每次普攻提升5%攻击速度和移动速度，最多可叠5层</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000066</t>
+  </si>
+  <si>
+    <t>魔闪之击冷却时间降低1秒，燃烧魔球伤害提升75%，契约之地伤害提升25%</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;64013102,64013103,64013104,64013105,64013106;4;1@SkillPropertyAdd;64014202,64014203,64014204,64014205,64014206;2;0.75@SkillPropertyAdd;64015102,64015103,64015104,64015105,64015106;2;0.25</t>
+  </si>
+  <si>
+    <t>造成伤害提升5%</t>
+  </si>
+  <si>
+    <t>魔法之力</t>
+  </si>
+  <si>
+    <t>每层魔法印记造成的伤害提升10%</t>
+  </si>
+  <si>
+    <t>BuffPropertyAdd;95100001;1;0.1</t>
+  </si>
+  <si>
+    <t>暗影投掷冷却时间降低1秒;燃烧魔球冷却时间降低1秒;雷鸣之力冷却时间降低3秒</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;64013202,64013203,64013204,64013205,64013206;4;1@SkillPropertyAdd;64014202,64014203,64014204,64014205,64014206;4;1@SkillPropertyAdd;64015202,64015203,64015204,64015205,64015206;4;1</t>
+  </si>
+  <si>
+    <t>召唤之力</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000068</t>
+  </si>
+  <si>
+    <t>极速轰炸技能伤害提升75%;疾风烈焰技能冷却时间降低2秒;黑暗魔爆伤害提升75%</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;64013302,64013303,64013304,64013305,64013306;2;0.75@SkillPropertyAdd;64014302,64014303,64014304,64014305,64014106;4;1@SkillPropertyAdd;64015302,64015303,64015304,64015305,64015306;2;0.75</t>
+  </si>
+  <si>
+    <t>雷鸣之力</t>
+  </si>
+  <si>
+    <t>主动技能:雷鸣之力,立即对自身周围范围的6个区域造成350%闪电伤害，并造成1秒眩晕</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000067</t>
+  </si>
+  <si>
+    <t>迅捷移动</t>
+  </si>
+  <si>
+    <t>Swift Movement</t>
+  </si>
+  <si>
+    <t>移动速度提升15%</t>
+  </si>
+  <si>
+    <t>RolePropertyAdd;100902;0.15</t>
+  </si>
+  <si>
+    <t>造成暴击后会额外提升自身15%攻击,持续10秒</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000069</t>
+  </si>
+  <si>
+    <t>火焰旋风技能伤害提升75%;风神之女普攻伤害提升50%;恶魔契约冷却时间降低5秒</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;64013402,64013403,64013404,64013405,64013406;2;0.75@SkillPropertyAdd;64014451,64014452,64014453,64014454,64014455;2;0.5@SkillPropertyAdd;64015402,64015403,64015404,64015405,64015406;4;5</t>
+  </si>
+  <si>
+    <t>技能冷却时间降低5%</t>
+  </si>
+  <si>
+    <t>RolePropertyAdd;203603;0.05</t>
+  </si>
+  <si>
+    <t>召唤仪式</t>
+  </si>
+  <si>
+    <t>Summoning Ritual</t>
+  </si>
+  <si>
+    <t>每次使用技能会有概率额外召唤一个仪式怪物协助自身战斗</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000070</t>
+  </si>
+  <si>
+    <t>防御守护</t>
+  </si>
+  <si>
+    <t>新增防御守护技能,受到伤害有一定概率立即对自身范围内的怪物造成350%攻击伤害+2000,并击退周围附近敌方目标</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000064</t>
+  </si>
+  <si>
+    <t>技之能力</t>
+  </si>
+  <si>
+    <t>RolePropertyAdd;204103;0.1</t>
+  </si>
+  <si>
+    <t>生命提升</t>
+  </si>
+  <si>
+    <t>Health increase</t>
+  </si>
+  <si>
+    <t>攻击+10;攻击+20;攻击+30</t>
+  </si>
+  <si>
+    <t>Attack +10; Attack +20; Attack +30</t>
+  </si>
+  <si>
+    <t>RolePropertyAdd;100203;50</t>
+  </si>
+  <si>
+    <t>光环技能范围</t>
+  </si>
+  <si>
+    <t>Auras Skill Range</t>
+  </si>
+  <si>
+    <t>旋风斩的技能伤害范围+1;旋风斩的技能伤害范围+2</t>
+  </si>
+  <si>
+    <t>The skill damage range of Whirlwind Slash increases by 1; The skill damage range of Whirlwind Slash increases by 2</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;80000013;1;10</t>
+  </si>
+  <si>
+    <t>元素法球附带给自身加血对敌人定身效果</t>
+  </si>
+  <si>
+    <t>Elemental Ball attaches health to itself and stuns enemies</t>
+  </si>
+  <si>
+    <t>前冲距离延长3码距离</t>
+  </si>
+  <si>
+    <t>Forward movement distance extended by 3 yards</t>
+  </si>
+  <si>
+    <t>BuffIdAdd;61021201;90001021@BuffInitIdAdd;61021201;90000005</t>
+  </si>
+  <si>
+    <t>技能元素爆冰更换为元素法球</t>
+  </si>
+  <si>
+    <t>Change Skill Elemental Blast Ice to Elemental Ball</t>
+  </si>
+  <si>
+    <t>使用审判时可以将目标减速30%,持续3秒;使用审判时可以将目标减速30%,持续5秒</t>
+  </si>
+  <si>
+    <t>When using Judgment, you can slow the target by 30% for 3 seconds; when using Judgment, you can slow the target by 30% for 5 seconds.</t>
+  </si>
+  <si>
+    <t>ReplaceSkillId;61021301;61021201</t>
+  </si>
+  <si>
+    <t>新增技能光环</t>
+  </si>
+  <si>
+    <t>New skill aura</t>
+  </si>
+  <si>
+    <t>击杀怪物获得金币+1%;击杀怪物获得金币+2%;击杀怪物获得金币+3%;击杀怪物获得金币+4%;击杀怪物获得金币+5%</t>
+  </si>
+  <si>
+    <t>Kill monsters and gain 1% of gold; Kill monsters and gain 2% of gold; Kill monsters and gain 3% of gold; Kill monsters and gain 4% of gold; Kill monsters and gain 5% of gold</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;80000013</t>
+  </si>
+  <si>
+    <t>延长速度降低的时间</t>
+  </si>
+  <si>
+    <t>Extended speed reduction duration</t>
+  </si>
+  <si>
+    <t>基础移动速度+4%;基础移动速度+8%;基础移动速度+12%;基础移动速度+16%;基础移动速度+20%</t>
+  </si>
+  <si>
+    <t>Base movement speed + 4%; Base movement speed + 8%; Base movement speed + 12%; Base movement speed + 16%; Base movement speed + 20%</t>
+  </si>
+  <si>
+    <t>BuffPropertyAdd;90001032;2;10</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;61012102,61012103,61012104,61012105,61012106;4;2</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;62011102,62011103,62011104,62011105,62011106;2;0.5</t>
+  </si>
+  <si>
+    <t>BuffIdAdd;61011102,61011103,61011104,61011105,61011106;69000046</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;61012102,61012103,61012104,61012105,61012106;2;0.5</t>
+  </si>
+  <si>
+    <t>BuffIdAdd;62012302,62012303,62012304,62012305,62012306;69000047</t>
+  </si>
+  <si>
+    <t>BuffIdAdd;51011302,51011303,51011304,51011305,51011306;69000076</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;62012202,62012203,62012204,62012205,62012206;4;2</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;61011302,61011303,61011304,61011305,61011306;4;2</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;61012302,61012303,61012304,61012305,61012306;2;0.5@SkillPropertyAdd;63012102,63012103,63012104,63012105,63012106;2;0.5</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;62011202,62011203,62011204,62011205,62011206;2;0.5</t>
+  </si>
+  <si>
+    <t>BuffIdAdd;61011302,61011303,61011304,61011305,61011306;69000072</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;61012302,61012303,61012304,61012305,61012306;2;0.5</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;62011302,62011303,62011304,62011305,62011306;4;2</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;62012102,62012103,62012104,62012105,62012106;2;0.25</t>
+  </si>
+  <si>
+    <t>Life Recovery</t>
+  </si>
+  <si>
+    <t>Power Strike</t>
+  </si>
+  <si>
+    <t>Damage Up</t>
+  </si>
+  <si>
+    <t>Skill Refresh</t>
+  </si>
+  <si>
+    <t>Freedom of Movement</t>
+  </si>
+  <si>
+    <t>Speed of Light</t>
+  </si>
+  <si>
+    <t>Critical Up</t>
+  </si>
+  <si>
+    <t>Evasion Mastery</t>
+  </si>
+  <si>
+    <t>Skill Mastery</t>
+  </si>
+  <si>
+    <t>Shield of Defense</t>
+  </si>
+  <si>
+    <t>Bash</t>
+  </si>
+  <si>
+    <t>Skill Upgrade</t>
+  </si>
+  <si>
+    <t>Attack Recovery</t>
+  </si>
+  <si>
+    <t>Counterattack</t>
+  </si>
+  <si>
+    <t>Class Mastery</t>
+  </si>
+  <si>
+    <t>Hope of Victory</t>
+  </si>
+  <si>
+    <t>Class Promotion</t>
+  </si>
+  <si>
+    <t>Eye for an Eye</t>
+  </si>
+  <si>
+    <t>Time Control</t>
+  </si>
+  <si>
+    <t>Damage Amplification</t>
+  </si>
+  <si>
+    <t>Blast</t>
+  </si>
+  <si>
+    <t>Slow Spell</t>
+  </si>
+  <si>
+    <t>Increased Damage</t>
+  </si>
+  <si>
+    <t>Valorous Guard</t>
+  </si>
+  <si>
+    <t>Courage of Will</t>
+  </si>
+  <si>
+    <t>Attack Boost</t>
+  </si>
+  <si>
+    <t>Hand of Tenacity</t>
+  </si>
+  <si>
+    <t>Movement Amplification</t>
+  </si>
+  <si>
+    <t>Critical Recovery</t>
+  </si>
+  <si>
+    <t>Mobile Light Orb</t>
+  </si>
+  <si>
+    <t>Perfect Counter</t>
+  </si>
+  <si>
+    <t>Ferocity</t>
+  </si>
+  <si>
+    <t>Explosive Seed</t>
+  </si>
+  <si>
+    <t>Beast Strength</t>
+  </si>
+  <si>
+    <t>Scatter Stun</t>
+  </si>
+  <si>
+    <t>Power of Bash</t>
+  </si>
+  <si>
+    <t>Icy Arrow</t>
+  </si>
+  <si>
+    <t>Power of Critical</t>
+  </si>
+  <si>
+    <t>Rage</t>
+  </si>
+  <si>
+    <t>Marksmanship Mastery</t>
+  </si>
+  <si>
+    <t>Shield of Life</t>
+  </si>
+  <si>
+    <t>Shot Penetration</t>
+  </si>
+  <si>
+    <t>Rage Recovery</t>
+  </si>
+  <si>
+    <t>Power of Attack</t>
+  </si>
+  <si>
+    <t>Explosive Shot</t>
+  </si>
+  <si>
+    <t>Multi-Shot</t>
+  </si>
+  <si>
+    <t>Hand of Restoration</t>
+  </si>
+  <si>
+    <t>Power of Valor</t>
+  </si>
+  <si>
+    <t>Speed Aura</t>
+  </si>
+  <si>
+    <t>Power of Magic</t>
+  </si>
+  <si>
+    <t>Power of Summoning</t>
+  </si>
+  <si>
+    <t>Power of Thunder</t>
+  </si>
+  <si>
+    <t>Defensive Guardian</t>
+  </si>
+  <si>
+    <t>Technique Ability</t>
+  </si>
+  <si>
+    <t>New passive skill: Life Recovery. When taking damage, there is a chance to restore 5% of maximum HP.</t>
+  </si>
+  <si>
+    <t>New Power Strike skill: Immediately deals 400% + 1000 damage to the target.</t>
+  </si>
+  <si>
+    <t>Earthshatter Slash and Rip Wave Slash damage +75%.</t>
+  </si>
+  <si>
+    <t>Each attack has a 10% chance to automatically trigger Earthshatter Slash without affecting the main skill's cooldown.</t>
+  </si>
+  <si>
+    <t>Leap Slash and Charge Slash damage to the target area +75%.</t>
+  </si>
+  <si>
+    <t>Speed of Light: Greatly increases movement speed and evasion by 10% for 6s.</t>
+  </si>
+  <si>
+    <t>Critical hit chance permanently +5%.</t>
+  </si>
+  <si>
+    <t>Evasion cap permanently +5%.</t>
+  </si>
+  <si>
+    <t>Elemental Flames: damage +75%; Light Strike: damage +120%; Energy Absorption: damage +75%.</t>
+  </si>
+  <si>
+    <t>When taking damage, chance to cast a shield that resists 30% damage, up to 20% of max HP, lasting 20s.</t>
+  </si>
+  <si>
+    <t>New Skill: Bash. Immediately deals 350% damage + 1500 fixed damage. If target HP &lt;50%, damage +50%.</t>
+  </si>
+  <si>
+    <t>Elemental Orb: skill damage +75%; Light Saber Attack: duration +10s; Burst State: damage +1000.</t>
+  </si>
+  <si>
+    <t>Basic attacks have a 20% chance to restore 5% of max HP.</t>
+  </si>
+  <si>
+    <t>When HP &lt;30%, take 50% less damage and attacks restore HP for 6s.</t>
+  </si>
+  <si>
+    <t>Elemental Gravity Wave: skill damage +75%; Light Energy: damage area increased, damage +30%; Energy Sphere: damage increased to 30%.</t>
+  </si>
+  <si>
+    <t>When HP &lt;10%, immediately restore 20% max HP and increase damage by 25% for 6s (120s cooldown).</t>
+  </si>
+  <si>
+    <t>New Skill: Explosive Bombardment. Deals 150% damage per second in self-radius for 6s.</t>
+  </si>
+  <si>
+    <t>Elemental Flames: skill damage +75%; Light Blast: skill damage +75%; Energy Land: skill damage effect increased to 20%.</t>
+  </si>
+  <si>
+    <t>Each evasion of an attack deals 100% attack damage to the target.</t>
+  </si>
+  <si>
+    <t>Elemental Gravity Wave cooldown -4s; Light Blast cooldown -5s; Energy Land attack effect +10%.</t>
+  </si>
+  <si>
+    <t>Skill cooldown -10%.</t>
+  </si>
+  <si>
+    <t>Magic Blitz and Tornado Strike damage +75%.</t>
+  </si>
+  <si>
+    <t>New Skill: Blast. Immediately deals 350% + 1000 damage to the target and area.</t>
+  </si>
+  <si>
+    <t>Basic attacks apply 30% slow for 3s.</t>
+  </si>
+  <si>
+    <t>Attacks have a 10% chance to cast Tornado Strike on the target.</t>
+  </si>
+  <si>
+    <t>New Skill: Freezing Strike. Charge for 1s, deals 350% damage to front rectangular area and immobilizes targets for 2s.</t>
+  </si>
+  <si>
+    <t>Guardian Strike and Ice Spike Strike damage +75%.</t>
+  </si>
+  <si>
+    <t>15% chance to trigger Guardian Strike when taking damage.</t>
+  </si>
+  <si>
+    <t>Shockwave: skill damage effect +75%; Elf Strike: skill damage effect +75%; Healing Realm: skill healing effect +25%.</t>
+  </si>
+  <si>
+    <t>Attacks have a 10% chance to grant 30% damage bonus for 10s.</t>
+  </si>
+  <si>
+    <t>Attack permanently +5%.</t>
+  </si>
+  <si>
+    <t>Magic Field: skill damage effect +75%; Flaming Burst: duration +4s; Healing Realm: recovery effect +3%.</t>
+  </si>
+  <si>
+    <t>When HP drops to 30%, take 75% less damage for 6s (once every 45s).</t>
+  </si>
+  <si>
+    <t>New Skill: Defensive Strike. Immediately deals 250% damage to surrounding enemies, silences and slows nearby units, and increases movement speed by 50% for 3s.</t>
+  </si>
+  <si>
+    <t>Shockwave: immobilizes damaged targets for 3s; Burn Blast: duration +4s; Mind Strike: damage +50%.</t>
+  </si>
+  <si>
+    <t>Movement speed permanently +10%.</t>
+  </si>
+  <si>
+    <t>Each critical hit restores 4% of max HP for the party.</t>
+  </si>
+  <si>
+    <t>Lava Ground: damage +25%; Flaming Burst cooldown -3s; Mind Strike cooldown -3s.</t>
+  </si>
+  <si>
+    <t>New Skill: Magic Light Orb. Releases a moving orb in front, dealing 350% + 2500 damage to touched units, reducing their movement speed by 50% for 3s.</t>
+  </si>
+  <si>
+    <t>Archmage Shadow cooldown -20s; Elf Blast cast time removed (instant cast); Mind Healing cooldown -5s.</t>
+  </si>
+  <si>
+    <t>15% chance to cast skills twice in a row.</t>
+  </si>
+  <si>
+    <t>20% chance to stun the attacker for 2s when hit (once every 20s).</t>
+  </si>
+  <si>
+    <t>Bow basic attacks have a 20% chance to restore 2% of max HP.</t>
+  </si>
+  <si>
+    <t>Instantly increases attack speed of party and summons by 100% for 6s.</t>
+  </si>
+  <si>
+    <t>Concussive Shot damage +75%.</t>
+  </si>
+  <si>
+    <t>Each attack has a chance to plant an Explosive Seed on the target, exploding after 1.5s for 300% + 1000 damage in area.</t>
+  </si>
+  <si>
+    <t>Summoned beasts' attack and HP +20%.</t>
+  </si>
+  <si>
+    <t>Scatter Shot skill damage +75%.</t>
+  </si>
+  <si>
+    <t>Bash chance permanently +5%.</t>
+  </si>
+  <si>
+    <t>Each attack has a chance to reduce target's movement speed by 30% for 5s.</t>
+  </si>
+  <si>
+    <t>Ice Trap: cooldown -2s; Scorching Arrow: damage +75%; Beast Power: burst duration +3s.</t>
+  </si>
+  <si>
+    <t>Critical basic attacks increase self-damage by 20% for 6s.</t>
+  </si>
+  <si>
+    <t>Each attack has a chance to restore 10 rage.</t>
+  </si>
+  <si>
+    <t>Explosion Trap: deals damage and stuns target for 1s; Burning Cyclone: skill damage +75%; Hunt Mark: damage +10%.</t>
+  </si>
+  <si>
+    <t>Bow basic attacks damage +20%.</t>
+  </si>
+  <si>
+    <t>When taking damage, chance to cast a shield that resists 50% damage, up to 30% of max HP, lasting 20s.</t>
+  </si>
+  <si>
+    <t>Ice Land: damage +25%; Charged Strike: damage +75%; Beast Flames: damage increased to 75%.</t>
+  </si>
+  <si>
+    <t>Damage bonus +5%.</t>
+  </si>
+  <si>
+    <t>Rage cap increased to 150, rage recovery +3 per second.</t>
+  </si>
+  <si>
+    <t>Fire Tongue Guard: cooldown -5s; Wind Arrow Domain: reduces target's movement speed by 30%; Beast Call: all summoned monsters' attributes +25%.</t>
+  </si>
+  <si>
+    <t>Each attack has a chance to reduce target's defense to 0 for 5s.</t>
+  </si>
+  <si>
+    <t>Fires a scatter shot that deals 100% area damage to nearby units when hitting the target.</t>
+  </si>
+  <si>
+    <t>Attacks target and nearby units simultaneously.</t>
+  </si>
+  <si>
+    <t>New Magic Strike Skill: Immediately deals 400% damage to the target.</t>
+  </si>
+  <si>
+    <t>Magic Baptism and Magic Bombardment damage +75%.</t>
+  </si>
+  <si>
+    <t>Each skill use has a chance to restore HP.</t>
+  </si>
+  <si>
+    <t>Basic attacks have a chance to apply 1 stack of Magic Mark.</t>
+  </si>
+  <si>
+    <t>New Defensive Strike Skill: Immediately restores 10% HP. When taking damage, chance to deal 350% attack damage + 2000 to nearby monsters and stun them for 2s.</t>
+  </si>
+  <si>
+    <t>Self basic attack damage +25%.</t>
+  </si>
+  <si>
+    <t>Each basic attack increases attack speed and movement speed by 5%, stacking up to 5 layers.</t>
+  </si>
+  <si>
+    <t>Magic Flash Strike cooldown -1s; Burning Magic Orb damage +75%; Contract Land damage +25%.</t>
+  </si>
+  <si>
+    <t>Damage dealt +5%.</t>
+  </si>
+  <si>
+    <t>Each stack of Magic Mark increases damage by 10%.</t>
+  </si>
+  <si>
+    <t>Shadow Throw cooldown -1s; Burning Magic Orb cooldown -1s; Thunder Power cooldown -3s.</t>
+  </si>
+  <si>
+    <t>Rapid Bombardment skill damage +75%; Wind Flames cooldown -2s; Dark Magic Explosion damage +75%.</t>
+  </si>
+  <si>
+    <t>Active Skill: Thunder Power. Immediately deals 350% lightning damage to 6 areas around self and stuns for 1s.</t>
+  </si>
+  <si>
+    <t>Movement speed +15%.</t>
+  </si>
+  <si>
+    <t>Critical hits grant an additional 15% attack for 10s.</t>
+  </si>
+  <si>
+    <t>Fire Cyclone skill damage +75%; Wind Goddess basic attack damage +50%; Demon Contract cooldown -5s.</t>
+  </si>
+  <si>
+    <t>Skill cooldown -5%.</t>
+  </si>
+  <si>
+    <t>Each skill use has a chance to summon an additional ritual monster to assist.</t>
+  </si>
+  <si>
+    <t>New Defensive Guardian Skill: When taking damage, chance to immediately deal 350% attack damage + 2000 to nearby monsters and knock them back.</t>
+  </si>
+  <si>
+    <t>10% chance to deal double skill damage when casting.</t>
+  </si>
+  <si>
+    <t>新增防御之击技能,立即恢复自身10%血量,受到伤害有一定概率立即对自身范围内的怪物造成350%攻击伤害+2000,并对造成2秒眩晕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通攻击有概率为目标附加1层魔法印记</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>魔法洗礼和魔法轰炸伤害提升75%</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;64011202,64011203,64011204,64011205,64011206;2;0.75@SkillPropertyAdd;64012202,64012203,64012204,64012205,64012206;2;0.75</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到伤害有15%概率触发守护之击</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增技能:轰击 立即对目标及其范围造成350%+1000点伤害</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放技能有10%的概率造成技能伤害的双倍伤害</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>破界巨刃和裂空之击伤害提升75%</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;65011102,65011103,65011104,65011105,65011106;2;0.75@SkillPropertyAdd;65012102,65012103,65012104,65012105,65012106;2;0.75</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害之力</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次使用技能有一定概率恢复自身的一定生命值</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击有10%概率使自身获得30%伤害加成,持续6秒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000501</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000502</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>恢复之手</t>
-  </si>
-  <si>
-    <t>每次使用技能有一定概率恢复自身的一定生命值</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;62000062</t>
-  </si>
-  <si>
-    <t>魔法印记</t>
-  </si>
-  <si>
-    <t>Magic Mark</t>
-  </si>
-  <si>
-    <t>普通攻击有概率为目标附加1层魔法印记</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;62000063</t>
-  </si>
-  <si>
-    <t>新增防御之击技能,立即恢复自身10%血量,受到伤害有一定概率立即对自身范围内的怪物造成350%攻击伤害+2000,并对造成2秒眩晕</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;62000065</t>
-  </si>
-  <si>
-    <t>勇猛之力</t>
-  </si>
-  <si>
-    <t>自身普攻伤害提升25%</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;60000601,60000602,60000701,60000702;2;0.25</t>
-  </si>
-  <si>
-    <t>疾风光环</t>
-  </si>
-  <si>
-    <t>每次普攻提升5%攻击速度和移动速度，最多可叠5层</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;62000066</t>
-  </si>
-  <si>
-    <t>魔闪之击冷却时间降低1秒，燃烧魔球伤害提升75%，契约之地伤害提升25%</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;64013102,64013103,64013104,64013105,64013106;4;1@SkillPropertyAdd;64014202,64014203,64014204,64014205,64014206;2;0.75@SkillPropertyAdd;64015102,64015103,64015104,64015105,64015106;2;0.25</t>
-  </si>
-  <si>
-    <t>造成伤害提升5%</t>
-  </si>
-  <si>
-    <t>魔法之力</t>
-  </si>
-  <si>
-    <t>每层魔法印记造成的伤害提升10%</t>
-  </si>
-  <si>
-    <t>BuffPropertyAdd;95100001;1;0.1</t>
-  </si>
-  <si>
-    <t>暗影投掷冷却时间降低1秒;燃烧魔球冷却时间降低1秒;雷鸣之力冷却时间降低3秒</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;64013202,64013203,64013204,64013205,64013206;4;1@SkillPropertyAdd;64014202,64014203,64014204,64014205,64014206;4;1@SkillPropertyAdd;64015202,64015203,64015204,64015205,64015206;4;1</t>
-  </si>
-  <si>
-    <t>召唤之力</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;62000068</t>
-  </si>
-  <si>
-    <t>极速轰炸技能伤害提升75%;疾风烈焰技能冷却时间降低2秒;黑暗魔爆伤害提升75%</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;64013302,64013303,64013304,64013305,64013306;2;0.75@SkillPropertyAdd;64014302,64014303,64014304,64014305,64014106;4;1@SkillPropertyAdd;64015302,64015303,64015304,64015305,64015306;2;0.75</t>
-  </si>
-  <si>
-    <t>雷鸣之力</t>
-  </si>
-  <si>
-    <t>主动技能:雷鸣之力,立即对自身周围范围的6个区域造成350%闪电伤害，并造成1秒眩晕</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;62000067</t>
-  </si>
-  <si>
-    <t>迅捷移动</t>
-  </si>
-  <si>
-    <t>Swift Movement</t>
-  </si>
-  <si>
-    <t>移动速度提升15%</t>
-  </si>
-  <si>
-    <t>RolePropertyAdd;100902;0.15</t>
-  </si>
-  <si>
-    <t>造成暴击后会额外提升自身15%攻击,持续10秒</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;62000069</t>
-  </si>
-  <si>
-    <t>火焰旋风技能伤害提升75%;风神之女普攻伤害提升50%;恶魔契约冷却时间降低5秒</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;64013402,64013403,64013404,64013405,64013406;2;0.75@SkillPropertyAdd;64014451,64014452,64014453,64014454,64014455;2;0.5@SkillPropertyAdd;64015402,64015403,64015404,64015405,64015406;4;5</t>
-  </si>
-  <si>
-    <t>技能冷却时间降低5%</t>
-  </si>
-  <si>
-    <t>RolePropertyAdd;203603;0.05</t>
-  </si>
-  <si>
-    <t>召唤仪式</t>
-  </si>
-  <si>
-    <t>Summoning Ritual</t>
-  </si>
-  <si>
-    <t>每次使用技能会有概率额外召唤一个仪式怪物协助自身战斗</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;62000070</t>
-  </si>
-  <si>
-    <t>防御守护</t>
-  </si>
-  <si>
-    <t>新增防御守护技能,受到伤害有一定概率立即对自身范围内的怪物造成350%攻击伤害+2000,并击退周围附近敌方目标</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;62000064</t>
-  </si>
-  <si>
-    <t>技之能力</t>
-  </si>
-  <si>
-    <t>释放技能有10%的概率造成技能伤害的双倍伤害</t>
-  </si>
-  <si>
-    <t>RolePropertyAdd;204103;0.1</t>
-  </si>
-  <si>
-    <t>生命提升</t>
-  </si>
-  <si>
-    <t>Health increase</t>
-  </si>
-  <si>
-    <t>攻击+10;攻击+20;攻击+30</t>
-  </si>
-  <si>
-    <t>Attack +10; Attack +20; Attack +30</t>
-  </si>
-  <si>
-    <t>RolePropertyAdd;100203;50</t>
-  </si>
-  <si>
-    <t>光环技能范围</t>
-  </si>
-  <si>
-    <t>Auras Skill Range</t>
-  </si>
-  <si>
-    <t>旋风斩的技能伤害范围+1;旋风斩的技能伤害范围+2</t>
-  </si>
-  <si>
-    <t>The skill damage range of Whirlwind Slash increases by 1; The skill damage range of Whirlwind Slash increases by 2</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;80000013;1;10</t>
-  </si>
-  <si>
-    <t>元素法球附带给自身加血对敌人定身效果</t>
-  </si>
-  <si>
-    <t>Elemental Ball attaches health to itself and stuns enemies</t>
-  </si>
-  <si>
-    <t>前冲距离延长3码距离</t>
-  </si>
-  <si>
-    <t>Forward movement distance extended by 3 yards</t>
-  </si>
-  <si>
-    <t>BuffIdAdd;61021201;90001021@BuffInitIdAdd;61021201;90000005</t>
-  </si>
-  <si>
-    <t>技能元素爆冰更换为元素法球</t>
-  </si>
-  <si>
-    <t>Change Skill Elemental Blast Ice to Elemental Ball</t>
-  </si>
-  <si>
-    <t>使用审判时可以将目标减速30%,持续3秒;使用审判时可以将目标减速30%,持续5秒</t>
-  </si>
-  <si>
-    <t>When using Judgment, you can slow the target by 30% for 3 seconds; when using Judgment, you can slow the target by 30% for 5 seconds.</t>
-  </si>
-  <si>
-    <t>ReplaceSkillId;61021301;61021201</t>
-  </si>
-  <si>
-    <t>新增技能光环</t>
-  </si>
-  <si>
-    <t>New skill aura</t>
-  </si>
-  <si>
-    <t>击杀怪物获得金币+1%;击杀怪物获得金币+2%;击杀怪物获得金币+3%;击杀怪物获得金币+4%;击杀怪物获得金币+5%</t>
-  </si>
-  <si>
-    <t>Kill monsters and gain 1% of gold; Kill monsters and gain 2% of gold; Kill monsters and gain 3% of gold; Kill monsters and gain 4% of gold; Kill monsters and gain 5% of gold</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;80000013</t>
-  </si>
-  <si>
-    <t>延长速度降低的时间</t>
-  </si>
-  <si>
-    <t>Extended speed reduction duration</t>
-  </si>
-  <si>
-    <t>基础移动速度+4%;基础移动速度+8%;基础移动速度+12%;基础移动速度+16%;基础移动速度+20%</t>
-  </si>
-  <si>
-    <t>Base movement speed + 4%; Base movement speed + 8%; Base movement speed + 12%; Base movement speed + 16%; Base movement speed + 20%</t>
-  </si>
-  <si>
-    <t>BuffPropertyAdd;90001032;2;10</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;61012102,61012103,61012104,61012105,61012106;4;2</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;62011102,62011103,62011104,62011105,62011106;2;0.5</t>
-  </si>
-  <si>
-    <t>BuffIdAdd;61011102,61011103,61011104,61011105,61011106;69000046</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;61012102,61012103,61012104,61012105,61012106;2;0.5</t>
-  </si>
-  <si>
-    <t>BuffIdAdd;62012302,62012303,62012304,62012305,62012306;69000047</t>
-  </si>
-  <si>
-    <t>BuffIdAdd;51011302,51011303,51011304,51011305,51011306;69000076</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;62012202,62012203,62012204,62012205,62012206;4;2</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;61011302,61011303,61011304,61011305,61011306;4;2</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;61012302,61012303,61012304,61012305,61012306;2;0.5@SkillPropertyAdd;63012102,63012103,63012104,63012105,63012106;2;0.5</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;62011202,62011203,62011204,62011205,62011206;2;0.5</t>
-  </si>
-  <si>
-    <t>BuffIdAdd;61011302,61011303,61011304,61011305,61011306;69000072</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;61012302,61012303,61012304,61012305,61012306;2;0.5</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;62011302,62011303,62011304,62011305,62011306;4;2</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;62012102,62012103,62012104,62012105,62012106;2;0.25</t>
-  </si>
-  <si>
-    <t>Life Recovery</t>
-  </si>
-  <si>
-    <t>Power Strike</t>
-  </si>
-  <si>
-    <t>Damage Up</t>
-  </si>
-  <si>
-    <t>Skill Refresh</t>
-  </si>
-  <si>
-    <t>Freedom of Movement</t>
-  </si>
-  <si>
-    <t>Speed of Light</t>
-  </si>
-  <si>
-    <t>Critical Up</t>
-  </si>
-  <si>
-    <t>Evasion Mastery</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Skill Mastery</t>
-  </si>
-  <si>
-    <t>Shield of Defense</t>
-  </si>
-  <si>
-    <t>Bash</t>
-  </si>
-  <si>
-    <t>Skill Upgrade</t>
-  </si>
-  <si>
-    <t>Attack Recovery</t>
-  </si>
-  <si>
-    <t>Counterattack</t>
-  </si>
-  <si>
-    <t>Class Mastery</t>
-  </si>
-  <si>
-    <t>Hope of Victory</t>
-  </si>
-  <si>
-    <t>Class Promotion</t>
-  </si>
-  <si>
-    <t>Eye for an Eye</t>
-  </si>
-  <si>
-    <t>Time Control</t>
-  </si>
-  <si>
-    <t>Damage Amplification</t>
-  </si>
-  <si>
-    <t>Blast</t>
-  </si>
-  <si>
-    <t>Slow Spell</t>
-  </si>
-  <si>
-    <t>Increased Damage</t>
-  </si>
-  <si>
-    <t>Valorous Guard</t>
-  </si>
-  <si>
-    <t>Courage of Will</t>
-  </si>
-  <si>
-    <t>Attack Boost</t>
-  </si>
-  <si>
-    <t>Hand of Tenacity</t>
-  </si>
-  <si>
-    <t>Movement Amplification</t>
-  </si>
-  <si>
-    <t>Critical Recovery</t>
-  </si>
-  <si>
-    <t>Mobile Light Orb</t>
-  </si>
-  <si>
-    <t>Perfect Counter</t>
-  </si>
-  <si>
-    <t>Ferocity</t>
-  </si>
-  <si>
-    <t>Explosive Seed</t>
-  </si>
-  <si>
-    <t>Beast Strength</t>
-  </si>
-  <si>
-    <t>Scatter Stun</t>
-  </si>
-  <si>
-    <t>Power of Bash</t>
-  </si>
-  <si>
-    <t>Icy Arrow</t>
-  </si>
-  <si>
-    <t>Power of Critical</t>
-  </si>
-  <si>
-    <t>Rage</t>
-  </si>
-  <si>
-    <t>Marksmanship Mastery</t>
-  </si>
-  <si>
-    <t>Shield of Life</t>
-  </si>
-  <si>
-    <t>Shot Penetration</t>
-  </si>
-  <si>
-    <t>Rage Recovery</t>
-  </si>
-  <si>
-    <t>Power of Attack</t>
-  </si>
-  <si>
-    <t>Explosive Shot</t>
-  </si>
-  <si>
-    <t>Multi-Shot</t>
-  </si>
-  <si>
-    <t>Hand of Restoration</t>
-  </si>
-  <si>
-    <t>Power of Valor</t>
-  </si>
-  <si>
-    <t>Speed Aura</t>
-  </si>
-  <si>
-    <t>Power of Magic</t>
-  </si>
-  <si>
-    <t>Power of Summoning</t>
-  </si>
-  <si>
-    <t>Power of Thunder</t>
-  </si>
-  <si>
-    <t>Defensive Guardian</t>
-  </si>
-  <si>
-    <t>Technique Ability</t>
-  </si>
-  <si>
-    <t>New passive skill: Life Recovery. When taking damage, there is a chance to restore 5% of maximum HP.</t>
-  </si>
-  <si>
-    <t>New Power Strike skill: Immediately deals 400% + 1000 damage to the target.</t>
-  </si>
-  <si>
-    <t>Earthshatter Slash and Rip Wave Slash damage +75%.</t>
-  </si>
-  <si>
-    <t>Each attack has a 10% chance to automatically trigger Earthshatter Slash without affecting the main skill's cooldown.</t>
-  </si>
-  <si>
-    <t>Leap Slash and Charge Slash damage to the target area +75%.</t>
-  </si>
-  <si>
-    <t>Speed of Light: Greatly increases movement speed and evasion by 10% for 6s.</t>
-  </si>
-  <si>
-    <t>Critical hit chance permanently +5%.</t>
-  </si>
-  <si>
-    <t>Evasion cap permanently +5%.</t>
-  </si>
-  <si>
-    <t>Elemental Flames: damage +75%; Light Strike: damage +120%; Energy Absorption: damage +75%.</t>
-  </si>
-  <si>
-    <t>When taking damage, chance to cast a shield that resists 30% damage, up to 20% of max HP, lasting 20s.</t>
-  </si>
-  <si>
-    <t>New Skill: Bash. Immediately deals 350% damage + 1500 fixed damage. If target HP &lt;50%, damage +50%.</t>
-  </si>
-  <si>
-    <t>Elemental Orb: skill damage +75%; Light Saber Attack: duration +10s; Burst State: damage +1000.</t>
-  </si>
-  <si>
-    <t>Basic attacks have a 20% chance to restore 5% of max HP.</t>
-  </si>
-  <si>
-    <t>When HP &lt;30%, take 50% less damage and attacks restore HP for 6s.</t>
-  </si>
-  <si>
-    <t>Elemental Gravity Wave: skill damage +75%; Light Energy: damage area increased, damage +30%; Energy Sphere: damage increased to 30%.</t>
-  </si>
-  <si>
-    <t>When HP &lt;10%, immediately restore 20% max HP and increase damage by 25% for 6s (120s cooldown).</t>
-  </si>
-  <si>
-    <t>New Skill: Explosive Bombardment. Deals 150% damage per second in self-radius for 6s.</t>
-  </si>
-  <si>
-    <t>Elemental Flames: skill damage +75%; Light Blast: skill damage +75%; Energy Land: skill damage effect increased to 20%.</t>
-  </si>
-  <si>
-    <t>Each evasion of an attack deals 100% attack damage to the target.</t>
-  </si>
-  <si>
-    <t>Elemental Gravity Wave cooldown -4s; Light Blast cooldown -5s; Energy Land attack effect +10%.</t>
-  </si>
-  <si>
-    <t>Skill cooldown -10%.</t>
-  </si>
-  <si>
-    <t>Magic Blitz and Tornado Strike damage +75%.</t>
-  </si>
-  <si>
-    <t>New Skill: Blast. Immediately deals 350% + 1000 damage to the target and area.</t>
-  </si>
-  <si>
-    <t>Basic attacks apply 30% slow for 3s.</t>
-  </si>
-  <si>
-    <t>Attacks have a 10% chance to cast Tornado Strike on the target.</t>
-  </si>
-  <si>
-    <t>New Skill: Freezing Strike. Charge for 1s, deals 350% damage to front rectangular area and immobilizes targets for 2s.</t>
-  </si>
-  <si>
-    <t>Guardian Strike and Ice Spike Strike damage +75%.</t>
-  </si>
-  <si>
-    <t>15% chance to trigger Guardian Strike when taking damage.</t>
-  </si>
-  <si>
-    <t>Shockwave: skill damage effect +75%; Elf Strike: skill damage effect +75%; Healing Realm: skill healing effect +25%.</t>
-  </si>
-  <si>
-    <t>Attacks have a 10% chance to grant 30% damage bonus for 10s.</t>
-  </si>
-  <si>
-    <t>Attack permanently +5%.</t>
-  </si>
-  <si>
-    <t>Magic Field: skill damage effect +75%; Flaming Burst: duration +4s; Healing Realm: recovery effect +3%.</t>
-  </si>
-  <si>
-    <t>When HP drops to 30%, take 75% less damage for 6s (once every 45s).</t>
-  </si>
-  <si>
-    <t>New Skill: Defensive Strike. Immediately deals 250% damage to surrounding enemies, silences and slows nearby units, and increases movement speed by 50% for 3s.</t>
-  </si>
-  <si>
-    <t>Shockwave: immobilizes damaged targets for 3s; Burn Blast: duration +4s; Mind Strike: damage +50%.</t>
-  </si>
-  <si>
-    <t>Movement speed permanently +10%.</t>
-  </si>
-  <si>
-    <t>Each critical hit restores 4% of max HP for the party.</t>
-  </si>
-  <si>
-    <t>Lava Ground: damage +25%; Flaming Burst cooldown -3s; Mind Strike cooldown -3s.</t>
-  </si>
-  <si>
-    <t>New Skill: Magic Light Orb. Releases a moving orb in front, dealing 350% + 2500 damage to touched units, reducing their movement speed by 50% for 3s.</t>
-  </si>
-  <si>
-    <t>Archmage Shadow cooldown -20s; Elf Blast cast time removed (instant cast); Mind Healing cooldown -5s.</t>
-  </si>
-  <si>
-    <t>15% chance to cast skills twice in a row.</t>
-  </si>
-  <si>
-    <t>20% chance to stun the attacker for 2s when hit (once every 20s).</t>
-  </si>
-  <si>
-    <t>Bow basic attacks have a 20% chance to restore 2% of max HP.</t>
-  </si>
-  <si>
-    <t>Instantly increases attack speed of party and summons by 100% for 6s.</t>
-  </si>
-  <si>
-    <t>Concussive Shot damage +75%.</t>
-  </si>
-  <si>
-    <t>Each attack has a chance to plant an Explosive Seed on the target, exploding after 1.5s for 300% + 1000 damage in area.</t>
-  </si>
-  <si>
-    <t>Summoned beasts' attack and HP +20%.</t>
-  </si>
-  <si>
-    <t>Scatter Shot skill damage +75%.</t>
-  </si>
-  <si>
-    <t>Bash chance permanently +5%.</t>
-  </si>
-  <si>
-    <t>Each attack has a chance to reduce target's movement speed by 30% for 5s.</t>
-  </si>
-  <si>
-    <t>Ice Trap: cooldown -2s; Scorching Arrow: damage +75%; Beast Power: burst duration +3s.</t>
-  </si>
-  <si>
-    <t>Critical basic attacks increase self-damage by 20% for 6s.</t>
-  </si>
-  <si>
-    <t>Each attack has a chance to restore 10 rage.</t>
-  </si>
-  <si>
-    <t>Explosion Trap: deals damage and stuns target for 1s; Burning Cyclone: skill damage +75%; Hunt Mark: damage +10%.</t>
-  </si>
-  <si>
-    <t>Bow basic attacks damage +20%.</t>
-  </si>
-  <si>
-    <t>When taking damage, chance to cast a shield that resists 50% damage, up to 30% of max HP, lasting 20s.</t>
-  </si>
-  <si>
-    <t>Ice Land: damage +25%; Charged Strike: damage +75%; Beast Flames: damage increased to 75%.</t>
-  </si>
-  <si>
-    <t>Damage bonus +5%.</t>
-  </si>
-  <si>
-    <t>Rage cap increased to 150, rage recovery +3 per second.</t>
-  </si>
-  <si>
-    <t>Fire Tongue Guard: cooldown -5s; Wind Arrow Domain: reduces target's movement speed by 30%; Beast Call: all summoned monsters' attributes +25%.</t>
-  </si>
-  <si>
-    <t>Each attack has a chance to reduce target's defense to 0 for 5s.</t>
-  </si>
-  <si>
-    <t>Fires a scatter shot that deals 100% area damage to nearby units when hitting the target.</t>
-  </si>
-  <si>
-    <t>Attacks target and nearby units simultaneously.</t>
-  </si>
-  <si>
-    <t>New Magic Strike Skill: Immediately deals 400% damage to the target.</t>
-  </si>
-  <si>
-    <t>Magic Baptism and Magic Bombardment damage +75%.</t>
-  </si>
-  <si>
-    <t>Each skill use has a chance to restore HP.</t>
-  </si>
-  <si>
-    <t>Basic attacks have a chance to apply 1 stack of Magic Mark.</t>
-  </si>
-  <si>
-    <t>New Defensive Strike Skill: Immediately restores 10% HP. When taking damage, chance to deal 350% attack damage + 2000 to nearby monsters and stun them for 2s.</t>
-  </si>
-  <si>
-    <t>Self basic attack damage +25%.</t>
-  </si>
-  <si>
-    <t>Each basic attack increases attack speed and movement speed by 5%, stacking up to 5 layers.</t>
-  </si>
-  <si>
-    <t>Magic Flash Strike cooldown -1s; Burning Magic Orb damage +75%; Contract Land damage +25%.</t>
-  </si>
-  <si>
-    <t>Damage dealt +5%.</t>
-  </si>
-  <si>
-    <t>Each stack of Magic Mark increases damage by 10%.</t>
-  </si>
-  <si>
-    <t>Shadow Throw cooldown -1s; Burning Magic Orb cooldown -1s; Thunder Power cooldown -3s.</t>
-  </si>
-  <si>
-    <t>Rapid Bombardment skill damage +75%; Wind Flames cooldown -2s; Dark Magic Explosion damage +75%.</t>
-  </si>
-  <si>
-    <t>Active Skill: Thunder Power. Immediately deals 350% lightning damage to 6 areas around self and stuns for 1s.</t>
-  </si>
-  <si>
-    <t>Movement speed +15%.</t>
-  </si>
-  <si>
-    <t>Critical hits grant an additional 15% attack for 10s.</t>
-  </si>
-  <si>
-    <t>Fire Cyclone skill damage +75%; Wind Goddess basic attack damage +50%; Demon Contract cooldown -5s.</t>
-  </si>
-  <si>
-    <t>Skill cooldown -5%.</t>
-  </si>
-  <si>
-    <t>Each skill use has a chance to summon an additional ritual monster to assist.</t>
-  </si>
-  <si>
-    <t>New Defensive Guardian Skill: When taking damage, chance to immediately deal 350% attack damage + 2000 to nearby monsters and knock them back.</t>
-  </si>
-  <si>
-    <t>10% chance to deal double skill damage when casting.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放咆哮之击可以使移动速度降低50%，并使其命中属性降低30%,持续3秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffIdAdd;65011202,65011203,65011204,65011205,65011206;92000046,92000047</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到怪物伤害降低20%，且受到玩家的普攻伤害降低20%</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>跃空击技能冷却时间降低2秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;65011302,65011303,65011304,65011305,65011306;4;2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;65021102,65021103,65021104,65021105,65021106;2;0.75@SkillPropertyAdd;65022102,65022103,65022104,65022105,65022106;4;3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨力震击伤害提升75%；隐匿一击冷却时间降低3秒；召唤的镜像攻击和生命提升20%</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到所有伤害降低5%</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RolePropertyAdd;201003;0.05</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RolePropertyAdd;205703;0.2@RolePropertyAdd;203201;0.2@RolePropertyAdd;203303;0.2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000013</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次普通攻击有一定概率对前方区域触发巨力震击技能</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功闪避会给自身增加一个伤害印记，使己方伤害提升5%，最多叠加5层，每个闪避印记持续6秒，每次附加新的闪避印记会刷新伤害印记的冷却时间。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000503</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避印记</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;65021302,65021303,65021304,65021305,65021306;4;2@SkillPropertyAdd;65022302,65022303,65022304,65022305,65022306;2;0.75@SkillPropertyAdd;64015102,64015103,64015104,64015105,64015106;2;0.25</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨剑之力冷却时间降低3秒；破风之击伤害提升75%；幻影冲击如果目标血量低于50%，则提升50%伤害。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>守护冲击伤害提升25%；精灵共鸣可以额外召唤出2个精灵协助战斗；战灵怒吼会对目标额外造成1秒眩晕。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;65021202,65021203,65021204,65021205,65021206;2;0.75@SkillPropertyAdd;65022302,65022303,65022304,65022305,65022306;2;0.75@BuffIdAdd;65023202,65023203,65023204,65023205,65023206;92000049</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000504</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增技能:爆裂击,立即对前方矩形范围的目标造成350%伤害,并使目标置空秒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RolePropertyAdd;202702;0.2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通攻击造成的伤害提升20%</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>守护天使伤害提升75%；释放唤灵之契有概率不进入冷却时间；逆转之力冷却时间降低3秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;65021402,65021403,65021404,65021405,65021406;2;0.75@@SkillPropertyAdd;65023402,65023403,65023404,65023405,65023406;4;3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值低于50%时，自身伤害提升30%,持续10秒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000505</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>逆境反击</t>
+  </si>
+  <si>
+    <t>普通攻击和释放技能有一定的概率对目标身上附加闪避标记，每个闪避标记可以降低目标5%的闪避,最多叠加5层。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000506</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通攻击和释放技能有概率为目标附加1层黑暗印记，当黑暗印记达到5层时，造成350%伤害和1秒眩晕。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000507</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>当生命值降低至30%后,受到闪避提升50%,持续3秒，30秒内只能触发一次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000509</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能专精</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵抗专精</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -12535,14 +12720,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:Q119"/>
+  <dimension ref="C1:Q140"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="8.5" customWidth="1"/>
     <col min="4" max="5" width="39" customWidth="1"/>
     <col min="6" max="6" width="11.375" customWidth="1"/>
     <col min="7" max="7" width="12.75" customWidth="1"/>
-    <col min="8" max="9" width="108.25" customWidth="1"/>
+    <col min="8" max="8" width="108.25" customWidth="1"/>
+    <col min="9" max="9" width="108.25" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="43.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12641,7 +12827,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="F6" s="11">
         <v>10001</v>
@@ -12653,7 +12839,7 @@
         <v>16</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="J6" s="24" t="s">
         <v>17</v>
@@ -12667,7 +12853,7 @@
         <v>18</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="F7" s="11">
         <v>10002</v>
@@ -12679,7 +12865,7 @@
         <v>19</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="J7" s="24" t="s">
         <v>20</v>
@@ -12693,7 +12879,7 @@
         <v>21</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="F8" s="11">
         <v>10003</v>
@@ -12705,7 +12891,7 @@
         <v>22</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="J8" s="25" t="s">
         <v>23</v>
@@ -12719,7 +12905,7 @@
         <v>24</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="F9" s="11">
         <v>10011</v>
@@ -12731,7 +12917,7 @@
         <v>25</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="J9" s="24" t="s">
         <v>26</v>
@@ -12745,7 +12931,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="F10" s="11">
         <v>10012</v>
@@ -12757,7 +12943,7 @@
         <v>28</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="J10" s="25" t="s">
         <v>29</v>
@@ -12771,7 +12957,7 @@
         <v>30</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="F11" s="11">
         <v>10013</v>
@@ -12783,7 +12969,7 @@
         <v>31</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="J11" s="24" t="s">
         <v>32</v>
@@ -12797,7 +12983,7 @@
         <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="F12" s="11">
         <v>10021</v>
@@ -12809,7 +12995,7 @@
         <v>34</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="J12" s="25" t="s">
         <v>35</v>
@@ -12823,7 +13009,7 @@
         <v>36</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="F13" s="11">
         <v>10022</v>
@@ -12835,7 +13021,7 @@
         <v>37</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="J13" s="25" t="s">
         <v>38</v>
@@ -12849,7 +13035,7 @@
         <v>39</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="F14" s="11">
         <v>10023</v>
@@ -12861,7 +13047,7 @@
         <v>40</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="J14" s="25" t="s">
         <v>41</v>
@@ -12875,7 +13061,7 @@
         <v>42</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F15" s="11">
         <v>10031</v>
@@ -12887,7 +13073,7 @@
         <v>43</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="J15" s="24" t="s">
         <v>44</v>
@@ -12901,7 +13087,7 @@
         <v>45</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F16" s="11">
         <v>10032</v>
@@ -12913,7 +13099,7 @@
         <v>46</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="J16" s="24" t="s">
         <v>47</v>
@@ -12927,7 +13113,7 @@
         <v>48</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F17" s="11">
         <v>10033</v>
@@ -12939,7 +13125,7 @@
         <v>49</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="J17" s="25" t="s">
         <v>50</v>
@@ -12953,7 +13139,7 @@
         <v>51</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F18" s="11">
         <v>10041</v>
@@ -12965,7 +13151,7 @@
         <v>52</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="J18" s="24" t="s">
         <v>53</v>
@@ -12979,7 +13165,7 @@
         <v>54</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="F19" s="11">
         <v>10042</v>
@@ -12991,7 +13177,7 @@
         <v>55</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="J19" s="24" t="s">
         <v>56</v>
@@ -13005,7 +13191,7 @@
         <v>57</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="F20" s="11">
         <v>10043</v>
@@ -13017,7 +13203,7 @@
         <v>58</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="J20" s="25" t="s">
         <v>59</v>
@@ -13031,7 +13217,7 @@
         <v>60</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="F21" s="11">
         <v>10051</v>
@@ -13043,7 +13229,7 @@
         <v>61</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="J21" s="24" t="s">
         <v>62</v>
@@ -13069,7 +13255,7 @@
         <v>65</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="J22" s="24" t="s">
         <v>66</v>
@@ -13083,7 +13269,7 @@
         <v>67</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="F23" s="11">
         <v>10053</v>
@@ -13095,7 +13281,7 @@
         <v>68</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="J23" s="25" t="s">
         <v>69</v>
@@ -13109,7 +13295,7 @@
         <v>70</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F24" s="14">
         <v>10061</v>
@@ -13121,7 +13307,7 @@
         <v>71</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="J24" s="26" t="s">
         <v>72</v>
@@ -13135,7 +13321,7 @@
         <v>57</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="F25" s="14">
         <v>10062</v>
@@ -13147,7 +13333,7 @@
         <v>73</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="J25" s="26" t="s">
         <v>74</v>
@@ -13161,7 +13347,7 @@
         <v>75</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F26" s="14">
         <v>10063</v>
@@ -13173,7 +13359,7 @@
         <v>76</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="J26" s="27" t="s">
         <v>77</v>
@@ -13187,7 +13373,7 @@
         <v>78</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F27" s="11">
         <v>20001</v>
@@ -13199,7 +13385,7 @@
         <v>79</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="J27" s="25" t="s">
         <v>80</v>
@@ -13213,7 +13399,7 @@
         <v>81</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F28" s="11">
         <v>20002</v>
@@ -13222,13 +13408,13 @@
         <v>15</v>
       </c>
       <c r="H28" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="J28" s="24" t="s">
         <v>82</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="J28" s="24" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="29" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13236,10 +13422,10 @@
         <v>20003</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F29" s="11">
         <v>20003</v>
@@ -13248,13 +13434,13 @@
         <v>15</v>
       </c>
       <c r="H29" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="J29" s="25" t="s">
         <v>85</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="J29" s="25" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="30" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13262,10 +13448,10 @@
         <v>20011</v>
       </c>
       <c r="D30" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>87</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>88</v>
       </c>
       <c r="F30" s="11">
         <v>20011</v>
@@ -13274,13 +13460,13 @@
         <v>22</v>
       </c>
       <c r="H30" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="J30" s="24" t="s">
         <v>89</v>
-      </c>
-      <c r="I30" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="J30" s="24" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="31" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13288,10 +13474,10 @@
         <v>20012</v>
       </c>
       <c r="D31" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>91</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>92</v>
       </c>
       <c r="F31" s="11">
         <v>20012</v>
@@ -13300,13 +13486,13 @@
         <v>22</v>
       </c>
       <c r="H31" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="J31" s="25" t="s">
         <v>93</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="J31" s="25" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="32" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13314,10 +13500,10 @@
         <v>20013</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F32" s="11">
         <v>20013</v>
@@ -13326,13 +13512,13 @@
         <v>22</v>
       </c>
       <c r="H32" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="J32" s="25" t="s">
         <v>96</v>
-      </c>
-      <c r="I32" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="J32" s="25" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="33" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13340,10 +13526,10 @@
         <v>20021</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="F33" s="11">
         <v>20021</v>
@@ -13352,13 +13538,13 @@
         <v>28</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>99</v>
+        <v>430</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="J33" s="25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13369,7 +13555,7 @@
         <v>39</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="F34" s="11">
         <v>20022</v>
@@ -13378,13 +13564,13 @@
         <v>28</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="J34" s="25" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13392,10 +13578,10 @@
         <v>20023</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F35" s="11">
         <v>20023</v>
@@ -13404,13 +13590,13 @@
         <v>28</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="J35" s="25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13418,10 +13604,10 @@
         <v>20031</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F36" s="11">
         <v>20031</v>
@@ -13430,13 +13616,13 @@
         <v>32</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="J36" s="25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13447,7 +13633,7 @@
         <v>39</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="F37" s="11">
         <v>20032</v>
@@ -13456,13 +13642,13 @@
         <v>32</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="J37" s="24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13470,10 +13656,10 @@
         <v>20033</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F38" s="11">
         <v>20033</v>
@@ -13482,13 +13668,13 @@
         <v>32</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="J38" s="25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13496,10 +13682,10 @@
         <v>20041</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F39" s="11">
         <v>20041</v>
@@ -13508,13 +13694,13 @@
         <v>38</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="J39" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13525,7 +13711,7 @@
         <v>39</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="F40" s="11">
         <v>20042</v>
@@ -13534,13 +13720,13 @@
         <v>38</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="J40" s="25" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13548,10 +13734,10 @@
         <v>20043</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F41" s="11">
         <v>20043</v>
@@ -13560,13 +13746,13 @@
         <v>38</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="J41" s="25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13574,10 +13760,10 @@
         <v>20051</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F42" s="11">
         <v>20051</v>
@@ -13586,13 +13772,13 @@
         <v>42</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="J42" s="24" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13603,7 +13789,7 @@
         <v>39</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="F43" s="11">
         <v>20052</v>
@@ -13612,13 +13798,13 @@
         <v>42</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="J43" s="24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13626,10 +13812,10 @@
         <v>20053</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="F44" s="11">
         <v>20053</v>
@@ -13638,13 +13824,13 @@
         <v>42</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="J44" s="24" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13655,7 +13841,7 @@
         <v>57</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="F45" s="11">
         <v>20061</v>
@@ -13664,13 +13850,13 @@
         <v>52</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13678,10 +13864,10 @@
         <v>20062</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F46" s="11">
         <v>20062</v>
@@ -13690,13 +13876,13 @@
         <v>52</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="J46" s="27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13704,10 +13890,10 @@
         <v>20063</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="F47" s="11">
         <v>20063</v>
@@ -13716,13 +13902,13 @@
         <v>52</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="J47" s="26" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13733,7 +13919,7 @@
         <v>15</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="F48" s="11">
         <v>30001</v>
@@ -13742,13 +13928,13 @@
         <v>15</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I48" s="17" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="J48" s="26" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="49" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13756,10 +13942,10 @@
         <v>30002</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="F49" s="11">
         <v>30002</v>
@@ -13768,13 +13954,13 @@
         <v>15</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="J49" s="26" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13785,7 +13971,7 @@
         <v>21</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="F50" s="11">
         <v>30003</v>
@@ -13794,13 +13980,13 @@
         <v>15</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="J50" s="25" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13808,10 +13994,10 @@
         <v>30011</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F51" s="11">
         <v>30011</v>
@@ -13820,13 +14006,13 @@
         <v>22</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="J51" s="26" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="52" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13834,10 +14020,10 @@
         <v>30012</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F52" s="11">
         <v>30012</v>
@@ -13846,13 +14032,13 @@
         <v>22</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I52" s="20" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="J52" s="25" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13860,10 +14046,10 @@
         <v>30013</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F53" s="11">
         <v>30013</v>
@@ -13872,13 +14058,13 @@
         <v>22</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="J53" s="25" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="54" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13886,10 +14072,10 @@
         <v>30021</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F54" s="11">
         <v>30021</v>
@@ -13898,13 +14084,13 @@
         <v>28</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="J54" s="25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="55" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13912,10 +14098,10 @@
         <v>30022</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="F55" s="11">
         <v>30022</v>
@@ -13924,13 +14110,13 @@
         <v>28</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="J55" s="26" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13941,7 +14127,7 @@
         <v>39</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="F56" s="11">
         <v>30023</v>
@@ -13950,13 +14136,13 @@
         <v>28</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="J56" s="25" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13964,10 +14150,10 @@
         <v>30031</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F57" s="11">
         <v>30031</v>
@@ -13976,13 +14162,13 @@
         <v>32</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="J57" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13990,10 +14176,10 @@
         <v>30032</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="F58" s="11">
         <v>30032</v>
@@ -14002,13 +14188,13 @@
         <v>32</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="J58" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14019,7 +14205,7 @@
         <v>48</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F59" s="11">
         <v>30033</v>
@@ -14028,13 +14214,13 @@
         <v>32</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="J59" s="25" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14042,10 +14228,10 @@
         <v>30041</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="F60" s="11">
         <v>30041</v>
@@ -14054,13 +14240,13 @@
         <v>38</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="J60" s="25" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14068,10 +14254,10 @@
         <v>30042</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="F61" s="11">
         <v>30042</v>
@@ -14080,10 +14266,10 @@
         <v>38</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="J61" s="24" t="s">
         <v>44</v>
@@ -14097,7 +14283,7 @@
         <v>57</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="F62" s="11">
         <v>30043</v>
@@ -14106,13 +14292,13 @@
         <v>38</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I62" s="12" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="J62" s="25" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14120,10 +14306,10 @@
         <v>30051</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="F63" s="11">
         <v>30051</v>
@@ -14132,13 +14318,13 @@
         <v>42</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="J63" s="25" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14146,10 +14332,10 @@
         <v>30052</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="F64" s="11">
         <v>30052</v>
@@ -14158,13 +14344,13 @@
         <v>42</v>
       </c>
       <c r="H64" s="23" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I64" s="23" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="J64" s="24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14175,7 +14361,7 @@
         <v>67</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="F65" s="11">
         <v>30053</v>
@@ -14184,13 +14370,13 @@
         <v>42</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="J65" s="25" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14198,10 +14384,10 @@
         <v>30061</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="F66" s="11">
         <v>30061</v>
@@ -14210,13 +14396,13 @@
         <v>52</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="J66" s="26" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14224,10 +14410,10 @@
         <v>30062</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E67" s="28" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="F67" s="11">
         <v>30062</v>
@@ -14236,13 +14422,13 @@
         <v>52</v>
       </c>
       <c r="H67" s="29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I67" s="29" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="J67" s="27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="68" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14250,10 +14436,10 @@
         <v>30063</v>
       </c>
       <c r="D68" s="30" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E68" s="30" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="F68" s="11">
         <v>30063</v>
@@ -14262,13 +14448,13 @@
         <v>52</v>
       </c>
       <c r="H68" s="31" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I68" s="31" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="J68" s="26" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14276,10 +14462,10 @@
         <v>40001</v>
       </c>
       <c r="D69" s="32" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E69" s="32" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F69" s="14">
         <v>40001</v>
@@ -14288,13 +14474,13 @@
         <v>15</v>
       </c>
       <c r="H69" s="33" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I69" s="33" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="J69" s="26" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="70" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14305,7 +14491,7 @@
         <v>39</v>
       </c>
       <c r="E70" s="32" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="F70" s="14">
         <v>40002</v>
@@ -14314,13 +14500,13 @@
         <v>15</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>200</v>
+        <v>429</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="J70" s="25" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14328,10 +14514,10 @@
         <v>40003</v>
       </c>
       <c r="D71" s="35" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E71" s="35" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="F71" s="34">
         <v>40003</v>
@@ -14340,13 +14526,13 @@
         <v>15</v>
       </c>
       <c r="H71" s="36" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I71" s="36" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="J71" s="26" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="72" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14354,10 +14540,10 @@
         <v>40011</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E72" s="32" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F72" s="14">
         <v>40011</v>
@@ -14366,13 +14552,13 @@
         <v>22</v>
       </c>
       <c r="H72" s="33" t="s">
-        <v>207</v>
+        <v>428</v>
       </c>
       <c r="I72" s="33" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="J72" s="26" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14383,7 +14569,7 @@
         <v>57</v>
       </c>
       <c r="E73" s="32" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="F73" s="14">
         <v>40012</v>
@@ -14392,13 +14578,13 @@
         <v>22</v>
       </c>
       <c r="H73" s="33" t="s">
-        <v>209</v>
+        <v>427</v>
       </c>
       <c r="I73" s="33" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="J73" s="26" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14406,10 +14592,10 @@
         <v>40013</v>
       </c>
       <c r="D74" s="35" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E74" s="35" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="F74" s="34">
         <v>40013</v>
@@ -14418,13 +14604,13 @@
         <v>22</v>
       </c>
       <c r="H74" s="36" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="I74" s="36" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="J74" s="41" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="75" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14432,10 +14618,10 @@
         <v>40021</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E75" s="32" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="F75" s="14">
         <v>40021</v>
@@ -14444,13 +14630,13 @@
         <v>28</v>
       </c>
       <c r="H75" s="33" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I75" s="33" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="J75" s="26" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="76" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14461,7 +14647,7 @@
         <v>57</v>
       </c>
       <c r="E76" s="32" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="F76" s="14">
         <v>40022</v>
@@ -14470,13 +14656,13 @@
         <v>28</v>
       </c>
       <c r="H76" s="33" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="I76" s="33" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="J76" s="25" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="77" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14487,7 +14673,7 @@
         <v>21</v>
       </c>
       <c r="E77" s="35" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="F77" s="34">
         <v>40023</v>
@@ -14496,13 +14682,13 @@
         <v>28</v>
       </c>
       <c r="H77" s="36" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="I77" s="36" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="J77" s="25" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="78" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14510,10 +14696,10 @@
         <v>40031</v>
       </c>
       <c r="D78" s="37" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E78" s="37" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="F78" s="34">
         <v>40031</v>
@@ -14522,13 +14708,13 @@
         <v>32</v>
       </c>
       <c r="H78" s="38" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I78" s="38" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="J78" s="39" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="79" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14539,7 +14725,7 @@
         <v>57</v>
       </c>
       <c r="E79" s="37" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="F79" s="34">
         <v>40032</v>
@@ -14548,13 +14734,13 @@
         <v>32</v>
       </c>
       <c r="H79" s="38" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="I79" s="38" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="J79" s="25" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="80" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14562,10 +14748,10 @@
         <v>40033</v>
       </c>
       <c r="D80" s="35" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E80" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F80" s="34">
         <v>40033</v>
@@ -14574,13 +14760,13 @@
         <v>32</v>
       </c>
       <c r="H80" s="36" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I80" s="36" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="J80" s="25" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="81" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14591,7 +14777,7 @@
         <v>57</v>
       </c>
       <c r="E81" s="37" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="F81" s="34">
         <v>40041</v>
@@ -14600,13 +14786,13 @@
         <v>38</v>
       </c>
       <c r="H81" s="38" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I81" s="38" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="J81" s="25" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14614,10 +14800,10 @@
         <v>40042</v>
       </c>
       <c r="D82" s="37" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E82" s="37" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F82" s="34">
         <v>40042</v>
@@ -14626,13 +14812,13 @@
         <v>38</v>
       </c>
       <c r="H82" s="38" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I82" s="38" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="J82" s="39" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="83" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14640,10 +14826,10 @@
         <v>40043</v>
       </c>
       <c r="D83" s="35" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="E83" s="35" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F83" s="34">
         <v>40043</v>
@@ -14652,13 +14838,13 @@
         <v>38</v>
       </c>
       <c r="H83" s="36" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="I83" s="36" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="J83" s="25" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="84" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14666,10 +14852,10 @@
         <v>40051</v>
       </c>
       <c r="D84" s="37" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E84" s="37" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F84" s="34">
         <v>40051</v>
@@ -14678,13 +14864,13 @@
         <v>42</v>
       </c>
       <c r="H84" s="38" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I84" s="38" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="J84" s="39" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="85" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14695,7 +14881,7 @@
         <v>39</v>
       </c>
       <c r="E85" s="37" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="F85" s="34">
         <v>40052</v>
@@ -14704,13 +14890,13 @@
         <v>42</v>
       </c>
       <c r="H85" s="38" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="I85" s="38" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="J85" s="25" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="86" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14721,7 +14907,7 @@
         <v>75</v>
       </c>
       <c r="E86" s="35" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F86" s="34">
         <v>40053</v>
@@ -14730,13 +14916,13 @@
         <v>42</v>
       </c>
       <c r="H86" s="36" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I86" s="36" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="J86" s="27" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="87" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14744,10 +14930,10 @@
         <v>40061</v>
       </c>
       <c r="D87" s="37" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E87" s="37" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F87" s="34">
         <v>40061</v>
@@ -14756,13 +14942,13 @@
         <v>52</v>
       </c>
       <c r="H87" s="38" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I87" s="38" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="J87" s="39" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="88" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14770,10 +14956,10 @@
         <v>40062</v>
       </c>
       <c r="D88" s="37" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E88" s="37" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="F88" s="34">
         <v>40062</v>
@@ -14782,13 +14968,13 @@
         <v>52</v>
       </c>
       <c r="H88" s="38" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I88" s="38" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="J88" s="26" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="89" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14796,10 +14982,10 @@
         <v>40063</v>
       </c>
       <c r="D89" s="35" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E89" s="35" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="F89" s="34">
         <v>40063</v>
@@ -14808,479 +14994,720 @@
         <v>52</v>
       </c>
       <c r="H89" s="36" t="s">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="I89" s="36" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="J89" s="27" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
-    <row r="90" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C90" s="11">
+    <row r="90" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C90" s="14">
+        <v>50001</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="E90" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="F90" s="14">
+        <v>50001</v>
+      </c>
+      <c r="G90" s="14">
+        <v>15</v>
+      </c>
+      <c r="H90" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="I90" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J90" s="27" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="91" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C91" s="14">
+        <v>50002</v>
+      </c>
+      <c r="D91" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="E91" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F91" s="14">
+        <v>50002</v>
+      </c>
+      <c r="G91" s="14">
+        <v>15</v>
+      </c>
+      <c r="H91" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="I91" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="J91" s="27" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="92" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C92" s="14">
+        <v>50003</v>
+      </c>
+      <c r="D92" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="E92" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F92" s="14">
+        <v>50003</v>
+      </c>
+      <c r="G92" s="14">
+        <v>15</v>
+      </c>
+      <c r="H92" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="I92" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="J92" s="27" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="93" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C93" s="14">
+        <v>50011</v>
+      </c>
+      <c r="D93" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="E93" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="F93" s="14">
+        <v>50011</v>
+      </c>
+      <c r="G93" s="14">
+        <v>22</v>
+      </c>
+      <c r="H93" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="I93" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="J93" s="27" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="94" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C94" s="14">
+        <v>50012</v>
+      </c>
+      <c r="D94" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="E94" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="F94" s="14">
+        <v>50012</v>
+      </c>
+      <c r="G94" s="14">
+        <v>22</v>
+      </c>
+      <c r="H94" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="I94" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="J94" s="27" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="95" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C95" s="14">
+        <v>50013</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E95" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="F95" s="14">
+        <v>50013</v>
+      </c>
+      <c r="G95" s="14">
+        <v>22</v>
+      </c>
+      <c r="H95" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="I95" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="J95" s="27" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="96" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C96" s="14">
+        <v>50021</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E96" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="F96" s="14">
+        <v>50021</v>
+      </c>
+      <c r="G96" s="14">
+        <v>28</v>
+      </c>
+      <c r="H96" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="I96" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="J96" s="27" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="97" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C97" s="14">
+        <v>50022</v>
+      </c>
+      <c r="D97" s="14" t="s">
+        <v>477</v>
+      </c>
+      <c r="E97" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="F97" s="14">
+        <v>50022</v>
+      </c>
+      <c r="G97" s="14">
+        <v>28</v>
+      </c>
+      <c r="H97" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="I97" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="J97" s="27" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="98" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C98" s="14">
+        <v>50023</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E98" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="F98" s="14">
+        <v>50023</v>
+      </c>
+      <c r="G98" s="14">
+        <v>28</v>
+      </c>
+      <c r="H98" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="I98" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="J98" s="27" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="99" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C99" s="14">
+        <v>50031</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E99" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="F99" s="14">
+        <v>50031</v>
+      </c>
+      <c r="G99" s="14">
+        <v>32</v>
+      </c>
+      <c r="H99" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="I99" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="J99" s="27" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="100" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C100" s="14">
+        <v>50032</v>
+      </c>
+      <c r="D100" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="E100" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="F100" s="14">
+        <v>50032</v>
+      </c>
+      <c r="G100" s="14">
+        <v>32</v>
+      </c>
+      <c r="H100" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="I100" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="J100" s="27" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="101" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C101" s="14">
+        <v>50033</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E101" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="F101" s="14">
+        <v>50033</v>
+      </c>
+      <c r="G101" s="14">
+        <v>32</v>
+      </c>
+      <c r="H101" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="I101" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="J101" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="102" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C102" s="14">
+        <v>50041</v>
+      </c>
+      <c r="D102" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E102" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="F102" s="14">
+        <v>50041</v>
+      </c>
+      <c r="G102" s="14">
+        <v>38</v>
+      </c>
+      <c r="H102" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="I102" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="J102" s="27" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="103" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C103" s="14">
+        <v>50042</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E103" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="F103" s="14">
+        <v>50042</v>
+      </c>
+      <c r="G103" s="14">
+        <v>38</v>
+      </c>
+      <c r="H103" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="I103" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="J103" s="27" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="104" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C104" s="14">
+        <v>50043</v>
+      </c>
+      <c r="D104" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E104" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="F104" s="14">
+        <v>50043</v>
+      </c>
+      <c r="G104" s="14">
+        <v>38</v>
+      </c>
+      <c r="H104" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="I104" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="J104" s="27" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="105" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C105" s="14">
+        <v>50051</v>
+      </c>
+      <c r="D105" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E105" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="F105" s="14">
+        <v>50051</v>
+      </c>
+      <c r="G105" s="14">
+        <v>42</v>
+      </c>
+      <c r="H105" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="I105" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="J105" s="27" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="106" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C106" s="14">
+        <v>50052</v>
+      </c>
+      <c r="D106" s="14" t="s">
+        <v>469</v>
+      </c>
+      <c r="E106" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="F106" s="14">
+        <v>50052</v>
+      </c>
+      <c r="G106" s="14">
+        <v>42</v>
+      </c>
+      <c r="H106" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="I106" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="J106" s="27" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="107" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C107" s="14">
+        <v>50053</v>
+      </c>
+      <c r="D107" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E107" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F107" s="14">
+        <v>50053</v>
+      </c>
+      <c r="G107" s="14">
+        <v>42</v>
+      </c>
+      <c r="H107" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="I107" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="J107" s="27" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="108" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C108" s="14">
+        <v>50061</v>
+      </c>
+      <c r="D108" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E108" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F108" s="14">
+        <v>50061</v>
+      </c>
+      <c r="G108" s="14">
+        <v>52</v>
+      </c>
+      <c r="H108" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="I108" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="J108" s="27" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="109" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C109" s="14">
+        <v>50062</v>
+      </c>
+      <c r="D109" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E109" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="F109" s="14">
+        <v>50062</v>
+      </c>
+      <c r="G109" s="14">
+        <v>52</v>
+      </c>
+      <c r="H109" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="I109" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="J109" s="27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="110" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C110" s="14">
+        <v>50063</v>
+      </c>
+      <c r="D110" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="E110" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="F110" s="14">
+        <v>50063</v>
+      </c>
+      <c r="G110" s="14">
+        <v>52</v>
+      </c>
+      <c r="H110" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I110" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="J110" s="27" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="111" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C111" s="11">
         <v>90001</v>
       </c>
-      <c r="D90" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="E90" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="F90" s="11">
+      <c r="D111" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="E111" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F111" s="11">
         <v>60010100</v>
-      </c>
-      <c r="G90" s="11">
-        <v>1</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="I90" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J90" s="25" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="91" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C91" s="11">
-        <v>90002</v>
-      </c>
-      <c r="D91" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="E91" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="F91" s="11">
-        <v>60010200</v>
-      </c>
-      <c r="G91" s="11">
-        <v>1</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="J91" s="25" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="92" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C92" s="11">
-        <v>90003</v>
-      </c>
-      <c r="D92" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="E92" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="F92" s="11">
-        <v>60010300</v>
-      </c>
-      <c r="G92" s="11">
-        <v>1</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="J92" s="25" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="93" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C93" s="11">
-        <v>90004</v>
-      </c>
-      <c r="D93" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="E93" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="F93" s="11">
-        <v>60010400</v>
-      </c>
-      <c r="G93" s="11">
-        <v>2</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="J93" s="25" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="94" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C94" s="11">
-        <v>90005</v>
-      </c>
-      <c r="D94" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="E94" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="F94" s="11">
-        <v>60010500</v>
-      </c>
-      <c r="G94" s="11">
-        <v>2</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="J94" s="25" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="95" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C95" s="11">
-        <v>90006</v>
-      </c>
-      <c r="D95" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="E95" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="F95" s="11">
-        <v>60010600</v>
-      </c>
-      <c r="G95" s="11">
-        <v>2</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="J95" s="25" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="96" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C96" s="11">
-        <v>100001</v>
-      </c>
-      <c r="F96" s="11">
-        <v>0</v>
-      </c>
-      <c r="G96" s="11">
-        <v>1</v>
-      </c>
-      <c r="J96" s="40" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="97" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C97" s="11">
-        <v>100002</v>
-      </c>
-      <c r="F97" s="11">
-        <v>0</v>
-      </c>
-      <c r="G97" s="11">
-        <v>1</v>
-      </c>
-      <c r="J97" s="40" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="98" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C98" s="11">
-        <v>100003</v>
-      </c>
-      <c r="F98" s="11">
-        <v>0</v>
-      </c>
-      <c r="G98" s="11">
-        <v>1</v>
-      </c>
-      <c r="J98" s="40" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="99" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C99" s="11">
-        <v>100004</v>
-      </c>
-      <c r="F99" s="11">
-        <v>0</v>
-      </c>
-      <c r="G99" s="11">
-        <v>1</v>
-      </c>
-      <c r="J99" s="40" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="100" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C100" s="11">
-        <v>100005</v>
-      </c>
-      <c r="F100" s="11">
-        <v>0</v>
-      </c>
-      <c r="G100" s="11">
-        <v>1</v>
-      </c>
-      <c r="J100" s="40" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="101" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C101" s="11">
-        <v>100006</v>
-      </c>
-      <c r="F101" s="11">
-        <v>0</v>
-      </c>
-      <c r="G101" s="11">
-        <v>1</v>
-      </c>
-      <c r="J101" s="40" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="102" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C102" s="11">
-        <v>100007</v>
-      </c>
-      <c r="F102" s="11">
-        <v>0</v>
-      </c>
-      <c r="G102" s="11">
-        <v>1</v>
-      </c>
-      <c r="J102" s="40" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="103" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C103" s="11">
-        <v>100008</v>
-      </c>
-      <c r="F103" s="11">
-        <v>0</v>
-      </c>
-      <c r="G103" s="11">
-        <v>1</v>
-      </c>
-      <c r="J103" s="40" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="104" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C104" s="11">
-        <v>100009</v>
-      </c>
-      <c r="F104" s="11">
-        <v>0</v>
-      </c>
-      <c r="G104" s="11">
-        <v>1</v>
-      </c>
-      <c r="J104" s="40" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="105" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C105" s="11">
-        <v>100010</v>
-      </c>
-      <c r="F105" s="11">
-        <v>0</v>
-      </c>
-      <c r="G105" s="11">
-        <v>1</v>
-      </c>
-      <c r="J105" s="40" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="106" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C106" s="11">
-        <v>200001</v>
-      </c>
-      <c r="F106" s="11">
-        <v>0</v>
-      </c>
-      <c r="G106" s="11">
-        <v>1</v>
-      </c>
-      <c r="J106" s="40" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q106" s="11"/>
-    </row>
-    <row r="107" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C107" s="11">
-        <v>200002</v>
-      </c>
-      <c r="F107" s="11">
-        <v>0</v>
-      </c>
-      <c r="G107" s="11">
-        <v>1</v>
-      </c>
-      <c r="J107" s="40" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q107" s="11"/>
-    </row>
-    <row r="108" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C108" s="11">
-        <v>200003</v>
-      </c>
-      <c r="F108" s="11">
-        <v>0</v>
-      </c>
-      <c r="G108" s="11">
-        <v>1</v>
-      </c>
-      <c r="J108" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q108" s="11"/>
-    </row>
-    <row r="109" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C109" s="11">
-        <v>200004</v>
-      </c>
-      <c r="F109" s="11">
-        <v>0</v>
-      </c>
-      <c r="G109" s="11">
-        <v>1</v>
-      </c>
-      <c r="J109" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q109" s="11"/>
-    </row>
-    <row r="110" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C110" s="11">
-        <v>200005</v>
-      </c>
-      <c r="F110" s="11">
-        <v>0</v>
-      </c>
-      <c r="G110" s="11">
-        <v>1</v>
-      </c>
-      <c r="J110" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q110" s="11"/>
-    </row>
-    <row r="111" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C111" s="11">
-        <v>200006</v>
-      </c>
-      <c r="F111" s="11">
-        <v>0</v>
       </c>
       <c r="G111" s="11">
         <v>1</v>
       </c>
-      <c r="J111" s="40" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q111" s="11"/>
+      <c r="H111" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J111" s="25" t="s">
+        <v>250</v>
+      </c>
     </row>
-    <row r="112" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C112" s="11">
-        <v>200007</v>
+        <v>90002</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="E112" s="11" t="s">
+        <v>252</v>
       </c>
       <c r="F112" s="11">
-        <v>0</v>
+        <v>60010200</v>
       </c>
       <c r="G112" s="11">
         <v>1</v>
       </c>
-      <c r="J112" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q112" s="11"/>
+      <c r="H112" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="J112" s="25" t="s">
+        <v>255</v>
+      </c>
     </row>
-    <row r="113" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C113" s="11">
-        <v>200008</v>
+        <v>90003</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="E113" s="11" t="s">
+        <v>257</v>
       </c>
       <c r="F113" s="11">
-        <v>0</v>
+        <v>60010300</v>
       </c>
       <c r="G113" s="11">
         <v>1</v>
       </c>
-      <c r="J113" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q113" s="11"/>
+      <c r="H113" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="J113" s="25" t="s">
+        <v>260</v>
+      </c>
     </row>
-    <row r="114" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C114" s="11">
-        <v>200009</v>
+        <v>90004</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="E114" s="11" t="s">
+        <v>262</v>
       </c>
       <c r="F114" s="11">
-        <v>0</v>
+        <v>60010400</v>
       </c>
       <c r="G114" s="11">
-        <v>1</v>
-      </c>
-      <c r="J114" s="40" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q114" s="11"/>
+        <v>2</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="J114" s="25" t="s">
+        <v>265</v>
+      </c>
     </row>
-    <row r="115" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C115" s="11">
-        <v>200010</v>
+        <v>90005</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="E115" s="11" t="s">
+        <v>267</v>
       </c>
       <c r="F115" s="11">
-        <v>0</v>
+        <v>60010500</v>
       </c>
       <c r="G115" s="11">
-        <v>1</v>
-      </c>
-      <c r="J115" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q115" s="11"/>
+        <v>2</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="J115" s="25" t="s">
+        <v>270</v>
+      </c>
     </row>
-    <row r="116" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C116" s="11">
-        <v>200011</v>
+        <v>90006</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="E116" s="11" t="s">
+        <v>272</v>
       </c>
       <c r="F116" s="11">
-        <v>0</v>
+        <v>60010600</v>
       </c>
       <c r="G116" s="11">
-        <v>1</v>
-      </c>
-      <c r="J116" s="40" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q116" s="11"/>
+        <v>2</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J116" s="25" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="117" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C117" s="11">
-        <v>200012</v>
+        <v>100001</v>
       </c>
       <c r="F117" s="11">
         <v>0</v>
@@ -15289,13 +15716,12 @@
         <v>1</v>
       </c>
       <c r="J117" s="40" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q117" s="11"/>
+        <v>276</v>
+      </c>
     </row>
     <row r="118" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C118" s="11">
-        <v>200013</v>
+        <v>100002</v>
       </c>
       <c r="F118" s="11">
         <v>0</v>
@@ -15304,13 +15730,12 @@
         <v>1</v>
       </c>
       <c r="J118" s="40" t="s">
-        <v>286</v>
-      </c>
-      <c r="Q118" s="11"/>
+        <v>277</v>
+      </c>
     </row>
     <row r="119" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C119" s="11">
-        <v>200014</v>
+        <v>100003</v>
       </c>
       <c r="F119" s="11">
         <v>0</v>
@@ -15319,14 +15744,321 @@
         <v>1</v>
       </c>
       <c r="J119" s="40" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="120" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C120" s="11">
+        <v>100004</v>
+      </c>
+      <c r="F120" s="11">
+        <v>0</v>
+      </c>
+      <c r="G120" s="11">
+        <v>1</v>
+      </c>
+      <c r="J120" s="40" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="121" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C121" s="11">
+        <v>100005</v>
+      </c>
+      <c r="F121" s="11">
+        <v>0</v>
+      </c>
+      <c r="G121" s="11">
+        <v>1</v>
+      </c>
+      <c r="J121" s="40" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="122" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C122" s="11">
+        <v>100006</v>
+      </c>
+      <c r="F122" s="11">
+        <v>0</v>
+      </c>
+      <c r="G122" s="11">
+        <v>1</v>
+      </c>
+      <c r="J122" s="40" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="123" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C123" s="11">
+        <v>100007</v>
+      </c>
+      <c r="F123" s="11">
+        <v>0</v>
+      </c>
+      <c r="G123" s="11">
+        <v>1</v>
+      </c>
+      <c r="J123" s="40" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="124" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C124" s="11">
+        <v>100008</v>
+      </c>
+      <c r="F124" s="11">
+        <v>0</v>
+      </c>
+      <c r="G124" s="11">
+        <v>1</v>
+      </c>
+      <c r="J124" s="40" t="s">
         <v>283</v>
       </c>
-      <c r="Q119" s="11"/>
+    </row>
+    <row r="125" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C125" s="11">
+        <v>100009</v>
+      </c>
+      <c r="F125" s="11">
+        <v>0</v>
+      </c>
+      <c r="G125" s="11">
+        <v>1</v>
+      </c>
+      <c r="J125" s="40" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="126" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C126" s="11">
+        <v>100010</v>
+      </c>
+      <c r="F126" s="11">
+        <v>0</v>
+      </c>
+      <c r="G126" s="11">
+        <v>1</v>
+      </c>
+      <c r="J126" s="40" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="127" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C127" s="11">
+        <v>200001</v>
+      </c>
+      <c r="F127" s="11">
+        <v>0</v>
+      </c>
+      <c r="G127" s="11">
+        <v>1</v>
+      </c>
+      <c r="J127" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q127" s="11"/>
+    </row>
+    <row r="128" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C128" s="11">
+        <v>200002</v>
+      </c>
+      <c r="F128" s="11">
+        <v>0</v>
+      </c>
+      <c r="G128" s="11">
+        <v>1</v>
+      </c>
+      <c r="J128" s="40" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q128" s="11"/>
+    </row>
+    <row r="129" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C129" s="11">
+        <v>200003</v>
+      </c>
+      <c r="F129" s="11">
+        <v>0</v>
+      </c>
+      <c r="G129" s="11">
+        <v>1</v>
+      </c>
+      <c r="J129" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q129" s="11"/>
+    </row>
+    <row r="130" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C130" s="11">
+        <v>200004</v>
+      </c>
+      <c r="F130" s="11">
+        <v>0</v>
+      </c>
+      <c r="G130" s="11">
+        <v>1</v>
+      </c>
+      <c r="J130" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q130" s="11"/>
+    </row>
+    <row r="131" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C131" s="11">
+        <v>200005</v>
+      </c>
+      <c r="F131" s="11">
+        <v>0</v>
+      </c>
+      <c r="G131" s="11">
+        <v>1</v>
+      </c>
+      <c r="J131" s="40" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q131" s="11"/>
+    </row>
+    <row r="132" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C132" s="11">
+        <v>200006</v>
+      </c>
+      <c r="F132" s="11">
+        <v>0</v>
+      </c>
+      <c r="G132" s="11">
+        <v>1</v>
+      </c>
+      <c r="J132" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q132" s="11"/>
+    </row>
+    <row r="133" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C133" s="11">
+        <v>200007</v>
+      </c>
+      <c r="F133" s="11">
+        <v>0</v>
+      </c>
+      <c r="G133" s="11">
+        <v>1</v>
+      </c>
+      <c r="J133" s="40" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q133" s="11"/>
+    </row>
+    <row r="134" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C134" s="11">
+        <v>200008</v>
+      </c>
+      <c r="F134" s="11">
+        <v>0</v>
+      </c>
+      <c r="G134" s="11">
+        <v>1</v>
+      </c>
+      <c r="J134" s="40" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q134" s="11"/>
+    </row>
+    <row r="135" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C135" s="11">
+        <v>200009</v>
+      </c>
+      <c r="F135" s="11">
+        <v>0</v>
+      </c>
+      <c r="G135" s="11">
+        <v>1</v>
+      </c>
+      <c r="J135" s="40" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q135" s="11"/>
+    </row>
+    <row r="136" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C136" s="11">
+        <v>200010</v>
+      </c>
+      <c r="F136" s="11">
+        <v>0</v>
+      </c>
+      <c r="G136" s="11">
+        <v>1</v>
+      </c>
+      <c r="J136" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q136" s="11"/>
+    </row>
+    <row r="137" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C137" s="11">
+        <v>200011</v>
+      </c>
+      <c r="F137" s="11">
+        <v>0</v>
+      </c>
+      <c r="G137" s="11">
+        <v>1</v>
+      </c>
+      <c r="J137" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q137" s="11"/>
+    </row>
+    <row r="138" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C138" s="11">
+        <v>200012</v>
+      </c>
+      <c r="F138" s="11">
+        <v>0</v>
+      </c>
+      <c r="G138" s="11">
+        <v>1</v>
+      </c>
+      <c r="J138" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q138" s="11"/>
+    </row>
+    <row r="139" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C139" s="11">
+        <v>200013</v>
+      </c>
+      <c r="F139" s="11">
+        <v>0</v>
+      </c>
+      <c r="G139" s="11">
+        <v>1</v>
+      </c>
+      <c r="J139" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q139" s="11"/>
+    </row>
+    <row r="140" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C140" s="11">
+        <v>200014</v>
+      </c>
+      <c r="F140" s="11">
+        <v>0</v>
+      </c>
+      <c r="G140" s="11">
+        <v>1</v>
+      </c>
+      <c r="J140" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q140" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AB06AA-6E7B-4103-A31C-A07A33AB6877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699326CC-B75A-4783-8F39-7ACEE2686443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1260,9 +1260,6 @@
     <t>SkillIdAdd;62000110</t>
   </si>
   <si>
-    <t>SkillIdAdd;62000111</t>
-  </si>
-  <si>
     <t>BuffIdAdd;65011202,65011203,65011204,65011205,65011206;92000046,92000047</t>
   </si>
   <si>
@@ -1278,9 +1275,6 @@
     <t>SkillPropertyAdd;65011302,65011303,65011304,65011305,65011306;4;2</t>
   </si>
   <si>
-    <t>巨力震击伤害提升75%；隐匿一击冷却时间降低3秒；召唤的镜像攻击和生命提升20%</t>
-  </si>
-  <si>
     <t>SkillPropertyAdd;65021102,65021103,65021104,65021105,65021106;2;0.75@SkillPropertyAdd;65022102,65022103,65022104,65022105,65022106;4;3</t>
   </si>
   <si>
@@ -1299,9 +1293,6 @@
     <t>SkillPropertyAdd;65021202,65021203,65021204,65021205,65021206;2;0.75@SkillPropertyAdd;65022302,65022303,65022304,65022305,65022306;2;0.75@BuffIdAdd;65023202,65023203,65023204,65023205,65023206;92000049</t>
   </si>
   <si>
-    <t>SkillIdAdd;62000112</t>
-  </si>
-  <si>
     <t>巨剑之力冷却时间降低3秒；破风之击伤害提升75%；幻影冲击如果目标血量低于50%，则提升50%伤害。</t>
   </si>
   <si>
@@ -1332,19 +1323,10 @@
     <t>SkillIdAdd;62000114</t>
   </si>
   <si>
-    <t>SkillIdAdd;62000115</t>
-  </si>
-  <si>
     <t>普通攻击和释放技能有概率为目标附加1层黑暗印记，当黑暗印记达到5层时，造成范围350%伤害和1秒置空。</t>
   </si>
   <si>
-    <t>SkillIdAdd;62000116</t>
-  </si>
-  <si>
     <t>当生命值降低至30%后,受到闪避提升50%,持续3秒，30秒内只能触发一次</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;62000117</t>
   </si>
   <si>
     <t>SkillIdAdd;62000118</t>
@@ -1530,10 +1512,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>普通攻击和释放技能有一定的概率对目标身上附加闪避标记，每个闪避标记可以降低目标5%的闪避,最多叠加5层。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>坚韧之力</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1559,6 +1537,34 @@
   </si>
   <si>
     <t>黑暗印记</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000111</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨力震击伤害提升75%；隐匿一击冷却时间降低3秒；召唤的镜像攻击和生命提升20%</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000112</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000115</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通攻击和释放技能有一定的概率对目标身上附加闪避标记，每个闪避标记可以降低目标10%的闪避,最多叠加5层。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000117</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000116</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -9660,7 +9666,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -9784,6 +9790,9 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2603">
@@ -15074,8 +15083,8 @@
       <c r="I92" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="J92" s="27" t="s">
-        <v>394</v>
+      <c r="J92" s="44" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="93" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15083,7 +15092,7 @@
         <v>50011</v>
       </c>
       <c r="D93" s="43" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="E93" s="14" t="s">
         <v>56</v>
@@ -15095,13 +15104,13 @@
         <v>22</v>
       </c>
       <c r="H93" s="42" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="I93" s="13" t="s">
         <v>180</v>
       </c>
       <c r="J93" s="27" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="94" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15109,7 +15118,7 @@
         <v>50012</v>
       </c>
       <c r="D94" s="43" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="E94" s="14" t="s">
         <v>327</v>
@@ -15121,13 +15130,13 @@
         <v>22</v>
       </c>
       <c r="H94" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I94" s="13" t="s">
         <v>329</v>
       </c>
       <c r="J94" s="27" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="95" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15135,7 +15144,7 @@
         <v>50013</v>
       </c>
       <c r="D95" s="43" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="E95" s="14" t="s">
         <v>56</v>
@@ -15147,13 +15156,13 @@
         <v>22</v>
       </c>
       <c r="H95" s="13" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I95" s="13" t="s">
         <v>250</v>
       </c>
       <c r="J95" s="27" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="96" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15172,14 +15181,14 @@
       <c r="G96" s="14">
         <v>28</v>
       </c>
-      <c r="H96" s="13" t="s">
-        <v>400</v>
+      <c r="H96" s="42" t="s">
+        <v>482</v>
       </c>
       <c r="I96" s="13" t="s">
         <v>250</v>
       </c>
       <c r="J96" s="27" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="97" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15187,7 +15196,7 @@
         <v>50022</v>
       </c>
       <c r="D97" s="43" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E97" s="14" t="s">
         <v>51</v>
@@ -15199,13 +15208,13 @@
         <v>28</v>
       </c>
       <c r="H97" s="13" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I97" s="13" t="s">
         <v>53</v>
       </c>
       <c r="J97" s="27" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="98" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15213,7 +15222,7 @@
         <v>50023</v>
       </c>
       <c r="D98" s="43" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="E98" s="14" t="s">
         <v>31</v>
@@ -15225,13 +15234,13 @@
         <v>28</v>
       </c>
       <c r="H98" s="42" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="I98" s="13" t="s">
         <v>33</v>
       </c>
       <c r="J98" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="99" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15239,7 +15248,7 @@
         <v>50031</v>
       </c>
       <c r="D99" s="43" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="E99" s="14" t="s">
         <v>86</v>
@@ -15251,13 +15260,13 @@
         <v>32</v>
       </c>
       <c r="H99" s="13" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I99" s="13" t="s">
         <v>337</v>
       </c>
       <c r="J99" s="27" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="100" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15265,7 +15274,7 @@
         <v>50032</v>
       </c>
       <c r="D100" s="43" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="E100" s="14" t="s">
         <v>106</v>
@@ -15277,13 +15286,13 @@
         <v>32</v>
       </c>
       <c r="H100" s="42" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="I100" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="J100" s="27" t="s">
-        <v>407</v>
+      <c r="J100" s="44" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="101" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15291,7 +15300,7 @@
         <v>50033</v>
       </c>
       <c r="D101" s="43" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="E101" s="14" t="s">
         <v>162</v>
@@ -15317,7 +15326,7 @@
         <v>50041</v>
       </c>
       <c r="D102" s="43" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="E102" s="14" t="s">
         <v>86</v>
@@ -15329,13 +15338,13 @@
         <v>38</v>
       </c>
       <c r="H102" s="13" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I102" s="13" t="s">
         <v>337</v>
       </c>
       <c r="J102" s="27" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="103" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15343,7 +15352,7 @@
         <v>50042</v>
       </c>
       <c r="D103" s="43" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="E103" s="14" t="s">
         <v>139</v>
@@ -15355,13 +15364,13 @@
         <v>38</v>
       </c>
       <c r="H103" s="13" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="I103" s="13" t="s">
         <v>141</v>
       </c>
       <c r="J103" s="27" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="104" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15369,7 +15378,7 @@
         <v>50043</v>
       </c>
       <c r="D104" s="43" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="E104" s="14" t="s">
         <v>162</v>
@@ -15381,13 +15390,13 @@
         <v>38</v>
       </c>
       <c r="H104" s="13" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="I104" s="13" t="s">
         <v>164</v>
       </c>
       <c r="J104" s="27" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="105" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15407,13 +15416,13 @@
         <v>42</v>
       </c>
       <c r="H105" s="13" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I105" s="13" t="s">
         <v>250</v>
       </c>
       <c r="J105" s="27" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="106" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15421,7 +15430,7 @@
         <v>50052</v>
       </c>
       <c r="D106" s="43" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="E106" s="14" t="s">
         <v>170</v>
@@ -15433,13 +15442,13 @@
         <v>42</v>
       </c>
       <c r="H106" s="13" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="I106" s="13" t="s">
         <v>172</v>
       </c>
       <c r="J106" s="27" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="107" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15447,7 +15456,7 @@
         <v>50053</v>
       </c>
       <c r="D107" s="43" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="E107" s="14" t="s">
         <v>157</v>
@@ -15459,13 +15468,13 @@
         <v>42</v>
       </c>
       <c r="H107" s="42" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="I107" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="J107" s="27" t="s">
-        <v>418</v>
+      <c r="J107" s="44" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="108" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15473,7 +15482,7 @@
         <v>50061</v>
       </c>
       <c r="D108" s="43" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="E108" s="14" t="s">
         <v>157</v>
@@ -15485,13 +15494,13 @@
         <v>52</v>
       </c>
       <c r="H108" s="13" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="I108" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="J108" s="27" t="s">
-        <v>420</v>
+      <c r="J108" s="44" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="109" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15499,7 +15508,7 @@
         <v>50062</v>
       </c>
       <c r="D109" s="43" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="E109" s="14" t="s">
         <v>170</v>
@@ -15511,13 +15520,13 @@
         <v>52</v>
       </c>
       <c r="H109" s="13" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="I109" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="J109" s="27" t="s">
-        <v>422</v>
+      <c r="J109" s="44" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="110" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15525,7 +15534,7 @@
         <v>50063</v>
       </c>
       <c r="D110" s="43" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="E110" s="14" t="s">
         <v>291</v>
@@ -15537,13 +15546,13 @@
         <v>52</v>
       </c>
       <c r="H110" s="42" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="I110" s="13" t="s">
         <v>293</v>
       </c>
       <c r="J110" s="27" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="111" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15551,10 +15560,10 @@
         <v>90001</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="F111" s="11">
         <v>60010100</v>
@@ -15563,13 +15572,13 @@
         <v>1</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="J111" s="25" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="112" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15577,10 +15586,10 @@
         <v>90002</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="F112" s="11">
         <v>60010200</v>
@@ -15589,13 +15598,13 @@
         <v>1</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="J112" s="25" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="113" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15603,10 +15612,10 @@
         <v>90003</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="F113" s="11">
         <v>60010300</v>
@@ -15615,13 +15624,13 @@
         <v>1</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="J113" s="25" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="114" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15629,10 +15638,10 @@
         <v>90004</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="F114" s="11">
         <v>60010400</v>
@@ -15641,13 +15650,13 @@
         <v>2</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="J114" s="25" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="115" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15655,10 +15664,10 @@
         <v>90005</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="F115" s="11">
         <v>60010500</v>
@@ -15667,13 +15676,13 @@
         <v>2</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="J115" s="25" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="116" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15681,10 +15690,10 @@
         <v>90006</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="F116" s="11">
         <v>60010600</v>
@@ -15693,13 +15702,13 @@
         <v>2</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="J116" s="25" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
     </row>
     <row r="117" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15713,7 +15722,7 @@
         <v>1</v>
       </c>
       <c r="J117" s="40" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="118" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15727,7 +15736,7 @@
         <v>1</v>
       </c>
       <c r="J118" s="40" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="119" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15741,7 +15750,7 @@
         <v>1</v>
       </c>
       <c r="J119" s="40" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="120" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15755,7 +15764,7 @@
         <v>1</v>
       </c>
       <c r="J120" s="40" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
     <row r="121" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15769,7 +15778,7 @@
         <v>1</v>
       </c>
       <c r="J121" s="40" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="122" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15783,7 +15792,7 @@
         <v>1</v>
       </c>
       <c r="J122" s="40" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="123" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15797,7 +15806,7 @@
         <v>1</v>
       </c>
       <c r="J123" s="40" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="124" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15811,7 +15820,7 @@
         <v>1</v>
       </c>
       <c r="J124" s="40" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="125" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15825,7 +15834,7 @@
         <v>1</v>
       </c>
       <c r="J125" s="40" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="126" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15839,7 +15848,7 @@
         <v>1</v>
       </c>
       <c r="J126" s="40" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="127" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15853,7 +15862,7 @@
         <v>1</v>
       </c>
       <c r="J127" s="40" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="Q127" s="11"/>
     </row>
@@ -15868,7 +15877,7 @@
         <v>1</v>
       </c>
       <c r="J128" s="40" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="Q128" s="11"/>
     </row>
@@ -15883,7 +15892,7 @@
         <v>1</v>
       </c>
       <c r="J129" s="40" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="Q129" s="11"/>
     </row>
@@ -15898,7 +15907,7 @@
         <v>1</v>
       </c>
       <c r="J130" s="40" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="Q130" s="11"/>
     </row>
@@ -15913,7 +15922,7 @@
         <v>1</v>
       </c>
       <c r="J131" s="40" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="Q131" s="11"/>
     </row>
@@ -15928,7 +15937,7 @@
         <v>1</v>
       </c>
       <c r="J132" s="40" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="Q132" s="11"/>
     </row>
@@ -15943,7 +15952,7 @@
         <v>1</v>
       </c>
       <c r="J133" s="40" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="Q133" s="11"/>
     </row>
@@ -15958,7 +15967,7 @@
         <v>1</v>
       </c>
       <c r="J134" s="40" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="Q134" s="11"/>
     </row>
@@ -15973,7 +15982,7 @@
         <v>1</v>
       </c>
       <c r="J135" s="40" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="Q135" s="11"/>
     </row>
@@ -15988,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="J136" s="40" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="Q136" s="11"/>
     </row>
@@ -16003,7 +16012,7 @@
         <v>1</v>
       </c>
       <c r="J137" s="40" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="Q137" s="11"/>
     </row>
@@ -16018,7 +16027,7 @@
         <v>1</v>
       </c>
       <c r="J138" s="40" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="Q138" s="11"/>
     </row>
@@ -16033,7 +16042,7 @@
         <v>1</v>
       </c>
       <c r="J139" s="40" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="Q139" s="11"/>
     </row>
@@ -16048,7 +16057,7 @@
         <v>1</v>
       </c>
       <c r="J140" s="40" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="Q140" s="11"/>
     </row>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699326CC-B75A-4783-8F39-7ACEE2686443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D787C7-B503-48D0-9DA0-BE45620247EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,6 +32,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">RolePropertyAdd  增加角色属性
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="490">
   <si>
     <t>c</t>
   </si>
@@ -95,9 +96,6 @@
   </si>
   <si>
     <t>talentDes_EN</t>
-  </si>
-  <si>
-    <t>AddPropreListStr</t>
   </si>
   <si>
     <t>int</t>
@@ -927,6 +925,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>火舌守卫：冷却时间降低5秒;疾风箭域：技能会使目标的移动速度降低30%;</t>
@@ -936,6 +935,7 @@
         <sz val="10"/>
         <color rgb="FFFF0000"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>野兽呼唤:自身召唤的所有怪物属性提升25%</t>
@@ -1293,9 +1293,6 @@
     <t>SkillPropertyAdd;65021202,65021203,65021204,65021205,65021206;2;0.75@SkillPropertyAdd;65022302,65022303,65022304,65022305,65022306;2;0.75@BuffIdAdd;65023202,65023203,65023204,65023205,65023206;92000049</t>
   </si>
   <si>
-    <t>巨剑之力冷却时间降低3秒；破风之击伤害提升75%；幻影冲击如果目标血量低于50%，则提升50%伤害。</t>
-  </si>
-  <si>
     <t>SkillPropertyAdd;65021302,65021303,65021304,65021305,65021306;4;2@SkillPropertyAdd;65022302,65022303,65022304,65022305,65022306;2;0.75@SkillPropertyAdd;64015102,64015103,64015104,64015105,64015106;2;0.25@SkillPropertyAdd;65023301,65023302,65023303,65023304,65023305,65023306;9;0.5;0.5</t>
   </si>
   <si>
@@ -1308,9 +1305,6 @@
     <t>普通攻击造成的伤害提升20%</t>
   </si>
   <si>
-    <t>RolePropertyAdd;202702;0.2</t>
-  </si>
-  <si>
     <t>守护天使伤害提升75%；释放唤灵之契有概率不进入冷却时间；逆转之力冷却时间降低3秒。</t>
   </si>
   <si>
@@ -1324,9 +1318,6 @@
   </si>
   <si>
     <t>普通攻击和释放技能有概率为目标附加1层黑暗印记，当黑暗印记达到5层时，造成范围350%伤害和1秒置空。</t>
-  </si>
-  <si>
-    <t>当生命值降低至30%后,受到闪避提升50%,持续3秒，30秒内只能触发一次</t>
   </si>
   <si>
     <t>SkillIdAdd;62000118</t>
@@ -1565,6 +1556,30 @@
   </si>
   <si>
     <t>SkillIdAdd;62000116</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddPropreListStr</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨剑之力冷却时间降低3秒；破风之击伤害提升75%；幻影冲击如果目标血量低于50%，则大幅度提升自身技能伤害。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RolePropertyAdd;202703;0.2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RolePropertyAdd;205003;0.15</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度永久提升15%</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>当生命值降低至50%后,受到闪避提升40%,自身伤害提升50%,持续3秒，30秒内只能触发一次</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1584,12 +1599,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1597,6 +1614,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1605,12 +1623,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1618,23 +1638,27 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1642,11 +1666,13 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1655,18 +1681,21 @@
       <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1679,6 +1708,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1686,6 +1716,7 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -12796,33 +12827,33 @@
         <v>11</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>12</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>14</v>
-      </c>
       <c r="E5" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="I5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>14</v>
-      </c>
       <c r="J5" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12830,10 +12861,10 @@
         <v>10001</v>
       </c>
       <c r="D6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>15</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>16</v>
       </c>
       <c r="F6" s="11">
         <v>10001</v>
@@ -12842,13 +12873,13 @@
         <v>15</v>
       </c>
       <c r="H6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="J6" s="24" t="s">
         <v>18</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="7" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12856,10 +12887,10 @@
         <v>10002</v>
       </c>
       <c r="D7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>20</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>21</v>
       </c>
       <c r="F7" s="11">
         <v>10002</v>
@@ -12868,13 +12899,13 @@
         <v>15</v>
       </c>
       <c r="H7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="J7" s="24" t="s">
         <v>23</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12882,10 +12913,10 @@
         <v>10003</v>
       </c>
       <c r="D8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>26</v>
       </c>
       <c r="F8" s="11">
         <v>10003</v>
@@ -12894,13 +12925,13 @@
         <v>15</v>
       </c>
       <c r="H8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="J8" s="25" t="s">
         <v>28</v>
-      </c>
-      <c r="J8" s="25" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12908,10 +12939,10 @@
         <v>10011</v>
       </c>
       <c r="D9" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>31</v>
       </c>
       <c r="F9" s="11">
         <v>10011</v>
@@ -12920,13 +12951,13 @@
         <v>22</v>
       </c>
       <c r="H9" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="J9" s="24" t="s">
         <v>33</v>
-      </c>
-      <c r="J9" s="24" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="10" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12934,10 +12965,10 @@
         <v>10012</v>
       </c>
       <c r="D10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>36</v>
       </c>
       <c r="F10" s="11">
         <v>10012</v>
@@ -12946,13 +12977,13 @@
         <v>22</v>
       </c>
       <c r="H10" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="J10" s="25" t="s">
         <v>38</v>
-      </c>
-      <c r="J10" s="25" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="11" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12960,10 +12991,10 @@
         <v>10013</v>
       </c>
       <c r="D11" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>41</v>
       </c>
       <c r="F11" s="11">
         <v>10013</v>
@@ -12972,13 +13003,13 @@
         <v>22</v>
       </c>
       <c r="H11" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="J11" s="24" t="s">
         <v>43</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="12" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12986,10 +13017,10 @@
         <v>10021</v>
       </c>
       <c r="D12" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>45</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>46</v>
       </c>
       <c r="F12" s="11">
         <v>10021</v>
@@ -12998,13 +13029,13 @@
         <v>28</v>
       </c>
       <c r="H12" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="J12" s="25" t="s">
         <v>48</v>
-      </c>
-      <c r="J12" s="25" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13012,10 +13043,10 @@
         <v>10022</v>
       </c>
       <c r="D13" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>50</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>51</v>
       </c>
       <c r="F13" s="11">
         <v>10022</v>
@@ -13024,13 +13055,13 @@
         <v>28</v>
       </c>
       <c r="H13" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="J13" s="25" t="s">
         <v>53</v>
-      </c>
-      <c r="J13" s="25" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="14" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13038,10 +13069,10 @@
         <v>10023</v>
       </c>
       <c r="D14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>56</v>
       </c>
       <c r="F14" s="11">
         <v>10023</v>
@@ -13050,13 +13081,13 @@
         <v>28</v>
       </c>
       <c r="H14" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="J14" s="25" t="s">
         <v>58</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="15" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13064,10 +13095,10 @@
         <v>10031</v>
       </c>
       <c r="D15" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>60</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>61</v>
       </c>
       <c r="F15" s="11">
         <v>10031</v>
@@ -13076,13 +13107,13 @@
         <v>32</v>
       </c>
       <c r="H15" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="J15" s="24" t="s">
         <v>63</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="16" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13090,10 +13121,10 @@
         <v>10032</v>
       </c>
       <c r="D16" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>65</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>66</v>
       </c>
       <c r="F16" s="11">
         <v>10032</v>
@@ -13102,13 +13133,13 @@
         <v>32</v>
       </c>
       <c r="H16" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I16" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="J16" s="24" t="s">
         <v>68</v>
-      </c>
-      <c r="J16" s="24" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="17" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13116,10 +13147,10 @@
         <v>10033</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>70</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>71</v>
       </c>
       <c r="F17" s="11">
         <v>10033</v>
@@ -13128,13 +13159,13 @@
         <v>32</v>
       </c>
       <c r="H17" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I17" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="J17" s="25" t="s">
         <v>73</v>
-      </c>
-      <c r="J17" s="25" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="18" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13142,10 +13173,10 @@
         <v>10041</v>
       </c>
       <c r="D18" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="F18" s="11">
         <v>10041</v>
@@ -13154,13 +13185,13 @@
         <v>38</v>
       </c>
       <c r="H18" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="J18" s="24" t="s">
         <v>78</v>
-      </c>
-      <c r="J18" s="24" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="19" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13168,10 +13199,10 @@
         <v>10042</v>
       </c>
       <c r="D19" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>80</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>81</v>
       </c>
       <c r="F19" s="11">
         <v>10042</v>
@@ -13180,13 +13211,13 @@
         <v>38</v>
       </c>
       <c r="H19" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I19" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="J19" s="24" t="s">
         <v>83</v>
-      </c>
-      <c r="J19" s="24" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="20" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13194,10 +13225,10 @@
         <v>10043</v>
       </c>
       <c r="D20" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>85</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>86</v>
       </c>
       <c r="F20" s="11">
         <v>10043</v>
@@ -13206,13 +13237,13 @@
         <v>38</v>
       </c>
       <c r="H20" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="I20" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="J20" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="J20" s="25" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="21" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13220,10 +13251,10 @@
         <v>10051</v>
       </c>
       <c r="D21" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>90</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>91</v>
       </c>
       <c r="F21" s="11">
         <v>10051</v>
@@ -13232,13 +13263,13 @@
         <v>42</v>
       </c>
       <c r="H21" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="J21" s="24" t="s">
         <v>93</v>
-      </c>
-      <c r="J21" s="24" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="22" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13246,10 +13277,10 @@
         <v>10052</v>
       </c>
       <c r="D22" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F22" s="11">
         <v>10052</v>
@@ -13258,13 +13289,13 @@
         <v>42</v>
       </c>
       <c r="H22" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="I22" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="J22" s="24" t="s">
         <v>98</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="23" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13272,10 +13303,10 @@
         <v>10053</v>
       </c>
       <c r="D23" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>100</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>101</v>
       </c>
       <c r="F23" s="11">
         <v>10053</v>
@@ -13284,13 +13315,13 @@
         <v>42</v>
       </c>
       <c r="H23" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="I23" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="I23" s="13" t="s">
+      <c r="J23" s="25" t="s">
         <v>103</v>
-      </c>
-      <c r="J23" s="25" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="24" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13298,10 +13329,10 @@
         <v>10061</v>
       </c>
       <c r="D24" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>105</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>106</v>
       </c>
       <c r="F24" s="14">
         <v>10061</v>
@@ -13310,13 +13341,13 @@
         <v>52</v>
       </c>
       <c r="H24" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="I24" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="J24" s="26" t="s">
         <v>108</v>
-      </c>
-      <c r="J24" s="26" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="25" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13324,10 +13355,10 @@
         <v>10062</v>
       </c>
       <c r="D25" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="15" t="s">
         <v>85</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>86</v>
       </c>
       <c r="F25" s="14">
         <v>10062</v>
@@ -13336,13 +13367,13 @@
         <v>52</v>
       </c>
       <c r="H25" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="I25" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="J25" s="26" t="s">
         <v>111</v>
-      </c>
-      <c r="J25" s="26" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="26" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13350,10 +13381,10 @@
         <v>10063</v>
       </c>
       <c r="D26" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>113</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>114</v>
       </c>
       <c r="F26" s="14">
         <v>10063</v>
@@ -13362,13 +13393,13 @@
         <v>52</v>
       </c>
       <c r="H26" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="I26" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="I26" s="13" t="s">
+      <c r="J26" s="27" t="s">
         <v>116</v>
-      </c>
-      <c r="J26" s="27" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="27" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13376,10 +13407,10 @@
         <v>20001</v>
       </c>
       <c r="D27" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>119</v>
       </c>
       <c r="F27" s="11">
         <v>20001</v>
@@ -13388,13 +13419,13 @@
         <v>15</v>
       </c>
       <c r="H27" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="I27" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="I27" s="12" t="s">
+      <c r="J27" s="25" t="s">
         <v>121</v>
-      </c>
-      <c r="J27" s="25" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="28" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13402,10 +13433,10 @@
         <v>20002</v>
       </c>
       <c r="D28" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E28" s="11" t="s">
         <v>123</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>124</v>
       </c>
       <c r="F28" s="11">
         <v>20002</v>
@@ -13414,13 +13445,13 @@
         <v>15</v>
       </c>
       <c r="H28" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="I28" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="J28" s="24" t="s">
         <v>126</v>
-      </c>
-      <c r="J28" s="24" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="29" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13428,10 +13459,10 @@
         <v>20003</v>
       </c>
       <c r="D29" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>129</v>
       </c>
       <c r="F29" s="11">
         <v>20003</v>
@@ -13440,13 +13471,13 @@
         <v>15</v>
       </c>
       <c r="H29" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="I29" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="I29" s="12" t="s">
+      <c r="J29" s="25" t="s">
         <v>131</v>
-      </c>
-      <c r="J29" s="25" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="30" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13454,10 +13485,10 @@
         <v>20011</v>
       </c>
       <c r="D30" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>133</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>134</v>
       </c>
       <c r="F30" s="11">
         <v>20011</v>
@@ -13466,13 +13497,13 @@
         <v>22</v>
       </c>
       <c r="H30" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="I30" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="I30" s="12" t="s">
+      <c r="J30" s="24" t="s">
         <v>136</v>
-      </c>
-      <c r="J30" s="24" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="31" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13480,10 +13511,10 @@
         <v>20012</v>
       </c>
       <c r="D31" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>138</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>139</v>
       </c>
       <c r="F31" s="11">
         <v>20012</v>
@@ -13492,13 +13523,13 @@
         <v>22</v>
       </c>
       <c r="H31" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="I31" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="J31" s="25" t="s">
         <v>141</v>
-      </c>
-      <c r="J31" s="25" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="32" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13506,10 +13537,10 @@
         <v>20013</v>
       </c>
       <c r="D32" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" s="11" t="s">
         <v>143</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>144</v>
       </c>
       <c r="F32" s="11">
         <v>20013</v>
@@ -13518,13 +13549,13 @@
         <v>22</v>
       </c>
       <c r="H32" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="I32" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="J32" s="25" t="s">
         <v>146</v>
-      </c>
-      <c r="J32" s="25" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="33" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13532,10 +13563,10 @@
         <v>20021</v>
       </c>
       <c r="D33" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E33" s="11" t="s">
         <v>148</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>149</v>
       </c>
       <c r="F33" s="11">
         <v>20021</v>
@@ -13544,13 +13575,13 @@
         <v>28</v>
       </c>
       <c r="H33" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="I33" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="I33" s="12" t="s">
+      <c r="J33" s="25" t="s">
         <v>151</v>
-      </c>
-      <c r="J33" s="25" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="34" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13558,10 +13589,10 @@
         <v>20022</v>
       </c>
       <c r="D34" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>56</v>
       </c>
       <c r="F34" s="11">
         <v>20022</v>
@@ -13570,13 +13601,13 @@
         <v>28</v>
       </c>
       <c r="H34" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="I34" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="I34" s="12" t="s">
+      <c r="J34" s="25" t="s">
         <v>154</v>
-      </c>
-      <c r="J34" s="25" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="35" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13584,10 +13615,10 @@
         <v>20023</v>
       </c>
       <c r="D35" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E35" s="11" t="s">
         <v>156</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>157</v>
       </c>
       <c r="F35" s="11">
         <v>20023</v>
@@ -13596,13 +13627,13 @@
         <v>28</v>
       </c>
       <c r="H35" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="I35" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="I35" s="12" t="s">
+      <c r="J35" s="25" t="s">
         <v>159</v>
-      </c>
-      <c r="J35" s="25" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="36" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13610,10 +13641,10 @@
         <v>20031</v>
       </c>
       <c r="D36" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E36" s="11" t="s">
         <v>161</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>162</v>
       </c>
       <c r="F36" s="11">
         <v>20031</v>
@@ -13622,13 +13653,13 @@
         <v>32</v>
       </c>
       <c r="H36" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I36" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="I36" s="12" t="s">
+      <c r="J36" s="25" t="s">
         <v>164</v>
-      </c>
-      <c r="J36" s="25" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="37" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13636,10 +13667,10 @@
         <v>20032</v>
       </c>
       <c r="D37" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>56</v>
       </c>
       <c r="F37" s="11">
         <v>20032</v>
@@ -13648,13 +13679,13 @@
         <v>32</v>
       </c>
       <c r="H37" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="I37" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="I37" s="12" t="s">
+      <c r="J37" s="24" t="s">
         <v>167</v>
-      </c>
-      <c r="J37" s="24" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="38" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13662,10 +13693,10 @@
         <v>20033</v>
       </c>
       <c r="D38" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E38" s="11" t="s">
         <v>169</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>170</v>
       </c>
       <c r="F38" s="11">
         <v>20033</v>
@@ -13674,13 +13705,13 @@
         <v>32</v>
       </c>
       <c r="H38" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="I38" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="I38" s="12" t="s">
+      <c r="J38" s="25" t="s">
         <v>172</v>
-      </c>
-      <c r="J38" s="25" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="39" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13688,10 +13719,10 @@
         <v>20041</v>
       </c>
       <c r="D39" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>174</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>175</v>
       </c>
       <c r="F39" s="11">
         <v>20041</v>
@@ -13700,13 +13731,13 @@
         <v>38</v>
       </c>
       <c r="H39" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="I39" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="I39" s="12" t="s">
+      <c r="J39" s="24" t="s">
         <v>177</v>
-      </c>
-      <c r="J39" s="24" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="40" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13714,10 +13745,10 @@
         <v>20042</v>
       </c>
       <c r="D40" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>56</v>
       </c>
       <c r="F40" s="11">
         <v>20042</v>
@@ -13726,13 +13757,13 @@
         <v>38</v>
       </c>
       <c r="H40" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="I40" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="I40" s="12" t="s">
+      <c r="J40" s="25" t="s">
         <v>180</v>
-      </c>
-      <c r="J40" s="25" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="41" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13740,10 +13771,10 @@
         <v>20043</v>
       </c>
       <c r="D41" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E41" s="11" t="s">
         <v>182</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>183</v>
       </c>
       <c r="F41" s="11">
         <v>20043</v>
@@ -13752,13 +13783,13 @@
         <v>38</v>
       </c>
       <c r="H41" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="I41" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="I41" s="12" t="s">
+      <c r="J41" s="25" t="s">
         <v>185</v>
-      </c>
-      <c r="J41" s="25" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="42" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13766,10 +13797,10 @@
         <v>20051</v>
       </c>
       <c r="D42" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E42" s="11" t="s">
         <v>187</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>188</v>
       </c>
       <c r="F42" s="11">
         <v>20051</v>
@@ -13778,13 +13809,13 @@
         <v>42</v>
       </c>
       <c r="H42" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="I42" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="I42" s="12" t="s">
+      <c r="J42" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="J42" s="24" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="43" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13792,10 +13823,10 @@
         <v>20052</v>
       </c>
       <c r="D43" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>56</v>
       </c>
       <c r="F43" s="11">
         <v>20052</v>
@@ -13804,13 +13835,13 @@
         <v>42</v>
       </c>
       <c r="H43" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="I43" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="J43" s="24" t="s">
         <v>193</v>
-      </c>
-      <c r="J43" s="24" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="44" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13818,10 +13849,10 @@
         <v>20053</v>
       </c>
       <c r="D44" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E44" s="11" t="s">
         <v>195</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>196</v>
       </c>
       <c r="F44" s="11">
         <v>20053</v>
@@ -13830,13 +13861,13 @@
         <v>42</v>
       </c>
       <c r="H44" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="I44" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="I44" s="12" t="s">
+      <c r="J44" s="24" t="s">
         <v>198</v>
-      </c>
-      <c r="J44" s="24" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="45" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13844,10 +13875,10 @@
         <v>20061</v>
       </c>
       <c r="D45" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E45" s="15" t="s">
         <v>85</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>86</v>
       </c>
       <c r="F45" s="11">
         <v>20061</v>
@@ -13856,13 +13887,13 @@
         <v>52</v>
       </c>
       <c r="H45" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="I45" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="I45" s="13" t="s">
+      <c r="J45" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="46" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13870,10 +13901,10 @@
         <v>20062</v>
       </c>
       <c r="D46" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="E46" s="15" t="s">
         <v>203</v>
-      </c>
-      <c r="E46" s="15" t="s">
-        <v>204</v>
       </c>
       <c r="F46" s="11">
         <v>20062</v>
@@ -13882,13 +13913,13 @@
         <v>52</v>
       </c>
       <c r="H46" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="I46" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="I46" s="13" t="s">
+      <c r="J46" s="27" t="s">
         <v>206</v>
-      </c>
-      <c r="J46" s="27" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="47" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13896,10 +13927,10 @@
         <v>20063</v>
       </c>
       <c r="D47" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="E47" s="15" t="s">
         <v>208</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>209</v>
       </c>
       <c r="F47" s="11">
         <v>20063</v>
@@ -13908,13 +13939,13 @@
         <v>52</v>
       </c>
       <c r="H47" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="I47" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="I47" s="13" t="s">
+      <c r="J47" s="26" t="s">
         <v>211</v>
-      </c>
-      <c r="J47" s="26" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="48" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13922,10 +13953,10 @@
         <v>30001</v>
       </c>
       <c r="D48" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" s="16" t="s">
         <v>15</v>
-      </c>
-      <c r="E48" s="16" t="s">
-        <v>16</v>
       </c>
       <c r="F48" s="11">
         <v>30001</v>
@@ -13934,13 +13965,13 @@
         <v>15</v>
       </c>
       <c r="H48" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="I48" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="I48" s="17" t="s">
+      <c r="J48" s="26" t="s">
         <v>214</v>
-      </c>
-      <c r="J48" s="26" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="49" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13948,10 +13979,10 @@
         <v>30002</v>
       </c>
       <c r="D49" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="E49" s="16" t="s">
         <v>216</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>217</v>
       </c>
       <c r="F49" s="11">
         <v>30002</v>
@@ -13960,13 +13991,13 @@
         <v>15</v>
       </c>
       <c r="H49" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="I49" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="I49" s="17" t="s">
+      <c r="J49" s="26" t="s">
         <v>219</v>
-      </c>
-      <c r="J49" s="26" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="50" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13974,10 +14005,10 @@
         <v>30003</v>
       </c>
       <c r="D50" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="18" t="s">
         <v>25</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>26</v>
       </c>
       <c r="F50" s="11">
         <v>30003</v>
@@ -13986,13 +14017,13 @@
         <v>15</v>
       </c>
       <c r="H50" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I50" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="I50" s="12" t="s">
+      <c r="J50" s="25" t="s">
         <v>222</v>
-      </c>
-      <c r="J50" s="25" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="51" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14000,10 +14031,10 @@
         <v>30011</v>
       </c>
       <c r="D51" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="E51" s="16" t="s">
         <v>224</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>225</v>
       </c>
       <c r="F51" s="11">
         <v>30011</v>
@@ -14012,13 +14043,13 @@
         <v>22</v>
       </c>
       <c r="H51" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="I51" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="I51" s="17" t="s">
+      <c r="J51" s="26" t="s">
         <v>227</v>
-      </c>
-      <c r="J51" s="26" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="52" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14026,10 +14057,10 @@
         <v>30012</v>
       </c>
       <c r="D52" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="E52" s="19" t="s">
         <v>229</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>230</v>
       </c>
       <c r="F52" s="11">
         <v>30012</v>
@@ -14038,13 +14069,13 @@
         <v>22</v>
       </c>
       <c r="H52" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="I52" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="I52" s="20" t="s">
+      <c r="J52" s="25" t="s">
         <v>232</v>
-      </c>
-      <c r="J52" s="25" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="53" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14052,10 +14083,10 @@
         <v>30013</v>
       </c>
       <c r="D53" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="E53" s="18" t="s">
         <v>234</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>235</v>
       </c>
       <c r="F53" s="11">
         <v>30013</v>
@@ -14064,13 +14095,13 @@
         <v>22</v>
       </c>
       <c r="H53" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="I53" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="I53" s="12" t="s">
+      <c r="J53" s="25" t="s">
         <v>237</v>
-      </c>
-      <c r="J53" s="25" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="54" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14078,10 +14109,10 @@
         <v>30021</v>
       </c>
       <c r="D54" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="E54" s="18" t="s">
         <v>239</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>240</v>
       </c>
       <c r="F54" s="11">
         <v>30021</v>
@@ -14090,13 +14121,13 @@
         <v>28</v>
       </c>
       <c r="H54" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="I54" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="I54" s="12" t="s">
+      <c r="J54" s="25" t="s">
         <v>242</v>
-      </c>
-      <c r="J54" s="25" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="55" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14104,10 +14135,10 @@
         <v>30022</v>
       </c>
       <c r="D55" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="E55" s="18" t="s">
         <v>244</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>245</v>
       </c>
       <c r="F55" s="11">
         <v>30022</v>
@@ -14116,13 +14147,13 @@
         <v>28</v>
       </c>
       <c r="H55" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="I55" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="I55" s="12" t="s">
+      <c r="J55" s="26" t="s">
         <v>247</v>
-      </c>
-      <c r="J55" s="26" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="56" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14130,10 +14161,10 @@
         <v>30023</v>
       </c>
       <c r="D56" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E56" s="18" t="s">
         <v>55</v>
-      </c>
-      <c r="E56" s="18" t="s">
-        <v>56</v>
       </c>
       <c r="F56" s="11">
         <v>30023</v>
@@ -14142,13 +14173,13 @@
         <v>28</v>
       </c>
       <c r="H56" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="I56" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="I56" s="12" t="s">
+      <c r="J56" s="25" t="s">
         <v>250</v>
-      </c>
-      <c r="J56" s="25" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="57" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14156,10 +14187,10 @@
         <v>30031</v>
       </c>
       <c r="D57" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="E57" s="18" t="s">
         <v>252</v>
-      </c>
-      <c r="E57" s="18" t="s">
-        <v>253</v>
       </c>
       <c r="F57" s="11">
         <v>30031</v>
@@ -14168,13 +14199,13 @@
         <v>32</v>
       </c>
       <c r="H57" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="I57" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="I57" s="12" t="s">
+      <c r="J57" s="26" t="s">
         <v>255</v>
-      </c>
-      <c r="J57" s="26" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="58" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14182,10 +14213,10 @@
         <v>30032</v>
       </c>
       <c r="D58" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="E58" s="21" t="s">
         <v>257</v>
-      </c>
-      <c r="E58" s="21" t="s">
-        <v>258</v>
       </c>
       <c r="F58" s="11">
         <v>30032</v>
@@ -14194,13 +14225,13 @@
         <v>32</v>
       </c>
       <c r="H58" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="I58" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="I58" s="22" t="s">
+      <c r="J58" s="26" t="s">
         <v>260</v>
-      </c>
-      <c r="J58" s="26" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="59" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14208,10 +14239,10 @@
         <v>30033</v>
       </c>
       <c r="D59" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="18" t="s">
         <v>70</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>71</v>
       </c>
       <c r="F59" s="11">
         <v>30033</v>
@@ -14220,13 +14251,13 @@
         <v>32</v>
       </c>
       <c r="H59" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="I59" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="I59" s="12" t="s">
+      <c r="J59" s="25" t="s">
         <v>263</v>
-      </c>
-      <c r="J59" s="25" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="60" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14234,10 +14265,10 @@
         <v>30041</v>
       </c>
       <c r="D60" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="E60" s="18" t="s">
         <v>265</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>266</v>
       </c>
       <c r="F60" s="11">
         <v>30041</v>
@@ -14246,13 +14277,13 @@
         <v>38</v>
       </c>
       <c r="H60" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="I60" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="I60" s="12" t="s">
+      <c r="J60" s="25" t="s">
         <v>268</v>
-      </c>
-      <c r="J60" s="25" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="61" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14260,10 +14291,10 @@
         <v>30042</v>
       </c>
       <c r="D61" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="E61" s="16" t="s">
         <v>270</v>
-      </c>
-      <c r="E61" s="16" t="s">
-        <v>271</v>
       </c>
       <c r="F61" s="11">
         <v>30042</v>
@@ -14272,13 +14303,13 @@
         <v>38</v>
       </c>
       <c r="H61" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="I61" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="I61" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="J61" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14286,10 +14317,10 @@
         <v>30043</v>
       </c>
       <c r="D62" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="E62" s="18" t="s">
         <v>85</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>86</v>
       </c>
       <c r="F62" s="11">
         <v>30043</v>
@@ -14298,13 +14329,13 @@
         <v>38</v>
       </c>
       <c r="H62" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="I62" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="I62" s="12" t="s">
+      <c r="J62" s="25" t="s">
         <v>275</v>
-      </c>
-      <c r="J62" s="25" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="63" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14312,10 +14343,10 @@
         <v>30051</v>
       </c>
       <c r="D63" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="E63" s="18" t="s">
         <v>277</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>278</v>
       </c>
       <c r="F63" s="11">
         <v>30051</v>
@@ -14324,13 +14355,13 @@
         <v>42</v>
       </c>
       <c r="H63" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="I63" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="I63" s="12" t="s">
+      <c r="J63" s="25" t="s">
         <v>280</v>
-      </c>
-      <c r="J63" s="25" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="64" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14338,10 +14369,10 @@
         <v>30052</v>
       </c>
       <c r="D64" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="E64" s="21" t="s">
         <v>282</v>
-      </c>
-      <c r="E64" s="21" t="s">
-        <v>283</v>
       </c>
       <c r="F64" s="11">
         <v>30052</v>
@@ -14350,13 +14381,13 @@
         <v>42</v>
       </c>
       <c r="H64" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="I64" s="23" t="s">
         <v>284</v>
       </c>
-      <c r="I64" s="23" t="s">
+      <c r="J64" s="24" t="s">
         <v>285</v>
-      </c>
-      <c r="J64" s="24" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="65" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14364,10 +14395,10 @@
         <v>30053</v>
       </c>
       <c r="D65" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E65" s="18" t="s">
         <v>100</v>
-      </c>
-      <c r="E65" s="18" t="s">
-        <v>101</v>
       </c>
       <c r="F65" s="11">
         <v>30053</v>
@@ -14376,13 +14407,13 @@
         <v>42</v>
       </c>
       <c r="H65" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="I65" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="I65" s="12" t="s">
+      <c r="J65" s="25" t="s">
         <v>288</v>
-      </c>
-      <c r="J65" s="25" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="66" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14390,10 +14421,10 @@
         <v>30061</v>
       </c>
       <c r="D66" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="E66" s="15" t="s">
         <v>290</v>
-      </c>
-      <c r="E66" s="15" t="s">
-        <v>291</v>
       </c>
       <c r="F66" s="11">
         <v>30061</v>
@@ -14402,13 +14433,13 @@
         <v>52</v>
       </c>
       <c r="H66" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="I66" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="I66" s="13" t="s">
+      <c r="J66" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="J66" s="26" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="67" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14416,10 +14447,10 @@
         <v>30062</v>
       </c>
       <c r="D67" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="E67" s="28" t="s">
         <v>295</v>
-      </c>
-      <c r="E67" s="28" t="s">
-        <v>296</v>
       </c>
       <c r="F67" s="11">
         <v>30062</v>
@@ -14428,13 +14459,13 @@
         <v>52</v>
       </c>
       <c r="H67" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="I67" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="I67" s="29" t="s">
+      <c r="J67" s="27" t="s">
         <v>298</v>
-      </c>
-      <c r="J67" s="27" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="68" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14442,10 +14473,10 @@
         <v>30063</v>
       </c>
       <c r="D68" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="E68" s="30" t="s">
         <v>300</v>
-      </c>
-      <c r="E68" s="30" t="s">
-        <v>301</v>
       </c>
       <c r="F68" s="11">
         <v>30063</v>
@@ -14454,13 +14485,13 @@
         <v>52</v>
       </c>
       <c r="H68" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="I68" s="31" t="s">
         <v>302</v>
       </c>
-      <c r="I68" s="31" t="s">
+      <c r="J68" s="26" t="s">
         <v>303</v>
-      </c>
-      <c r="J68" s="26" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="69" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14468,10 +14499,10 @@
         <v>40001</v>
       </c>
       <c r="D69" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="E69" s="32" t="s">
         <v>305</v>
-      </c>
-      <c r="E69" s="32" t="s">
-        <v>306</v>
       </c>
       <c r="F69" s="14">
         <v>40001</v>
@@ -14480,13 +14511,13 @@
         <v>15</v>
       </c>
       <c r="H69" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="I69" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="I69" s="33" t="s">
+      <c r="J69" s="26" t="s">
         <v>308</v>
-      </c>
-      <c r="J69" s="26" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="70" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14494,10 +14525,10 @@
         <v>40002</v>
       </c>
       <c r="D70" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="E70" s="32" t="s">
         <v>55</v>
-      </c>
-      <c r="E70" s="32" t="s">
-        <v>56</v>
       </c>
       <c r="F70" s="14">
         <v>40002</v>
@@ -14506,13 +14537,13 @@
         <v>15</v>
       </c>
       <c r="H70" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="I70" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="I70" s="12" t="s">
+      <c r="J70" s="25" t="s">
         <v>311</v>
-      </c>
-      <c r="J70" s="25" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="71" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14520,10 +14551,10 @@
         <v>40003</v>
       </c>
       <c r="D71" s="35" t="s">
+        <v>312</v>
+      </c>
+      <c r="E71" s="35" t="s">
         <v>313</v>
-      </c>
-      <c r="E71" s="35" t="s">
-        <v>314</v>
       </c>
       <c r="F71" s="34">
         <v>40003</v>
@@ -14532,13 +14563,13 @@
         <v>15</v>
       </c>
       <c r="H71" s="36" t="s">
+        <v>314</v>
+      </c>
+      <c r="I71" s="36" t="s">
         <v>315</v>
       </c>
-      <c r="I71" s="36" t="s">
+      <c r="J71" s="26" t="s">
         <v>316</v>
-      </c>
-      <c r="J71" s="26" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="72" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14546,10 +14577,10 @@
         <v>40011</v>
       </c>
       <c r="D72" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="E72" s="32" t="s">
         <v>318</v>
-      </c>
-      <c r="E72" s="32" t="s">
-        <v>319</v>
       </c>
       <c r="F72" s="14">
         <v>40011</v>
@@ -14558,13 +14589,13 @@
         <v>22</v>
       </c>
       <c r="H72" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="I72" s="33" t="s">
         <v>320</v>
       </c>
-      <c r="I72" s="33" t="s">
+      <c r="J72" s="26" t="s">
         <v>321</v>
-      </c>
-      <c r="J72" s="26" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="73" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14572,10 +14603,10 @@
         <v>40012</v>
       </c>
       <c r="D73" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="E73" s="32" t="s">
         <v>85</v>
-      </c>
-      <c r="E73" s="32" t="s">
-        <v>86</v>
       </c>
       <c r="F73" s="14">
         <v>40012</v>
@@ -14584,13 +14615,13 @@
         <v>22</v>
       </c>
       <c r="H73" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="I73" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="I73" s="33" t="s">
+      <c r="J73" s="26" t="s">
         <v>324</v>
-      </c>
-      <c r="J73" s="26" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="74" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14598,10 +14629,10 @@
         <v>40013</v>
       </c>
       <c r="D74" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="E74" s="35" t="s">
         <v>326</v>
-      </c>
-      <c r="E74" s="35" t="s">
-        <v>327</v>
       </c>
       <c r="F74" s="34">
         <v>40013</v>
@@ -14610,13 +14641,13 @@
         <v>22</v>
       </c>
       <c r="H74" s="36" t="s">
+        <v>327</v>
+      </c>
+      <c r="I74" s="36" t="s">
         <v>328</v>
       </c>
-      <c r="I74" s="36" t="s">
+      <c r="J74" s="41" t="s">
         <v>329</v>
-      </c>
-      <c r="J74" s="41" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="75" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14624,10 +14655,10 @@
         <v>40021</v>
       </c>
       <c r="D75" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="E75" s="32" t="s">
         <v>331</v>
-      </c>
-      <c r="E75" s="32" t="s">
-        <v>332</v>
       </c>
       <c r="F75" s="14">
         <v>40021</v>
@@ -14636,13 +14667,13 @@
         <v>28</v>
       </c>
       <c r="H75" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="I75" s="33" t="s">
         <v>333</v>
       </c>
-      <c r="I75" s="33" t="s">
+      <c r="J75" s="26" t="s">
         <v>334</v>
-      </c>
-      <c r="J75" s="26" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="76" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14650,10 +14681,10 @@
         <v>40022</v>
       </c>
       <c r="D76" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="E76" s="32" t="s">
         <v>85</v>
-      </c>
-      <c r="E76" s="32" t="s">
-        <v>86</v>
       </c>
       <c r="F76" s="14">
         <v>40022</v>
@@ -14662,13 +14693,13 @@
         <v>28</v>
       </c>
       <c r="H76" s="33" t="s">
+        <v>335</v>
+      </c>
+      <c r="I76" s="33" t="s">
         <v>336</v>
       </c>
-      <c r="I76" s="33" t="s">
+      <c r="J76" s="25" t="s">
         <v>337</v>
-      </c>
-      <c r="J76" s="25" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="77" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14676,10 +14707,10 @@
         <v>40023</v>
       </c>
       <c r="D77" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E77" s="35" t="s">
         <v>25</v>
-      </c>
-      <c r="E77" s="35" t="s">
-        <v>26</v>
       </c>
       <c r="F77" s="34">
         <v>40023</v>
@@ -14688,13 +14719,13 @@
         <v>28</v>
       </c>
       <c r="H77" s="36" t="s">
+        <v>338</v>
+      </c>
+      <c r="I77" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="I77" s="36" t="s">
-        <v>340</v>
-      </c>
       <c r="J77" s="25" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="78" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14702,10 +14733,10 @@
         <v>40031</v>
       </c>
       <c r="D78" s="37" t="s">
+        <v>340</v>
+      </c>
+      <c r="E78" s="37" t="s">
         <v>341</v>
-      </c>
-      <c r="E78" s="37" t="s">
-        <v>342</v>
       </c>
       <c r="F78" s="34">
         <v>40031</v>
@@ -14714,13 +14745,13 @@
         <v>32</v>
       </c>
       <c r="H78" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="I78" s="38" t="s">
         <v>343</v>
       </c>
-      <c r="I78" s="38" t="s">
+      <c r="J78" s="39" t="s">
         <v>344</v>
-      </c>
-      <c r="J78" s="39" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="79" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14728,10 +14759,10 @@
         <v>40032</v>
       </c>
       <c r="D79" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E79" s="37" t="s">
         <v>85</v>
-      </c>
-      <c r="E79" s="37" t="s">
-        <v>86</v>
       </c>
       <c r="F79" s="34">
         <v>40032</v>
@@ -14740,13 +14771,13 @@
         <v>32</v>
       </c>
       <c r="H79" s="38" t="s">
+        <v>345</v>
+      </c>
+      <c r="I79" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="I79" s="38" t="s">
+      <c r="J79" s="25" t="s">
         <v>347</v>
-      </c>
-      <c r="J79" s="25" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="80" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14754,10 +14785,10 @@
         <v>40033</v>
       </c>
       <c r="D80" s="35" t="s">
+        <v>348</v>
+      </c>
+      <c r="E80" s="35" t="s">
         <v>349</v>
-      </c>
-      <c r="E80" s="35" t="s">
-        <v>350</v>
       </c>
       <c r="F80" s="34">
         <v>40033</v>
@@ -14766,13 +14797,13 @@
         <v>32</v>
       </c>
       <c r="H80" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="I80" s="36" t="s">
         <v>231</v>
       </c>
-      <c r="I80" s="36" t="s">
-        <v>232</v>
-      </c>
       <c r="J80" s="25" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14780,10 +14811,10 @@
         <v>40041</v>
       </c>
       <c r="D81" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E81" s="37" t="s">
         <v>85</v>
-      </c>
-      <c r="E81" s="37" t="s">
-        <v>86</v>
       </c>
       <c r="F81" s="34">
         <v>40041</v>
@@ -14792,13 +14823,13 @@
         <v>38</v>
       </c>
       <c r="H81" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="I81" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="I81" s="38" t="s">
+      <c r="J81" s="25" t="s">
         <v>353</v>
-      </c>
-      <c r="J81" s="25" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="82" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14806,10 +14837,10 @@
         <v>40042</v>
       </c>
       <c r="D82" s="37" t="s">
+        <v>354</v>
+      </c>
+      <c r="E82" s="37" t="s">
         <v>355</v>
-      </c>
-      <c r="E82" s="37" t="s">
-        <v>356</v>
       </c>
       <c r="F82" s="34">
         <v>40042</v>
@@ -14818,13 +14849,13 @@
         <v>38</v>
       </c>
       <c r="H82" s="38" t="s">
+        <v>356</v>
+      </c>
+      <c r="I82" s="38" t="s">
         <v>357</v>
       </c>
-      <c r="I82" s="38" t="s">
+      <c r="J82" s="39" t="s">
         <v>358</v>
-      </c>
-      <c r="J82" s="39" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="83" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14832,10 +14863,10 @@
         <v>40043</v>
       </c>
       <c r="D83" s="35" t="s">
+        <v>359</v>
+      </c>
+      <c r="E83" s="35" t="s">
         <v>360</v>
-      </c>
-      <c r="E83" s="35" t="s">
-        <v>361</v>
       </c>
       <c r="F83" s="34">
         <v>40043</v>
@@ -14844,13 +14875,13 @@
         <v>38</v>
       </c>
       <c r="H83" s="36" t="s">
+        <v>361</v>
+      </c>
+      <c r="I83" s="36" t="s">
         <v>362</v>
       </c>
-      <c r="I83" s="36" t="s">
+      <c r="J83" s="25" t="s">
         <v>363</v>
-      </c>
-      <c r="J83" s="25" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="84" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14858,10 +14889,10 @@
         <v>40051</v>
       </c>
       <c r="D84" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E84" s="37" t="s">
         <v>252</v>
-      </c>
-      <c r="E84" s="37" t="s">
-        <v>253</v>
       </c>
       <c r="F84" s="34">
         <v>40051</v>
@@ -14870,13 +14901,13 @@
         <v>42</v>
       </c>
       <c r="H84" s="38" t="s">
+        <v>364</v>
+      </c>
+      <c r="I84" s="38" t="s">
         <v>365</v>
       </c>
-      <c r="I84" s="38" t="s">
+      <c r="J84" s="39" t="s">
         <v>366</v>
-      </c>
-      <c r="J84" s="39" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="85" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14884,10 +14915,10 @@
         <v>40052</v>
       </c>
       <c r="D85" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E85" s="37" t="s">
         <v>55</v>
-      </c>
-      <c r="E85" s="37" t="s">
-        <v>56</v>
       </c>
       <c r="F85" s="34">
         <v>40052</v>
@@ -14896,13 +14927,13 @@
         <v>42</v>
       </c>
       <c r="H85" s="38" t="s">
+        <v>367</v>
+      </c>
+      <c r="I85" s="38" t="s">
         <v>368</v>
       </c>
-      <c r="I85" s="38" t="s">
+      <c r="J85" s="25" t="s">
         <v>369</v>
-      </c>
-      <c r="J85" s="25" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="86" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14910,10 +14941,10 @@
         <v>40053</v>
       </c>
       <c r="D86" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="E86" s="35" t="s">
         <v>113</v>
-      </c>
-      <c r="E86" s="35" t="s">
-        <v>114</v>
       </c>
       <c r="F86" s="34">
         <v>40053</v>
@@ -14922,13 +14953,13 @@
         <v>42</v>
       </c>
       <c r="H86" s="36" t="s">
+        <v>370</v>
+      </c>
+      <c r="I86" s="36" t="s">
         <v>371</v>
       </c>
-      <c r="I86" s="36" t="s">
+      <c r="J86" s="27" t="s">
         <v>372</v>
-      </c>
-      <c r="J86" s="27" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="87" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14936,10 +14967,10 @@
         <v>40061</v>
       </c>
       <c r="D87" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="E87" s="37" t="s">
         <v>374</v>
-      </c>
-      <c r="E87" s="37" t="s">
-        <v>375</v>
       </c>
       <c r="F87" s="34">
         <v>40061</v>
@@ -14948,13 +14979,13 @@
         <v>52</v>
       </c>
       <c r="H87" s="38" t="s">
+        <v>375</v>
+      </c>
+      <c r="I87" s="38" t="s">
         <v>376</v>
       </c>
-      <c r="I87" s="38" t="s">
+      <c r="J87" s="39" t="s">
         <v>377</v>
-      </c>
-      <c r="J87" s="39" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="88" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14962,10 +14993,10 @@
         <v>40062</v>
       </c>
       <c r="D88" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="E88" s="37" t="s">
         <v>379</v>
-      </c>
-      <c r="E88" s="37" t="s">
-        <v>380</v>
       </c>
       <c r="F88" s="34">
         <v>40062</v>
@@ -14974,13 +15005,13 @@
         <v>52</v>
       </c>
       <c r="H88" s="38" t="s">
+        <v>380</v>
+      </c>
+      <c r="I88" s="38" t="s">
         <v>381</v>
       </c>
-      <c r="I88" s="38" t="s">
+      <c r="J88" s="26" t="s">
         <v>382</v>
-      </c>
-      <c r="J88" s="26" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="89" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14988,10 +15019,10 @@
         <v>40063</v>
       </c>
       <c r="D89" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="E89" s="35" t="s">
         <v>384</v>
-      </c>
-      <c r="E89" s="35" t="s">
-        <v>385</v>
       </c>
       <c r="F89" s="34">
         <v>40063</v>
@@ -15000,13 +15031,13 @@
         <v>52</v>
       </c>
       <c r="H89" s="36" t="s">
+        <v>385</v>
+      </c>
+      <c r="I89" s="36" t="s">
         <v>386</v>
       </c>
-      <c r="I89" s="36" t="s">
+      <c r="J89" s="27" t="s">
         <v>387</v>
-      </c>
-      <c r="J89" s="27" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="90" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15014,10 +15045,10 @@
         <v>50001</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F90" s="14">
         <v>50001</v>
@@ -15026,13 +15057,13 @@
         <v>15</v>
       </c>
       <c r="H90" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="I90" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J90" s="27" t="s">
         <v>389</v>
-      </c>
-      <c r="I90" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J90" s="27" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="91" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15040,10 +15071,10 @@
         <v>50002</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F91" s="14">
         <v>50002</v>
@@ -15052,13 +15083,13 @@
         <v>15</v>
       </c>
       <c r="H91" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="I91" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J91" s="27" t="s">
         <v>392</v>
-      </c>
-      <c r="I91" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="J91" s="27" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="92" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15066,10 +15097,10 @@
         <v>50003</v>
       </c>
       <c r="D92" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="E92" s="14" t="s">
         <v>313</v>
-      </c>
-      <c r="E92" s="14" t="s">
-        <v>314</v>
       </c>
       <c r="F92" s="14">
         <v>50003</v>
@@ -15078,13 +15109,13 @@
         <v>15</v>
       </c>
       <c r="H92" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="I92" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="I92" s="13" t="s">
-        <v>316</v>
-      </c>
       <c r="J92" s="44" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="93" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15092,10 +15123,10 @@
         <v>50011</v>
       </c>
       <c r="D93" s="43" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F93" s="14">
         <v>50011</v>
@@ -15104,13 +15135,13 @@
         <v>22</v>
       </c>
       <c r="H93" s="42" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J93" s="27" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="94" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15118,10 +15149,10 @@
         <v>50012</v>
       </c>
       <c r="D94" s="43" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F94" s="14">
         <v>50012</v>
@@ -15130,13 +15161,13 @@
         <v>22</v>
       </c>
       <c r="H94" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="I94" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="J94" s="27" t="s">
         <v>395</v>
-      </c>
-      <c r="I94" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="J94" s="27" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="95" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15144,10 +15175,10 @@
         <v>50013</v>
       </c>
       <c r="D95" s="43" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E95" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F95" s="14">
         <v>50013</v>
@@ -15156,13 +15187,13 @@
         <v>22</v>
       </c>
       <c r="H95" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="I95" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="J95" s="27" t="s">
         <v>397</v>
-      </c>
-      <c r="I95" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="J95" s="27" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="96" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15170,10 +15201,10 @@
         <v>50021</v>
       </c>
       <c r="D96" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E96" s="14" t="s">
         <v>55</v>
-      </c>
-      <c r="E96" s="14" t="s">
-        <v>56</v>
       </c>
       <c r="F96" s="14">
         <v>50021</v>
@@ -15182,13 +15213,13 @@
         <v>28</v>
       </c>
       <c r="H96" s="42" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J96" s="27" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="97" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15196,10 +15227,10 @@
         <v>50022</v>
       </c>
       <c r="D97" s="43" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F97" s="14">
         <v>50022</v>
@@ -15208,13 +15239,13 @@
         <v>28</v>
       </c>
       <c r="H97" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="I97" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="J97" s="27" t="s">
         <v>400</v>
-      </c>
-      <c r="I97" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="J97" s="27" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="98" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15222,10 +15253,10 @@
         <v>50023</v>
       </c>
       <c r="D98" s="43" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F98" s="14">
         <v>50023</v>
@@ -15234,13 +15265,13 @@
         <v>28</v>
       </c>
       <c r="H98" s="42" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="I98" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J98" s="27" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="99" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15248,10 +15279,10 @@
         <v>50031</v>
       </c>
       <c r="D99" s="43" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F99" s="14">
         <v>50031</v>
@@ -15260,13 +15291,13 @@
         <v>32</v>
       </c>
       <c r="H99" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="I99" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="J99" s="27" t="s">
         <v>403</v>
-      </c>
-      <c r="I99" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="J99" s="27" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="100" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15274,10 +15305,10 @@
         <v>50032</v>
       </c>
       <c r="D100" s="43" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F100" s="14">
         <v>50032</v>
@@ -15286,13 +15317,13 @@
         <v>32</v>
       </c>
       <c r="H100" s="42" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J100" s="44" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="101" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15300,10 +15331,10 @@
         <v>50033</v>
       </c>
       <c r="D101" s="43" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F101" s="14">
         <v>50033</v>
@@ -15312,13 +15343,13 @@
         <v>32</v>
       </c>
       <c r="H101" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="I101" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="I101" s="13" t="s">
-        <v>164</v>
-      </c>
       <c r="J101" s="27" t="s">
-        <v>165</v>
+        <v>487</v>
       </c>
     </row>
     <row r="102" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15326,10 +15357,10 @@
         <v>50041</v>
       </c>
       <c r="D102" s="43" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F102" s="14">
         <v>50041</v>
@@ -15338,13 +15369,13 @@
         <v>38</v>
       </c>
       <c r="H102" s="13" t="s">
-        <v>405</v>
+        <v>485</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J102" s="27" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="103" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15352,10 +15383,10 @@
         <v>50042</v>
       </c>
       <c r="D103" s="43" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E103" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F103" s="14">
         <v>50042</v>
@@ -15364,13 +15395,13 @@
         <v>38</v>
       </c>
       <c r="H103" s="13" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J103" s="27" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="104" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15378,10 +15409,10 @@
         <v>50043</v>
       </c>
       <c r="D104" s="43" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F104" s="14">
         <v>50043</v>
@@ -15390,13 +15421,13 @@
         <v>38</v>
       </c>
       <c r="H104" s="13" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J104" s="27" t="s">
-        <v>410</v>
+        <v>486</v>
       </c>
     </row>
     <row r="105" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15404,10 +15435,10 @@
         <v>50051</v>
       </c>
       <c r="D105" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E105" s="14" t="s">
         <v>55</v>
-      </c>
-      <c r="E105" s="14" t="s">
-        <v>56</v>
       </c>
       <c r="F105" s="14">
         <v>50051</v>
@@ -15416,13 +15447,13 @@
         <v>42</v>
       </c>
       <c r="H105" s="13" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J105" s="27" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="106" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15430,10 +15461,10 @@
         <v>50052</v>
       </c>
       <c r="D106" s="43" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F106" s="14">
         <v>50052</v>
@@ -15442,13 +15473,13 @@
         <v>42</v>
       </c>
       <c r="H106" s="13" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J106" s="27" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="107" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15456,10 +15487,10 @@
         <v>50053</v>
       </c>
       <c r="D107" s="43" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="E107" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F107" s="14">
         <v>50053</v>
@@ -15468,13 +15499,13 @@
         <v>42</v>
       </c>
       <c r="H107" s="42" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="I107" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J107" s="44" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="108" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15482,10 +15513,10 @@
         <v>50061</v>
       </c>
       <c r="D108" s="43" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F108" s="14">
         <v>50061</v>
@@ -15494,13 +15525,13 @@
         <v>52</v>
       </c>
       <c r="H108" s="13" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="I108" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J108" s="44" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="109" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15508,10 +15539,10 @@
         <v>50062</v>
       </c>
       <c r="D109" s="43" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E109" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F109" s="14">
         <v>50062</v>
@@ -15520,13 +15551,13 @@
         <v>52</v>
       </c>
       <c r="H109" s="13" t="s">
-        <v>416</v>
+        <v>489</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="J109" s="44" t="s">
-        <v>486</v>
+        <v>171</v>
+      </c>
+      <c r="J109" s="27" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="110" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15534,10 +15565,10 @@
         <v>50063</v>
       </c>
       <c r="D110" s="43" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F110" s="14">
         <v>50063</v>
@@ -15546,13 +15577,13 @@
         <v>52</v>
       </c>
       <c r="H110" s="42" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="I110" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J110" s="27" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="111" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15560,10 +15591,10 @@
         <v>90001</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F111" s="11">
         <v>60010100</v>
@@ -15572,13 +15603,13 @@
         <v>1</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="J111" s="25" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="112" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15586,10 +15617,10 @@
         <v>90002</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F112" s="11">
         <v>60010200</v>
@@ -15598,13 +15629,13 @@
         <v>1</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="J112" s="25" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="113" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15612,10 +15643,10 @@
         <v>90003</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="F113" s="11">
         <v>60010300</v>
@@ -15624,13 +15655,13 @@
         <v>1</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="J113" s="25" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="114" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15638,10 +15669,10 @@
         <v>90004</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F114" s="11">
         <v>60010400</v>
@@ -15650,13 +15681,13 @@
         <v>2</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="J114" s="25" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="115" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15664,10 +15695,10 @@
         <v>90005</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="F115" s="11">
         <v>60010500</v>
@@ -15676,13 +15707,13 @@
         <v>2</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="J115" s="25" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="116" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15690,10 +15721,10 @@
         <v>90006</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F116" s="11">
         <v>60010600</v>
@@ -15702,13 +15733,13 @@
         <v>2</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="J116" s="25" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="117" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15722,7 +15753,7 @@
         <v>1</v>
       </c>
       <c r="J117" s="40" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="118" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15736,7 +15767,7 @@
         <v>1</v>
       </c>
       <c r="J118" s="40" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="119" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15750,7 +15781,7 @@
         <v>1</v>
       </c>
       <c r="J119" s="40" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="120" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15764,7 +15795,7 @@
         <v>1</v>
       </c>
       <c r="J120" s="40" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="121" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15778,7 +15809,7 @@
         <v>1</v>
       </c>
       <c r="J121" s="40" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="122" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15792,7 +15823,7 @@
         <v>1</v>
       </c>
       <c r="J122" s="40" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="123" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15806,7 +15837,7 @@
         <v>1</v>
       </c>
       <c r="J123" s="40" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="124" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15820,7 +15851,7 @@
         <v>1</v>
       </c>
       <c r="J124" s="40" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="125" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15834,7 +15865,7 @@
         <v>1</v>
       </c>
       <c r="J125" s="40" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="126" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15848,7 +15879,7 @@
         <v>1</v>
       </c>
       <c r="J126" s="40" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="127" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15862,7 +15893,7 @@
         <v>1</v>
       </c>
       <c r="J127" s="40" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="Q127" s="11"/>
     </row>
@@ -15877,7 +15908,7 @@
         <v>1</v>
       </c>
       <c r="J128" s="40" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="Q128" s="11"/>
     </row>
@@ -15892,7 +15923,7 @@
         <v>1</v>
       </c>
       <c r="J129" s="40" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="Q129" s="11"/>
     </row>
@@ -15907,7 +15938,7 @@
         <v>1</v>
       </c>
       <c r="J130" s="40" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="Q130" s="11"/>
     </row>
@@ -15922,7 +15953,7 @@
         <v>1</v>
       </c>
       <c r="J131" s="40" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="Q131" s="11"/>
     </row>
@@ -15937,7 +15968,7 @@
         <v>1</v>
       </c>
       <c r="J132" s="40" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="Q132" s="11"/>
     </row>
@@ -15952,7 +15983,7 @@
         <v>1</v>
       </c>
       <c r="J133" s="40" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="Q133" s="11"/>
     </row>
@@ -15967,7 +15998,7 @@
         <v>1</v>
       </c>
       <c r="J134" s="40" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="Q134" s="11"/>
     </row>
@@ -15982,7 +16013,7 @@
         <v>1</v>
       </c>
       <c r="J135" s="40" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="Q135" s="11"/>
     </row>
@@ -15997,7 +16028,7 @@
         <v>1</v>
       </c>
       <c r="J136" s="40" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="Q136" s="11"/>
     </row>
@@ -16012,7 +16043,7 @@
         <v>1</v>
       </c>
       <c r="J137" s="40" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="Q137" s="11"/>
     </row>
@@ -16027,7 +16058,7 @@
         <v>1</v>
       </c>
       <c r="J138" s="40" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="Q138" s="11"/>
     </row>
@@ -16042,7 +16073,7 @@
         <v>1</v>
       </c>
       <c r="J139" s="40" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="Q139" s="11"/>
     </row>
@@ -16057,7 +16088,7 @@
         <v>1</v>
       </c>
       <c r="J140" s="40" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="Q140" s="11"/>
     </row>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D787C7-B503-48D0-9DA0-BE45620247EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C77EDC-0990-440C-B2FD-A507EF625966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1579,7 +1579,7 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>当生命值降低至50%后,受到闪避提升40%,自身伤害提升50%,持续3秒，30秒内只能触发一次</t>
+    <t>当生命值降低至50%后,闪避提升40%,自身伤害提升50%,持续3秒，30秒内只能触发一次</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C77EDC-0990-440C-B2FD-A507EF625966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCCB6B9-98A5-48B5-B1FB-0E8F61E4DBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TalentProto" sheetId="1" r:id="rId1"/>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DA9FA4-FF52-4AC9-B9F8-93CB31A0FA36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87196AFC-BA51-431F-8DBD-FFFC4A8A6D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -434,9 +434,6 @@
     <t>Slow Spell</t>
   </si>
   <si>
-    <t>BuffIdAdd;60000301,60000302,60000401,60000402;90000301</t>
-  </si>
-  <si>
     <t>龙卷增强</t>
   </si>
   <si>
@@ -1561,6 +1558,10 @@
   </si>
   <si>
     <t>Basic attacks apply 30% slow for 3s, Permanently increases your auto-attack damage by 10%.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffIdAdd;60000301,60000302,60000401,60000402;90000301@SkillIdAdd;62000121</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -12895,7 +12896,7 @@
         <v>10011</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>30</v>
@@ -12907,13 +12908,13 @@
         <v>22</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I9" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="J9" s="24" t="s">
         <v>477</v>
-      </c>
-      <c r="J9" s="24" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="10" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13401,10 +13402,10 @@
         <v>15</v>
       </c>
       <c r="H28" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="I28" s="12" t="s">
         <v>485</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>486</v>
       </c>
       <c r="J28" s="24" t="s">
         <v>121</v>
@@ -13427,13 +13428,13 @@
         <v>15</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I29" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="J29" s="25" t="s">
         <v>487</v>
-      </c>
-      <c r="J29" s="25" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="30" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13441,10 +13442,10 @@
         <v>20011</v>
       </c>
       <c r="D30" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>125</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>126</v>
       </c>
       <c r="F30" s="11">
         <v>20011</v>
@@ -13453,13 +13454,13 @@
         <v>22</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J30" s="24" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="31" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13467,10 +13468,10 @@
         <v>20012</v>
       </c>
       <c r="D31" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>127</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>128</v>
       </c>
       <c r="F31" s="11">
         <v>20012</v>
@@ -13479,13 +13480,13 @@
         <v>22</v>
       </c>
       <c r="H31" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="I31" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="J31" s="25" t="s">
         <v>130</v>
-      </c>
-      <c r="J31" s="25" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="32" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13493,10 +13494,10 @@
         <v>20013</v>
       </c>
       <c r="D32" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="F32" s="11">
         <v>20013</v>
@@ -13505,13 +13506,13 @@
         <v>22</v>
       </c>
       <c r="H32" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="J32" s="25" t="s">
         <v>135</v>
-      </c>
-      <c r="J32" s="25" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="33" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13519,10 +13520,10 @@
         <v>20021</v>
       </c>
       <c r="D33" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E33" s="11" t="s">
         <v>137</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>138</v>
       </c>
       <c r="F33" s="11">
         <v>20021</v>
@@ -13531,13 +13532,13 @@
         <v>28</v>
       </c>
       <c r="H33" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="I33" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="I33" s="12" t="s">
+      <c r="J33" s="25" t="s">
         <v>140</v>
-      </c>
-      <c r="J33" s="25" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="34" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13557,13 +13558,13 @@
         <v>28</v>
       </c>
       <c r="H34" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="I34" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I34" s="12" t="s">
+      <c r="J34" s="25" t="s">
         <v>143</v>
-      </c>
-      <c r="J34" s="25" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="35" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13571,10 +13572,10 @@
         <v>20023</v>
       </c>
       <c r="D35" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="E35" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>146</v>
       </c>
       <c r="F35" s="11">
         <v>20023</v>
@@ -13583,13 +13584,13 @@
         <v>28</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J35" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13597,10 +13598,10 @@
         <v>20031</v>
       </c>
       <c r="D36" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E36" s="11" t="s">
         <v>148</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>149</v>
       </c>
       <c r="F36" s="11">
         <v>20031</v>
@@ -13609,13 +13610,13 @@
         <v>32</v>
       </c>
       <c r="H36" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="I36" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="I36" s="12" t="s">
+      <c r="J36" s="25" t="s">
         <v>151</v>
-      </c>
-      <c r="J36" s="25" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="37" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13635,13 +13636,13 @@
         <v>32</v>
       </c>
       <c r="H37" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="I37" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="I37" s="12" t="s">
+      <c r="J37" s="24" t="s">
         <v>154</v>
-      </c>
-      <c r="J37" s="24" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="38" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13649,10 +13650,10 @@
         <v>20033</v>
       </c>
       <c r="D38" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E38" s="11" t="s">
         <v>156</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>157</v>
       </c>
       <c r="F38" s="11">
         <v>20033</v>
@@ -13661,13 +13662,13 @@
         <v>32</v>
       </c>
       <c r="H38" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="I38" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="I38" s="12" t="s">
+      <c r="J38" s="25" t="s">
         <v>159</v>
-      </c>
-      <c r="J38" s="25" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="39" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13675,10 +13676,10 @@
         <v>20041</v>
       </c>
       <c r="D39" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>161</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>162</v>
       </c>
       <c r="F39" s="11">
         <v>20041</v>
@@ -13687,13 +13688,13 @@
         <v>38</v>
       </c>
       <c r="H39" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I39" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="I39" s="12" t="s">
+      <c r="J39" s="24" t="s">
         <v>164</v>
-      </c>
-      <c r="J39" s="24" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="40" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13713,13 +13714,13 @@
         <v>38</v>
       </c>
       <c r="H40" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="I40" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="I40" s="12" t="s">
+      <c r="J40" s="25" t="s">
         <v>167</v>
-      </c>
-      <c r="J40" s="25" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="41" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13727,10 +13728,10 @@
         <v>20043</v>
       </c>
       <c r="D41" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E41" s="11" t="s">
         <v>169</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>170</v>
       </c>
       <c r="F41" s="11">
         <v>20043</v>
@@ -13739,13 +13740,13 @@
         <v>38</v>
       </c>
       <c r="H41" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="I41" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="I41" s="12" t="s">
+      <c r="J41" s="25" t="s">
         <v>172</v>
-      </c>
-      <c r="J41" s="25" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="42" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13753,10 +13754,10 @@
         <v>20051</v>
       </c>
       <c r="D42" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" s="11" t="s">
         <v>174</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>175</v>
       </c>
       <c r="F42" s="11">
         <v>20051</v>
@@ -13765,13 +13766,13 @@
         <v>42</v>
       </c>
       <c r="H42" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="I42" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="I42" s="12" t="s">
+      <c r="J42" s="24" t="s">
         <v>177</v>
-      </c>
-      <c r="J42" s="24" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="43" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13791,13 +13792,13 @@
         <v>42</v>
       </c>
       <c r="H43" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="I43" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="J43" s="24" t="s">
         <v>180</v>
-      </c>
-      <c r="J43" s="24" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="44" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13805,10 +13806,10 @@
         <v>20053</v>
       </c>
       <c r="D44" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E44" s="11" t="s">
         <v>182</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>183</v>
       </c>
       <c r="F44" s="11">
         <v>20053</v>
@@ -13817,13 +13818,13 @@
         <v>42</v>
       </c>
       <c r="H44" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="I44" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="I44" s="12" t="s">
+      <c r="J44" s="24" t="s">
         <v>185</v>
-      </c>
-      <c r="J44" s="24" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="45" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13843,13 +13844,13 @@
         <v>52</v>
       </c>
       <c r="H45" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I45" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="I45" s="13" t="s">
+      <c r="J45" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="46" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13857,10 +13858,10 @@
         <v>20062</v>
       </c>
       <c r="D46" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="E46" s="15" t="s">
         <v>190</v>
-      </c>
-      <c r="E46" s="15" t="s">
-        <v>191</v>
       </c>
       <c r="F46" s="11">
         <v>20062</v>
@@ -13869,13 +13870,13 @@
         <v>52</v>
       </c>
       <c r="H46" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="I46" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="I46" s="13" t="s">
+      <c r="J46" s="27" t="s">
         <v>193</v>
-      </c>
-      <c r="J46" s="27" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="47" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13883,10 +13884,10 @@
         <v>20063</v>
       </c>
       <c r="D47" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="E47" s="15" t="s">
         <v>195</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>196</v>
       </c>
       <c r="F47" s="11">
         <v>20063</v>
@@ -13895,13 +13896,13 @@
         <v>52</v>
       </c>
       <c r="H47" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="I47" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="I47" s="13" t="s">
+      <c r="J47" s="26" t="s">
         <v>198</v>
-      </c>
-      <c r="J47" s="26" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="48" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13921,13 +13922,13 @@
         <v>15</v>
       </c>
       <c r="H48" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="I48" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="I48" s="17" t="s">
+      <c r="J48" s="26" t="s">
         <v>201</v>
-      </c>
-      <c r="J48" s="26" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="49" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13935,10 +13936,10 @@
         <v>30002</v>
       </c>
       <c r="D49" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" s="16" t="s">
         <v>203</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>204</v>
       </c>
       <c r="F49" s="11">
         <v>30002</v>
@@ -13947,13 +13948,13 @@
         <v>15</v>
       </c>
       <c r="H49" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="I49" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="I49" s="17" t="s">
+      <c r="J49" s="26" t="s">
         <v>206</v>
-      </c>
-      <c r="J49" s="26" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="50" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13973,13 +13974,13 @@
         <v>15</v>
       </c>
       <c r="H50" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="I50" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="I50" s="12" t="s">
+      <c r="J50" s="25" t="s">
         <v>209</v>
-      </c>
-      <c r="J50" s="25" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="51" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13987,10 +13988,10 @@
         <v>30011</v>
       </c>
       <c r="D51" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="E51" s="16" t="s">
         <v>211</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>212</v>
       </c>
       <c r="F51" s="11">
         <v>30011</v>
@@ -13999,13 +14000,13 @@
         <v>22</v>
       </c>
       <c r="H51" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="I51" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="I51" s="17" t="s">
+      <c r="J51" s="26" t="s">
         <v>214</v>
-      </c>
-      <c r="J51" s="26" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="52" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14013,10 +14014,10 @@
         <v>30012</v>
       </c>
       <c r="D52" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E52" s="19" t="s">
         <v>216</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>217</v>
       </c>
       <c r="F52" s="11">
         <v>30012</v>
@@ -14025,13 +14026,13 @@
         <v>22</v>
       </c>
       <c r="H52" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="I52" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="I52" s="20" t="s">
+      <c r="J52" s="25" t="s">
         <v>219</v>
-      </c>
-      <c r="J52" s="25" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="53" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14039,10 +14040,10 @@
         <v>30013</v>
       </c>
       <c r="D53" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="E53" s="18" t="s">
         <v>221</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>222</v>
       </c>
       <c r="F53" s="11">
         <v>30013</v>
@@ -14051,13 +14052,13 @@
         <v>22</v>
       </c>
       <c r="H53" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="I53" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="I53" s="12" t="s">
+      <c r="J53" s="25" t="s">
         <v>224</v>
-      </c>
-      <c r="J53" s="25" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="54" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14065,10 +14066,10 @@
         <v>30021</v>
       </c>
       <c r="D54" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="E54" s="18" t="s">
         <v>226</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>227</v>
       </c>
       <c r="F54" s="11">
         <v>30021</v>
@@ -14077,13 +14078,13 @@
         <v>28</v>
       </c>
       <c r="H54" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="I54" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="I54" s="12" t="s">
+      <c r="J54" s="25" t="s">
         <v>229</v>
-      </c>
-      <c r="J54" s="25" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="55" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14091,10 +14092,10 @@
         <v>30022</v>
       </c>
       <c r="D55" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="E55" s="18" t="s">
         <v>231</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>232</v>
       </c>
       <c r="F55" s="11">
         <v>30022</v>
@@ -14103,13 +14104,13 @@
         <v>28</v>
       </c>
       <c r="H55" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="I55" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="I55" s="12" t="s">
+      <c r="J55" s="26" t="s">
         <v>234</v>
-      </c>
-      <c r="J55" s="26" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="56" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14129,13 +14130,13 @@
         <v>28</v>
       </c>
       <c r="H56" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="I56" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="I56" s="12" t="s">
+      <c r="J56" s="25" t="s">
         <v>237</v>
-      </c>
-      <c r="J56" s="25" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="57" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14143,10 +14144,10 @@
         <v>30031</v>
       </c>
       <c r="D57" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="E57" s="18" t="s">
         <v>239</v>
-      </c>
-      <c r="E57" s="18" t="s">
-        <v>240</v>
       </c>
       <c r="F57" s="11">
         <v>30031</v>
@@ -14155,13 +14156,13 @@
         <v>32</v>
       </c>
       <c r="H57" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="I57" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="I57" s="12" t="s">
+      <c r="J57" s="26" t="s">
         <v>242</v>
-      </c>
-      <c r="J57" s="26" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="58" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14169,10 +14170,10 @@
         <v>30032</v>
       </c>
       <c r="D58" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="E58" s="21" t="s">
         <v>244</v>
-      </c>
-      <c r="E58" s="21" t="s">
-        <v>245</v>
       </c>
       <c r="F58" s="11">
         <v>30032</v>
@@ -14181,13 +14182,13 @@
         <v>32</v>
       </c>
       <c r="H58" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="I58" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="I58" s="22" t="s">
+      <c r="J58" s="26" t="s">
         <v>247</v>
-      </c>
-      <c r="J58" s="26" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="59" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14207,13 +14208,13 @@
         <v>32</v>
       </c>
       <c r="H59" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="I59" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="I59" s="12" t="s">
+      <c r="J59" s="25" t="s">
         <v>250</v>
-      </c>
-      <c r="J59" s="25" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="60" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14221,10 +14222,10 @@
         <v>30041</v>
       </c>
       <c r="D60" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="E60" s="18" t="s">
         <v>252</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>253</v>
       </c>
       <c r="F60" s="11">
         <v>30041</v>
@@ -14233,13 +14234,13 @@
         <v>38</v>
       </c>
       <c r="H60" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="I60" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="I60" s="12" t="s">
+      <c r="J60" s="25" t="s">
         <v>255</v>
-      </c>
-      <c r="J60" s="25" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="61" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14247,10 +14248,10 @@
         <v>30042</v>
       </c>
       <c r="D61" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="E61" s="16" t="s">
         <v>257</v>
-      </c>
-      <c r="E61" s="16" t="s">
-        <v>258</v>
       </c>
       <c r="F61" s="11">
         <v>30042</v>
@@ -14259,10 +14260,10 @@
         <v>38</v>
       </c>
       <c r="H61" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="I61" s="12" t="s">
         <v>259</v>
-      </c>
-      <c r="I61" s="12" t="s">
-        <v>260</v>
       </c>
       <c r="J61" s="24" t="s">
         <v>60</v>
@@ -14285,13 +14286,13 @@
         <v>38</v>
       </c>
       <c r="H62" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="I62" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="I62" s="12" t="s">
+      <c r="J62" s="25" t="s">
         <v>262</v>
-      </c>
-      <c r="J62" s="25" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="63" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14299,10 +14300,10 @@
         <v>30051</v>
       </c>
       <c r="D63" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="E63" s="18" t="s">
         <v>264</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>265</v>
       </c>
       <c r="F63" s="11">
         <v>30051</v>
@@ -14311,13 +14312,13 @@
         <v>42</v>
       </c>
       <c r="H63" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="I63" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="I63" s="12" t="s">
+      <c r="J63" s="25" t="s">
         <v>267</v>
-      </c>
-      <c r="J63" s="25" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="64" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14325,10 +14326,10 @@
         <v>30052</v>
       </c>
       <c r="D64" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="E64" s="21" t="s">
         <v>269</v>
-      </c>
-      <c r="E64" s="21" t="s">
-        <v>270</v>
       </c>
       <c r="F64" s="11">
         <v>30052</v>
@@ -14337,13 +14338,13 @@
         <v>42</v>
       </c>
       <c r="H64" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="I64" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="I64" s="23" t="s">
+      <c r="J64" s="24" t="s">
         <v>272</v>
-      </c>
-      <c r="J64" s="24" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="65" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14363,13 +14364,13 @@
         <v>42</v>
       </c>
       <c r="H65" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="I65" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="I65" s="12" t="s">
+      <c r="J65" s="25" t="s">
         <v>275</v>
-      </c>
-      <c r="J65" s="25" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="66" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14377,10 +14378,10 @@
         <v>30061</v>
       </c>
       <c r="D66" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="E66" s="15" t="s">
         <v>277</v>
-      </c>
-      <c r="E66" s="15" t="s">
-        <v>278</v>
       </c>
       <c r="F66" s="11">
         <v>30061</v>
@@ -14389,13 +14390,13 @@
         <v>52</v>
       </c>
       <c r="H66" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="I66" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="I66" s="13" t="s">
+      <c r="J66" s="26" t="s">
         <v>280</v>
-      </c>
-      <c r="J66" s="26" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="67" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14403,10 +14404,10 @@
         <v>30062</v>
       </c>
       <c r="D67" s="28" t="s">
+        <v>281</v>
+      </c>
+      <c r="E67" s="28" t="s">
         <v>282</v>
-      </c>
-      <c r="E67" s="28" t="s">
-        <v>283</v>
       </c>
       <c r="F67" s="11">
         <v>30062</v>
@@ -14415,13 +14416,13 @@
         <v>52</v>
       </c>
       <c r="H67" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="I67" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="I67" s="29" t="s">
+      <c r="J67" s="27" t="s">
         <v>285</v>
-      </c>
-      <c r="J67" s="27" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="68" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14429,10 +14430,10 @@
         <v>30063</v>
       </c>
       <c r="D68" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="E68" s="30" t="s">
         <v>287</v>
-      </c>
-      <c r="E68" s="30" t="s">
-        <v>288</v>
       </c>
       <c r="F68" s="11">
         <v>30063</v>
@@ -14441,13 +14442,13 @@
         <v>52</v>
       </c>
       <c r="H68" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="I68" s="31" t="s">
         <v>289</v>
       </c>
-      <c r="I68" s="31" t="s">
+      <c r="J68" s="26" t="s">
         <v>290</v>
-      </c>
-      <c r="J68" s="26" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="69" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14455,10 +14456,10 @@
         <v>40001</v>
       </c>
       <c r="D69" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="E69" s="32" t="s">
         <v>292</v>
-      </c>
-      <c r="E69" s="32" t="s">
-        <v>293</v>
       </c>
       <c r="F69" s="14">
         <v>40001</v>
@@ -14467,13 +14468,13 @@
         <v>15</v>
       </c>
       <c r="H69" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="I69" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="I69" s="33" t="s">
+      <c r="J69" s="26" t="s">
         <v>295</v>
-      </c>
-      <c r="J69" s="26" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="70" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14493,13 +14494,13 @@
         <v>15</v>
       </c>
       <c r="H70" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="I70" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="I70" s="12" t="s">
+      <c r="J70" s="25" t="s">
         <v>298</v>
-      </c>
-      <c r="J70" s="25" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="71" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14507,10 +14508,10 @@
         <v>40003</v>
       </c>
       <c r="D71" s="35" t="s">
+        <v>299</v>
+      </c>
+      <c r="E71" s="35" t="s">
         <v>300</v>
-      </c>
-      <c r="E71" s="35" t="s">
-        <v>301</v>
       </c>
       <c r="F71" s="34">
         <v>40003</v>
@@ -14519,13 +14520,13 @@
         <v>15</v>
       </c>
       <c r="H71" s="36" t="s">
+        <v>301</v>
+      </c>
+      <c r="I71" s="36" t="s">
         <v>302</v>
       </c>
-      <c r="I71" s="36" t="s">
+      <c r="J71" s="26" t="s">
         <v>303</v>
-      </c>
-      <c r="J71" s="26" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="72" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14533,10 +14534,10 @@
         <v>40011</v>
       </c>
       <c r="D72" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="E72" s="32" t="s">
         <v>305</v>
-      </c>
-      <c r="E72" s="32" t="s">
-        <v>306</v>
       </c>
       <c r="F72" s="14">
         <v>40011</v>
@@ -14545,13 +14546,13 @@
         <v>22</v>
       </c>
       <c r="H72" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="I72" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="I72" s="33" t="s">
+      <c r="J72" s="26" t="s">
         <v>308</v>
-      </c>
-      <c r="J72" s="26" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="73" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14571,13 +14572,13 @@
         <v>22</v>
       </c>
       <c r="H73" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="I73" s="33" t="s">
         <v>310</v>
       </c>
-      <c r="I73" s="33" t="s">
+      <c r="J73" s="26" t="s">
         <v>311</v>
-      </c>
-      <c r="J73" s="26" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="74" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14585,10 +14586,10 @@
         <v>40013</v>
       </c>
       <c r="D74" s="35" t="s">
+        <v>312</v>
+      </c>
+      <c r="E74" s="35" t="s">
         <v>313</v>
-      </c>
-      <c r="E74" s="35" t="s">
-        <v>314</v>
       </c>
       <c r="F74" s="34">
         <v>40013</v>
@@ -14597,13 +14598,13 @@
         <v>22</v>
       </c>
       <c r="H74" s="36" t="s">
+        <v>314</v>
+      </c>
+      <c r="I74" s="36" t="s">
         <v>315</v>
       </c>
-      <c r="I74" s="36" t="s">
+      <c r="J74" s="41" t="s">
         <v>316</v>
-      </c>
-      <c r="J74" s="41" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="75" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14611,10 +14612,10 @@
         <v>40021</v>
       </c>
       <c r="D75" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="E75" s="32" t="s">
         <v>318</v>
-      </c>
-      <c r="E75" s="32" t="s">
-        <v>319</v>
       </c>
       <c r="F75" s="14">
         <v>40021</v>
@@ -14623,13 +14624,13 @@
         <v>28</v>
       </c>
       <c r="H75" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="I75" s="33" t="s">
         <v>320</v>
       </c>
-      <c r="I75" s="33" t="s">
+      <c r="J75" s="26" t="s">
         <v>321</v>
-      </c>
-      <c r="J75" s="26" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="76" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14649,13 +14650,13 @@
         <v>28</v>
       </c>
       <c r="H76" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="I76" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="I76" s="33" t="s">
+      <c r="J76" s="25" t="s">
         <v>324</v>
-      </c>
-      <c r="J76" s="25" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="77" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14675,13 +14676,13 @@
         <v>28</v>
       </c>
       <c r="H77" s="36" t="s">
+        <v>325</v>
+      </c>
+      <c r="I77" s="36" t="s">
         <v>326</v>
       </c>
-      <c r="I77" s="36" t="s">
-        <v>327</v>
-      </c>
       <c r="J77" s="25" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="78" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14689,10 +14690,10 @@
         <v>40031</v>
       </c>
       <c r="D78" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="E78" s="37" t="s">
         <v>328</v>
-      </c>
-      <c r="E78" s="37" t="s">
-        <v>329</v>
       </c>
       <c r="F78" s="34">
         <v>40031</v>
@@ -14701,13 +14702,13 @@
         <v>32</v>
       </c>
       <c r="H78" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="I78" s="38" t="s">
         <v>330</v>
       </c>
-      <c r="I78" s="38" t="s">
+      <c r="J78" s="39" t="s">
         <v>331</v>
-      </c>
-      <c r="J78" s="39" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="79" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14727,13 +14728,13 @@
         <v>32</v>
       </c>
       <c r="H79" s="38" t="s">
+        <v>332</v>
+      </c>
+      <c r="I79" s="38" t="s">
         <v>333</v>
       </c>
-      <c r="I79" s="38" t="s">
+      <c r="J79" s="25" t="s">
         <v>334</v>
-      </c>
-      <c r="J79" s="25" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="80" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14741,10 +14742,10 @@
         <v>40033</v>
       </c>
       <c r="D80" s="35" t="s">
+        <v>335</v>
+      </c>
+      <c r="E80" s="35" t="s">
         <v>336</v>
-      </c>
-      <c r="E80" s="35" t="s">
-        <v>337</v>
       </c>
       <c r="F80" s="34">
         <v>40033</v>
@@ -14753,13 +14754,13 @@
         <v>32</v>
       </c>
       <c r="H80" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="I80" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="I80" s="36" t="s">
-        <v>219</v>
-      </c>
       <c r="J80" s="25" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="81" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14779,13 +14780,13 @@
         <v>38</v>
       </c>
       <c r="H81" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="I81" s="38" t="s">
         <v>339</v>
       </c>
-      <c r="I81" s="38" t="s">
+      <c r="J81" s="25" t="s">
         <v>340</v>
-      </c>
-      <c r="J81" s="25" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="82" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14793,10 +14794,10 @@
         <v>40042</v>
       </c>
       <c r="D82" s="37" t="s">
+        <v>341</v>
+      </c>
+      <c r="E82" s="37" t="s">
         <v>342</v>
-      </c>
-      <c r="E82" s="37" t="s">
-        <v>343</v>
       </c>
       <c r="F82" s="34">
         <v>40042</v>
@@ -14805,13 +14806,13 @@
         <v>38</v>
       </c>
       <c r="H82" s="38" t="s">
+        <v>343</v>
+      </c>
+      <c r="I82" s="38" t="s">
         <v>344</v>
       </c>
-      <c r="I82" s="38" t="s">
+      <c r="J82" s="39" t="s">
         <v>345</v>
-      </c>
-      <c r="J82" s="39" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="83" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14819,10 +14820,10 @@
         <v>40043</v>
       </c>
       <c r="D83" s="35" t="s">
+        <v>346</v>
+      </c>
+      <c r="E83" s="35" t="s">
         <v>347</v>
-      </c>
-      <c r="E83" s="35" t="s">
-        <v>348</v>
       </c>
       <c r="F83" s="34">
         <v>40043</v>
@@ -14831,13 +14832,13 @@
         <v>38</v>
       </c>
       <c r="H83" s="36" t="s">
+        <v>348</v>
+      </c>
+      <c r="I83" s="36" t="s">
         <v>349</v>
       </c>
-      <c r="I83" s="36" t="s">
+      <c r="J83" s="25" t="s">
         <v>350</v>
-      </c>
-      <c r="J83" s="25" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="84" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14845,10 +14846,10 @@
         <v>40051</v>
       </c>
       <c r="D84" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="E84" s="37" t="s">
         <v>239</v>
-      </c>
-      <c r="E84" s="37" t="s">
-        <v>240</v>
       </c>
       <c r="F84" s="34">
         <v>40051</v>
@@ -14857,13 +14858,13 @@
         <v>42</v>
       </c>
       <c r="H84" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="I84" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="I84" s="38" t="s">
+      <c r="J84" s="39" t="s">
         <v>353</v>
-      </c>
-      <c r="J84" s="39" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="85" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14883,13 +14884,13 @@
         <v>42</v>
       </c>
       <c r="H85" s="38" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I85" s="38" t="s">
+        <v>354</v>
+      </c>
+      <c r="J85" s="25" t="s">
         <v>355</v>
-      </c>
-      <c r="J85" s="25" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="86" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14909,13 +14910,13 @@
         <v>42</v>
       </c>
       <c r="H86" s="36" t="s">
+        <v>356</v>
+      </c>
+      <c r="I86" s="36" t="s">
         <v>357</v>
       </c>
-      <c r="I86" s="36" t="s">
+      <c r="J86" s="27" t="s">
         <v>358</v>
-      </c>
-      <c r="J86" s="27" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="87" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14923,10 +14924,10 @@
         <v>40061</v>
       </c>
       <c r="D87" s="37" t="s">
+        <v>359</v>
+      </c>
+      <c r="E87" s="37" t="s">
         <v>360</v>
-      </c>
-      <c r="E87" s="37" t="s">
-        <v>361</v>
       </c>
       <c r="F87" s="34">
         <v>40061</v>
@@ -14935,13 +14936,13 @@
         <v>52</v>
       </c>
       <c r="H87" s="38" t="s">
+        <v>361</v>
+      </c>
+      <c r="I87" s="38" t="s">
         <v>362</v>
       </c>
-      <c r="I87" s="38" t="s">
+      <c r="J87" s="39" t="s">
         <v>363</v>
-      </c>
-      <c r="J87" s="39" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="88" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14949,10 +14950,10 @@
         <v>40062</v>
       </c>
       <c r="D88" s="37" t="s">
+        <v>364</v>
+      </c>
+      <c r="E88" s="37" t="s">
         <v>365</v>
-      </c>
-      <c r="E88" s="37" t="s">
-        <v>366</v>
       </c>
       <c r="F88" s="34">
         <v>40062</v>
@@ -14961,13 +14962,13 @@
         <v>52</v>
       </c>
       <c r="H88" s="38" t="s">
+        <v>366</v>
+      </c>
+      <c r="I88" s="38" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="38" t="s">
+      <c r="J88" s="26" t="s">
         <v>368</v>
-      </c>
-      <c r="J88" s="26" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="89" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14975,10 +14976,10 @@
         <v>40063</v>
       </c>
       <c r="D89" s="35" t="s">
+        <v>369</v>
+      </c>
+      <c r="E89" s="35" t="s">
         <v>370</v>
-      </c>
-      <c r="E89" s="35" t="s">
-        <v>371</v>
       </c>
       <c r="F89" s="34">
         <v>40063</v>
@@ -14987,13 +14988,13 @@
         <v>52</v>
       </c>
       <c r="H89" s="36" t="s">
+        <v>371</v>
+      </c>
+      <c r="I89" s="36" t="s">
         <v>372</v>
       </c>
-      <c r="I89" s="36" t="s">
+      <c r="J89" s="27" t="s">
         <v>373</v>
-      </c>
-      <c r="J89" s="27" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="90" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15013,11 +15014,11 @@
         <v>15</v>
       </c>
       <c r="H90" s="13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I90" s="13"/>
       <c r="J90" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="91" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15025,10 +15026,10 @@
         <v>50002</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F91" s="14">
         <v>50002</v>
@@ -15037,11 +15038,11 @@
         <v>15</v>
       </c>
       <c r="H91" s="13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I91" s="13"/>
       <c r="J91" s="27" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="92" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15049,10 +15050,10 @@
         <v>50003</v>
       </c>
       <c r="D92" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="E92" s="14" t="s">
         <v>300</v>
-      </c>
-      <c r="E92" s="14" t="s">
-        <v>301</v>
       </c>
       <c r="F92" s="14">
         <v>50003</v>
@@ -15061,11 +15062,11 @@
         <v>15</v>
       </c>
       <c r="H92" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I92" s="13"/>
       <c r="J92" s="27" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="93" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15073,7 +15074,7 @@
         <v>50011</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E93" s="14" t="s">
         <v>52</v>
@@ -15085,11 +15086,11 @@
         <v>22</v>
       </c>
       <c r="H93" s="13" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I93" s="13"/>
       <c r="J93" s="27" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="94" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15097,10 +15098,10 @@
         <v>50012</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F94" s="14">
         <v>50012</v>
@@ -15109,11 +15110,11 @@
         <v>22</v>
       </c>
       <c r="H94" s="13" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I94" s="13"/>
       <c r="J94" s="27" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="95" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15121,7 +15122,7 @@
         <v>50013</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E95" s="14" t="s">
         <v>52</v>
@@ -15133,11 +15134,11 @@
         <v>22</v>
       </c>
       <c r="H95" s="13" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I95" s="13"/>
       <c r="J95" s="27" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="96" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15157,11 +15158,11 @@
         <v>28</v>
       </c>
       <c r="H96" s="13" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I96" s="13"/>
       <c r="J96" s="27" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="97" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15169,7 +15170,7 @@
         <v>50022</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E97" s="14" t="s">
         <v>47</v>
@@ -15181,11 +15182,11 @@
         <v>28</v>
       </c>
       <c r="H97" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I97" s="13"/>
       <c r="J97" s="27" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="98" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15193,7 +15194,7 @@
         <v>50023</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E98" s="14" t="s">
         <v>30</v>
@@ -15205,11 +15206,11 @@
         <v>28</v>
       </c>
       <c r="H98" s="13" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I98" s="13"/>
       <c r="J98" s="27" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="99" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15229,11 +15230,11 @@
         <v>32</v>
       </c>
       <c r="H99" s="13" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I99" s="13"/>
       <c r="J99" s="27" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="100" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15241,7 +15242,7 @@
         <v>50032</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E100" s="14" t="s">
         <v>102</v>
@@ -15253,11 +15254,11 @@
         <v>32</v>
       </c>
       <c r="H100" s="13" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I100" s="13"/>
       <c r="J100" s="27" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="101" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15265,10 +15266,10 @@
         <v>50033</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F101" s="14">
         <v>50033</v>
@@ -15277,11 +15278,11 @@
         <v>32</v>
       </c>
       <c r="H101" s="13" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I101" s="13"/>
       <c r="J101" s="27" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="102" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15301,11 +15302,11 @@
         <v>38</v>
       </c>
       <c r="H102" s="13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I102" s="13"/>
       <c r="J102" s="27" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="103" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15313,10 +15314,10 @@
         <v>50042</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E103" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F103" s="14">
         <v>50042</v>
@@ -15325,11 +15326,11 @@
         <v>38</v>
       </c>
       <c r="H103" s="13" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I103" s="13"/>
       <c r="J103" s="27" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="104" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15337,10 +15338,10 @@
         <v>50043</v>
       </c>
       <c r="D104" s="14" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F104" s="14">
         <v>50043</v>
@@ -15349,11 +15350,11 @@
         <v>38</v>
       </c>
       <c r="H104" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I104" s="13"/>
       <c r="J104" s="27" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="105" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15373,11 +15374,11 @@
         <v>42</v>
       </c>
       <c r="H105" s="13" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I105" s="13"/>
       <c r="J105" s="27" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="106" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15385,10 +15386,10 @@
         <v>50052</v>
       </c>
       <c r="D106" s="14" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F106" s="14">
         <v>50052</v>
@@ -15397,11 +15398,11 @@
         <v>42</v>
       </c>
       <c r="H106" s="13" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I106" s="13"/>
       <c r="J106" s="27" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="107" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15409,10 +15410,10 @@
         <v>50053</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E107" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F107" s="14">
         <v>50053</v>
@@ -15421,11 +15422,11 @@
         <v>42</v>
       </c>
       <c r="H107" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I107" s="13"/>
       <c r="J107" s="27" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="108" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15433,10 +15434,10 @@
         <v>50061</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F108" s="14">
         <v>50061</v>
@@ -15445,11 +15446,11 @@
         <v>52</v>
       </c>
       <c r="H108" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I108" s="13"/>
       <c r="J108" s="27" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="109" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15457,10 +15458,10 @@
         <v>50062</v>
       </c>
       <c r="D109" s="14" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E109" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F109" s="14">
         <v>50062</v>
@@ -15469,11 +15470,11 @@
         <v>52</v>
       </c>
       <c r="H109" s="13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I109" s="13"/>
       <c r="J109" s="27" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="110" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15481,10 +15482,10 @@
         <v>50063</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F110" s="14">
         <v>50063</v>
@@ -15493,11 +15494,11 @@
         <v>52</v>
       </c>
       <c r="H110" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I110" s="13"/>
       <c r="J110" s="27" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="111" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15505,10 +15506,10 @@
         <v>90001</v>
       </c>
       <c r="D111" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="E111" s="11" t="s">
         <v>421</v>
-      </c>
-      <c r="E111" s="11" t="s">
-        <v>422</v>
       </c>
       <c r="F111" s="11">
         <v>60010100</v>
@@ -15517,13 +15518,13 @@
         <v>1</v>
       </c>
       <c r="H111" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="I111" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="I111" s="3" t="s">
+      <c r="J111" s="25" t="s">
         <v>424</v>
-      </c>
-      <c r="J111" s="25" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="112" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15531,10 +15532,10 @@
         <v>90002</v>
       </c>
       <c r="D112" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="E112" s="11" t="s">
         <v>426</v>
-      </c>
-      <c r="E112" s="11" t="s">
-        <v>427</v>
       </c>
       <c r="F112" s="11">
         <v>60010200</v>
@@ -15543,13 +15544,13 @@
         <v>1</v>
       </c>
       <c r="H112" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="I112" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="I112" s="3" t="s">
+      <c r="J112" s="25" t="s">
         <v>429</v>
-      </c>
-      <c r="J112" s="25" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="113" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15557,10 +15558,10 @@
         <v>90003</v>
       </c>
       <c r="D113" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="E113" s="11" t="s">
         <v>431</v>
-      </c>
-      <c r="E113" s="11" t="s">
-        <v>432</v>
       </c>
       <c r="F113" s="11">
         <v>60010300</v>
@@ -15569,13 +15570,13 @@
         <v>1</v>
       </c>
       <c r="H113" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I113" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="I113" s="3" t="s">
+      <c r="J113" s="25" t="s">
         <v>434</v>
-      </c>
-      <c r="J113" s="25" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="114" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15583,10 +15584,10 @@
         <v>90004</v>
       </c>
       <c r="D114" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="E114" s="11" t="s">
         <v>436</v>
-      </c>
-      <c r="E114" s="11" t="s">
-        <v>437</v>
       </c>
       <c r="F114" s="11">
         <v>60010400</v>
@@ -15595,13 +15596,13 @@
         <v>2</v>
       </c>
       <c r="H114" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="I114" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="I114" s="3" t="s">
+      <c r="J114" s="25" t="s">
         <v>439</v>
-      </c>
-      <c r="J114" s="25" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="115" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15609,10 +15610,10 @@
         <v>90005</v>
       </c>
       <c r="D115" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="E115" s="11" t="s">
         <v>441</v>
-      </c>
-      <c r="E115" s="11" t="s">
-        <v>442</v>
       </c>
       <c r="F115" s="11">
         <v>60010500</v>
@@ -15621,13 +15622,13 @@
         <v>2</v>
       </c>
       <c r="H115" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="I115" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="I115" s="3" t="s">
+      <c r="J115" s="25" t="s">
         <v>444</v>
-      </c>
-      <c r="J115" s="25" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="116" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15635,10 +15636,10 @@
         <v>90006</v>
       </c>
       <c r="D116" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="E116" s="11" t="s">
         <v>446</v>
-      </c>
-      <c r="E116" s="11" t="s">
-        <v>447</v>
       </c>
       <c r="F116" s="11">
         <v>60010600</v>
@@ -15647,13 +15648,13 @@
         <v>2</v>
       </c>
       <c r="H116" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="I116" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="I116" s="3" t="s">
+      <c r="J116" s="25" t="s">
         <v>449</v>
-      </c>
-      <c r="J116" s="25" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="117" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15667,7 +15668,7 @@
         <v>1</v>
       </c>
       <c r="J117" s="40" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="118" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15681,7 +15682,7 @@
         <v>1</v>
       </c>
       <c r="J118" s="40" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="119" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15695,7 +15696,7 @@
         <v>1</v>
       </c>
       <c r="J119" s="40" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="120" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15709,7 +15710,7 @@
         <v>1</v>
       </c>
       <c r="J120" s="40" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="121" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15723,7 +15724,7 @@
         <v>1</v>
       </c>
       <c r="J121" s="40" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="122" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15737,7 +15738,7 @@
         <v>1</v>
       </c>
       <c r="J122" s="40" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="123" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15751,7 +15752,7 @@
         <v>1</v>
       </c>
       <c r="J123" s="40" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="124" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15765,7 +15766,7 @@
         <v>1</v>
       </c>
       <c r="J124" s="40" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="125" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15779,7 +15780,7 @@
         <v>1</v>
       </c>
       <c r="J125" s="40" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="126" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15793,7 +15794,7 @@
         <v>1</v>
       </c>
       <c r="J126" s="40" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="127" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15807,7 +15808,7 @@
         <v>1</v>
       </c>
       <c r="J127" s="40" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Q127" s="11"/>
     </row>
@@ -15822,7 +15823,7 @@
         <v>1</v>
       </c>
       <c r="J128" s="40" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q128" s="11"/>
     </row>
@@ -15837,7 +15838,7 @@
         <v>1</v>
       </c>
       <c r="J129" s="40" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q129" s="11"/>
     </row>
@@ -15852,7 +15853,7 @@
         <v>1</v>
       </c>
       <c r="J130" s="40" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q130" s="11"/>
     </row>
@@ -15867,7 +15868,7 @@
         <v>1</v>
       </c>
       <c r="J131" s="40" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="Q131" s="11"/>
     </row>
@@ -15882,7 +15883,7 @@
         <v>1</v>
       </c>
       <c r="J132" s="40" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Q132" s="11"/>
     </row>
@@ -15897,7 +15898,7 @@
         <v>1</v>
       </c>
       <c r="J133" s="40" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q133" s="11"/>
     </row>
@@ -15912,7 +15913,7 @@
         <v>1</v>
       </c>
       <c r="J134" s="40" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q134" s="11"/>
     </row>
@@ -15927,7 +15928,7 @@
         <v>1</v>
       </c>
       <c r="J135" s="40" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q135" s="11"/>
     </row>
@@ -15942,7 +15943,7 @@
         <v>1</v>
       </c>
       <c r="J136" s="40" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Q136" s="11"/>
     </row>
@@ -15957,7 +15958,7 @@
         <v>1</v>
       </c>
       <c r="J137" s="40" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q137" s="11"/>
     </row>
@@ -15972,7 +15973,7 @@
         <v>1</v>
       </c>
       <c r="J138" s="40" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q138" s="11"/>
     </row>
@@ -15987,7 +15988,7 @@
         <v>1</v>
       </c>
       <c r="J139" s="40" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Q139" s="11"/>
     </row>
@@ -16002,7 +16003,7 @@
         <v>1</v>
       </c>
       <c r="J140" s="40" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q140" s="11"/>
     </row>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87196AFC-BA51-431F-8DBD-FFFC4A8A6D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B645D70-4BBF-448E-A4A6-C3D47C01D070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="489">
   <si>
     <t>c</t>
   </si>
@@ -117,9 +117,6 @@
   </si>
   <si>
     <t>New passive skill: Life Recovery. When taking damage, there is a chance to restore 5% of maximum HP.</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;62000001</t>
   </si>
   <si>
     <t>强击</t>
@@ -1329,9 +1326,6 @@
     <t>坚韧之力</t>
   </si>
   <si>
-    <t>当生命值降低至50%后,闪避提升40%,自身伤害提升50%,持续3秒，30秒内只能触发一次</t>
-  </si>
-  <si>
     <t>SkillIdAdd;62000117</t>
   </si>
   <si>
@@ -1562,6 +1556,18 @@
   </si>
   <si>
     <t>BuffIdAdd;60000301,60000302,60000401,60000402;90000301@SkillIdAdd;62000121</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>当生命值降低至30%后,闪避提升50%,自身伤害提升30%,持续3秒，30秒内只能触发一次</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命恢复</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIdAdd;62000001</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -12818,7 +12824,7 @@
         <v>10001</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>15</v>
+        <v>487</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>16</v>
@@ -12836,7 +12842,7 @@
         <v>18</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>19</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12844,10 +12850,10 @@
         <v>10002</v>
       </c>
       <c r="D7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>20</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>21</v>
       </c>
       <c r="F7" s="11">
         <v>10002</v>
@@ -12856,13 +12862,13 @@
         <v>15</v>
       </c>
       <c r="H7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="J7" s="24" t="s">
         <v>23</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12870,10 +12876,10 @@
         <v>10003</v>
       </c>
       <c r="D8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>26</v>
       </c>
       <c r="F8" s="11">
         <v>10003</v>
@@ -12882,13 +12888,13 @@
         <v>15</v>
       </c>
       <c r="H8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="J8" s="25" t="s">
         <v>28</v>
-      </c>
-      <c r="J8" s="25" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12896,10 +12902,10 @@
         <v>10011</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" s="11">
         <v>10011</v>
@@ -12908,13 +12914,13 @@
         <v>22</v>
       </c>
       <c r="H9" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="I9" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>476</v>
-      </c>
       <c r="J9" s="24" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12922,10 +12928,10 @@
         <v>10012</v>
       </c>
       <c r="D10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>32</v>
       </c>
       <c r="F10" s="11">
         <v>10012</v>
@@ -12934,13 +12940,13 @@
         <v>22</v>
       </c>
       <c r="H10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="J10" s="25" t="s">
         <v>34</v>
-      </c>
-      <c r="J10" s="25" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="11" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12948,10 +12954,10 @@
         <v>10013</v>
       </c>
       <c r="D11" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>37</v>
       </c>
       <c r="F11" s="11">
         <v>10013</v>
@@ -12960,13 +12966,13 @@
         <v>22</v>
       </c>
       <c r="H11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="J11" s="24" t="s">
         <v>39</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="12" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12974,10 +12980,10 @@
         <v>10021</v>
       </c>
       <c r="D12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>42</v>
       </c>
       <c r="F12" s="11">
         <v>10021</v>
@@ -12986,13 +12992,13 @@
         <v>28</v>
       </c>
       <c r="H12" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="J12" s="25" t="s">
         <v>44</v>
-      </c>
-      <c r="J12" s="25" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="13" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13000,10 +13006,10 @@
         <v>10022</v>
       </c>
       <c r="D13" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>46</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>47</v>
       </c>
       <c r="F13" s="11">
         <v>10022</v>
@@ -13012,13 +13018,13 @@
         <v>28</v>
       </c>
       <c r="H13" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="J13" s="25" t="s">
         <v>49</v>
-      </c>
-      <c r="J13" s="25" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="14" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13026,10 +13032,10 @@
         <v>10023</v>
       </c>
       <c r="D14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>52</v>
       </c>
       <c r="F14" s="11">
         <v>10023</v>
@@ -13038,13 +13044,13 @@
         <v>28</v>
       </c>
       <c r="H14" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="J14" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="15" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13052,10 +13058,10 @@
         <v>10031</v>
       </c>
       <c r="D15" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>57</v>
       </c>
       <c r="F15" s="11">
         <v>10031</v>
@@ -13064,13 +13070,13 @@
         <v>32</v>
       </c>
       <c r="H15" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="J15" s="24" t="s">
         <v>59</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="16" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13078,10 +13084,10 @@
         <v>10032</v>
       </c>
       <c r="D16" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>61</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>62</v>
       </c>
       <c r="F16" s="11">
         <v>10032</v>
@@ -13090,13 +13096,13 @@
         <v>32</v>
       </c>
       <c r="H16" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I16" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="J16" s="24" t="s">
         <v>64</v>
-      </c>
-      <c r="J16" s="24" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="17" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13104,10 +13110,10 @@
         <v>10033</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>66</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>67</v>
       </c>
       <c r="F17" s="11">
         <v>10033</v>
@@ -13116,13 +13122,13 @@
         <v>32</v>
       </c>
       <c r="H17" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="J17" s="25" t="s">
         <v>69</v>
-      </c>
-      <c r="J17" s="25" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="18" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13130,10 +13136,10 @@
         <v>10041</v>
       </c>
       <c r="D18" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>71</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>72</v>
       </c>
       <c r="F18" s="11">
         <v>10041</v>
@@ -13142,13 +13148,13 @@
         <v>38</v>
       </c>
       <c r="H18" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="J18" s="24" t="s">
         <v>74</v>
-      </c>
-      <c r="J18" s="24" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="19" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13156,10 +13162,10 @@
         <v>10042</v>
       </c>
       <c r="D19" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>77</v>
       </c>
       <c r="F19" s="11">
         <v>10042</v>
@@ -13168,13 +13174,13 @@
         <v>38</v>
       </c>
       <c r="H19" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="J19" s="24" t="s">
         <v>79</v>
-      </c>
-      <c r="J19" s="24" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="20" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13182,10 +13188,10 @@
         <v>10043</v>
       </c>
       <c r="D20" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>81</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>82</v>
       </c>
       <c r="F20" s="11">
         <v>10043</v>
@@ -13194,13 +13200,13 @@
         <v>38</v>
       </c>
       <c r="H20" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="I20" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="J20" s="25" t="s">
         <v>84</v>
-      </c>
-      <c r="J20" s="25" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="21" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13208,10 +13214,10 @@
         <v>10051</v>
       </c>
       <c r="D21" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>86</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>87</v>
       </c>
       <c r="F21" s="11">
         <v>10051</v>
@@ -13220,13 +13226,13 @@
         <v>42</v>
       </c>
       <c r="H21" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="I21" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="J21" s="24" t="s">
         <v>89</v>
-      </c>
-      <c r="J21" s="24" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="22" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13234,10 +13240,10 @@
         <v>10052</v>
       </c>
       <c r="D22" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>91</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>92</v>
       </c>
       <c r="F22" s="11">
         <v>10052</v>
@@ -13246,13 +13252,13 @@
         <v>42</v>
       </c>
       <c r="H22" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="I22" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="J22" s="24" t="s">
         <v>94</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="23" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13260,10 +13266,10 @@
         <v>10053</v>
       </c>
       <c r="D23" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>96</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>97</v>
       </c>
       <c r="F23" s="11">
         <v>10053</v>
@@ -13272,13 +13278,13 @@
         <v>42</v>
       </c>
       <c r="H23" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="I23" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="I23" s="13" t="s">
+      <c r="J23" s="25" t="s">
         <v>99</v>
-      </c>
-      <c r="J23" s="25" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="24" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13286,10 +13292,10 @@
         <v>10061</v>
       </c>
       <c r="D24" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>101</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>102</v>
       </c>
       <c r="F24" s="14">
         <v>10061</v>
@@ -13298,13 +13304,13 @@
         <v>52</v>
       </c>
       <c r="H24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="J24" s="26" t="s">
         <v>104</v>
-      </c>
-      <c r="J24" s="26" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="25" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13312,10 +13318,10 @@
         <v>10062</v>
       </c>
       <c r="D25" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="15" t="s">
         <v>81</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>82</v>
       </c>
       <c r="F25" s="14">
         <v>10062</v>
@@ -13324,13 +13330,13 @@
         <v>52</v>
       </c>
       <c r="H25" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="I25" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="J25" s="26" t="s">
         <v>107</v>
-      </c>
-      <c r="J25" s="26" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="26" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13338,10 +13344,10 @@
         <v>10063</v>
       </c>
       <c r="D26" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>109</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>110</v>
       </c>
       <c r="F26" s="14">
         <v>10063</v>
@@ -13350,13 +13356,13 @@
         <v>52</v>
       </c>
       <c r="H26" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="I26" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="I26" s="13" t="s">
+      <c r="J26" s="27" t="s">
         <v>112</v>
-      </c>
-      <c r="J26" s="27" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="27" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13364,10 +13370,10 @@
         <v>20001</v>
       </c>
       <c r="D27" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>115</v>
       </c>
       <c r="F27" s="11">
         <v>20001</v>
@@ -13376,13 +13382,13 @@
         <v>15</v>
       </c>
       <c r="H27" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="I27" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I27" s="12" t="s">
+      <c r="J27" s="25" t="s">
         <v>117</v>
-      </c>
-      <c r="J27" s="25" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="28" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13390,10 +13396,10 @@
         <v>20002</v>
       </c>
       <c r="D28" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>120</v>
       </c>
       <c r="F28" s="11">
         <v>20002</v>
@@ -13402,13 +13408,13 @@
         <v>15</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J28" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13416,10 +13422,10 @@
         <v>20003</v>
       </c>
       <c r="D29" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>123</v>
       </c>
       <c r="F29" s="11">
         <v>20003</v>
@@ -13428,13 +13434,13 @@
         <v>15</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J29" s="25" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="30" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13442,10 +13448,10 @@
         <v>20011</v>
       </c>
       <c r="D30" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>124</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>125</v>
       </c>
       <c r="F30" s="11">
         <v>20011</v>
@@ -13454,13 +13460,13 @@
         <v>22</v>
       </c>
       <c r="H30" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="I30" s="12" t="s">
         <v>478</v>
       </c>
-      <c r="I30" s="12" t="s">
+      <c r="J30" s="24" t="s">
         <v>480</v>
-      </c>
-      <c r="J30" s="24" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="31" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13468,10 +13474,10 @@
         <v>20012</v>
       </c>
       <c r="D31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>126</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>127</v>
       </c>
       <c r="F31" s="11">
         <v>20012</v>
@@ -13480,13 +13486,13 @@
         <v>22</v>
       </c>
       <c r="H31" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I31" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="J31" s="25" t="s">
         <v>129</v>
-      </c>
-      <c r="J31" s="25" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="32" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13494,10 +13500,10 @@
         <v>20013</v>
       </c>
       <c r="D32" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E32" s="11" t="s">
         <v>131</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>132</v>
       </c>
       <c r="F32" s="11">
         <v>20013</v>
@@ -13506,13 +13512,13 @@
         <v>22</v>
       </c>
       <c r="H32" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="I32" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="J32" s="25" t="s">
         <v>134</v>
-      </c>
-      <c r="J32" s="25" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="33" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13520,10 +13526,10 @@
         <v>20021</v>
       </c>
       <c r="D33" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" s="11" t="s">
         <v>136</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>137</v>
       </c>
       <c r="F33" s="11">
         <v>20021</v>
@@ -13532,13 +13538,13 @@
         <v>28</v>
       </c>
       <c r="H33" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="I33" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="I33" s="12" t="s">
+      <c r="J33" s="25" t="s">
         <v>139</v>
-      </c>
-      <c r="J33" s="25" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="34" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13546,10 +13552,10 @@
         <v>20022</v>
       </c>
       <c r="D34" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>52</v>
       </c>
       <c r="F34" s="11">
         <v>20022</v>
@@ -13558,13 +13564,13 @@
         <v>28</v>
       </c>
       <c r="H34" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="I34" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="I34" s="12" t="s">
+      <c r="J34" s="25" t="s">
         <v>142</v>
-      </c>
-      <c r="J34" s="25" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="35" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13572,10 +13578,10 @@
         <v>20023</v>
       </c>
       <c r="D35" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E35" s="11" t="s">
         <v>144</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>145</v>
       </c>
       <c r="F35" s="11">
         <v>20023</v>
@@ -13584,13 +13590,13 @@
         <v>28</v>
       </c>
       <c r="H35" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="I35" s="12" t="s">
         <v>479</v>
       </c>
-      <c r="I35" s="12" t="s">
-        <v>481</v>
-      </c>
       <c r="J35" s="25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13598,10 +13604,10 @@
         <v>20031</v>
       </c>
       <c r="D36" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E36" s="11" t="s">
         <v>147</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>148</v>
       </c>
       <c r="F36" s="11">
         <v>20031</v>
@@ -13610,13 +13616,13 @@
         <v>32</v>
       </c>
       <c r="H36" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="I36" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="I36" s="12" t="s">
+      <c r="J36" s="25" t="s">
         <v>150</v>
-      </c>
-      <c r="J36" s="25" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="37" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13624,10 +13630,10 @@
         <v>20032</v>
       </c>
       <c r="D37" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>52</v>
       </c>
       <c r="F37" s="11">
         <v>20032</v>
@@ -13636,13 +13642,13 @@
         <v>32</v>
       </c>
       <c r="H37" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I37" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="I37" s="12" t="s">
+      <c r="J37" s="24" t="s">
         <v>153</v>
-      </c>
-      <c r="J37" s="24" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="38" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13650,10 +13656,10 @@
         <v>20033</v>
       </c>
       <c r="D38" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E38" s="11" t="s">
         <v>155</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>156</v>
       </c>
       <c r="F38" s="11">
         <v>20033</v>
@@ -13662,13 +13668,13 @@
         <v>32</v>
       </c>
       <c r="H38" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="I38" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="I38" s="12" t="s">
+      <c r="J38" s="25" t="s">
         <v>158</v>
-      </c>
-      <c r="J38" s="25" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="39" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13676,10 +13682,10 @@
         <v>20041</v>
       </c>
       <c r="D39" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>160</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>161</v>
       </c>
       <c r="F39" s="11">
         <v>20041</v>
@@ -13688,13 +13694,13 @@
         <v>38</v>
       </c>
       <c r="H39" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="I39" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="I39" s="12" t="s">
+      <c r="J39" s="24" t="s">
         <v>163</v>
-      </c>
-      <c r="J39" s="24" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="40" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13702,10 +13708,10 @@
         <v>20042</v>
       </c>
       <c r="D40" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>52</v>
       </c>
       <c r="F40" s="11">
         <v>20042</v>
@@ -13714,13 +13720,13 @@
         <v>38</v>
       </c>
       <c r="H40" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="I40" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="I40" s="12" t="s">
+      <c r="J40" s="25" t="s">
         <v>166</v>
-      </c>
-      <c r="J40" s="25" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="41" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13728,10 +13734,10 @@
         <v>20043</v>
       </c>
       <c r="D41" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="E41" s="11" t="s">
         <v>168</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>169</v>
       </c>
       <c r="F41" s="11">
         <v>20043</v>
@@ -13740,13 +13746,13 @@
         <v>38</v>
       </c>
       <c r="H41" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="I41" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="I41" s="12" t="s">
+      <c r="J41" s="25" t="s">
         <v>171</v>
-      </c>
-      <c r="J41" s="25" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="42" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13754,10 +13760,10 @@
         <v>20051</v>
       </c>
       <c r="D42" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E42" s="11" t="s">
         <v>173</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="F42" s="11">
         <v>20051</v>
@@ -13766,13 +13772,13 @@
         <v>42</v>
       </c>
       <c r="H42" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="I42" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="I42" s="12" t="s">
+      <c r="J42" s="24" t="s">
         <v>176</v>
-      </c>
-      <c r="J42" s="24" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="43" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13780,10 +13786,10 @@
         <v>20052</v>
       </c>
       <c r="D43" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>52</v>
       </c>
       <c r="F43" s="11">
         <v>20052</v>
@@ -13792,13 +13798,13 @@
         <v>42</v>
       </c>
       <c r="H43" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="I43" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="J43" s="24" t="s">
         <v>179</v>
-      </c>
-      <c r="J43" s="24" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="44" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13806,10 +13812,10 @@
         <v>20053</v>
       </c>
       <c r="D44" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E44" s="11" t="s">
         <v>181</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>182</v>
       </c>
       <c r="F44" s="11">
         <v>20053</v>
@@ -13818,13 +13824,13 @@
         <v>42</v>
       </c>
       <c r="H44" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="I44" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="I44" s="12" t="s">
+      <c r="J44" s="24" t="s">
         <v>184</v>
-      </c>
-      <c r="J44" s="24" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="45" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13832,10 +13838,10 @@
         <v>20061</v>
       </c>
       <c r="D45" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" s="15" t="s">
         <v>81</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>82</v>
       </c>
       <c r="F45" s="11">
         <v>20061</v>
@@ -13844,13 +13850,13 @@
         <v>52</v>
       </c>
       <c r="H45" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="I45" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="I45" s="13" t="s">
+      <c r="J45" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="46" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13858,10 +13864,10 @@
         <v>20062</v>
       </c>
       <c r="D46" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="E46" s="15" t="s">
         <v>189</v>
-      </c>
-      <c r="E46" s="15" t="s">
-        <v>190</v>
       </c>
       <c r="F46" s="11">
         <v>20062</v>
@@ -13870,13 +13876,13 @@
         <v>52</v>
       </c>
       <c r="H46" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="I46" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="I46" s="13" t="s">
+      <c r="J46" s="27" t="s">
         <v>192</v>
-      </c>
-      <c r="J46" s="27" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="47" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13884,10 +13890,10 @@
         <v>20063</v>
       </c>
       <c r="D47" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E47" s="15" t="s">
         <v>194</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>195</v>
       </c>
       <c r="F47" s="11">
         <v>20063</v>
@@ -13896,13 +13902,13 @@
         <v>52</v>
       </c>
       <c r="H47" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="I47" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="I47" s="13" t="s">
+      <c r="J47" s="26" t="s">
         <v>197</v>
-      </c>
-      <c r="J47" s="26" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="48" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13922,13 +13928,13 @@
         <v>15</v>
       </c>
       <c r="H48" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="I48" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="I48" s="17" t="s">
+      <c r="J48" s="26" t="s">
         <v>200</v>
-      </c>
-      <c r="J48" s="26" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="49" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13936,10 +13942,10 @@
         <v>30002</v>
       </c>
       <c r="D49" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E49" s="16" t="s">
         <v>202</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>203</v>
       </c>
       <c r="F49" s="11">
         <v>30002</v>
@@ -13948,13 +13954,13 @@
         <v>15</v>
       </c>
       <c r="H49" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="I49" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="I49" s="17" t="s">
+      <c r="J49" s="26" t="s">
         <v>205</v>
-      </c>
-      <c r="J49" s="26" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="50" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13962,10 +13968,10 @@
         <v>30003</v>
       </c>
       <c r="D50" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="18" t="s">
         <v>25</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>26</v>
       </c>
       <c r="F50" s="11">
         <v>30003</v>
@@ -13974,13 +13980,13 @@
         <v>15</v>
       </c>
       <c r="H50" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="I50" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="I50" s="12" t="s">
+      <c r="J50" s="25" t="s">
         <v>208</v>
-      </c>
-      <c r="J50" s="25" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="51" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13988,10 +13994,10 @@
         <v>30011</v>
       </c>
       <c r="D51" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="E51" s="16" t="s">
         <v>210</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>211</v>
       </c>
       <c r="F51" s="11">
         <v>30011</v>
@@ -14000,13 +14006,13 @@
         <v>22</v>
       </c>
       <c r="H51" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="I51" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="I51" s="17" t="s">
+      <c r="J51" s="26" t="s">
         <v>213</v>
-      </c>
-      <c r="J51" s="26" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="52" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14014,10 +14020,10 @@
         <v>30012</v>
       </c>
       <c r="D52" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="E52" s="19" t="s">
         <v>215</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>216</v>
       </c>
       <c r="F52" s="11">
         <v>30012</v>
@@ -14026,13 +14032,13 @@
         <v>22</v>
       </c>
       <c r="H52" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="I52" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="I52" s="20" t="s">
+      <c r="J52" s="25" t="s">
         <v>218</v>
-      </c>
-      <c r="J52" s="25" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="53" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14040,10 +14046,10 @@
         <v>30013</v>
       </c>
       <c r="D53" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="E53" s="18" t="s">
         <v>220</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>221</v>
       </c>
       <c r="F53" s="11">
         <v>30013</v>
@@ -14052,13 +14058,13 @@
         <v>22</v>
       </c>
       <c r="H53" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="I53" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="I53" s="12" t="s">
+      <c r="J53" s="25" t="s">
         <v>223</v>
-      </c>
-      <c r="J53" s="25" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="54" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14066,10 +14072,10 @@
         <v>30021</v>
       </c>
       <c r="D54" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="E54" s="18" t="s">
         <v>225</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>226</v>
       </c>
       <c r="F54" s="11">
         <v>30021</v>
@@ -14078,13 +14084,13 @@
         <v>28</v>
       </c>
       <c r="H54" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="I54" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="I54" s="12" t="s">
+      <c r="J54" s="25" t="s">
         <v>228</v>
-      </c>
-      <c r="J54" s="25" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="55" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14092,10 +14098,10 @@
         <v>30022</v>
       </c>
       <c r="D55" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="E55" s="18" t="s">
         <v>230</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>231</v>
       </c>
       <c r="F55" s="11">
         <v>30022</v>
@@ -14104,13 +14110,13 @@
         <v>28</v>
       </c>
       <c r="H55" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="I55" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="I55" s="12" t="s">
+      <c r="J55" s="26" t="s">
         <v>233</v>
-      </c>
-      <c r="J55" s="26" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="56" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14118,10 +14124,10 @@
         <v>30023</v>
       </c>
       <c r="D56" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E56" s="18" t="s">
         <v>51</v>
-      </c>
-      <c r="E56" s="18" t="s">
-        <v>52</v>
       </c>
       <c r="F56" s="11">
         <v>30023</v>
@@ -14130,13 +14136,13 @@
         <v>28</v>
       </c>
       <c r="H56" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="I56" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="I56" s="12" t="s">
+      <c r="J56" s="25" t="s">
         <v>236</v>
-      </c>
-      <c r="J56" s="25" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="57" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14144,10 +14150,10 @@
         <v>30031</v>
       </c>
       <c r="D57" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="E57" s="18" t="s">
         <v>238</v>
-      </c>
-      <c r="E57" s="18" t="s">
-        <v>239</v>
       </c>
       <c r="F57" s="11">
         <v>30031</v>
@@ -14156,13 +14162,13 @@
         <v>32</v>
       </c>
       <c r="H57" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I57" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="I57" s="12" t="s">
+      <c r="J57" s="26" t="s">
         <v>241</v>
-      </c>
-      <c r="J57" s="26" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="58" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14170,10 +14176,10 @@
         <v>30032</v>
       </c>
       <c r="D58" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="E58" s="21" t="s">
         <v>243</v>
-      </c>
-      <c r="E58" s="21" t="s">
-        <v>244</v>
       </c>
       <c r="F58" s="11">
         <v>30032</v>
@@ -14182,13 +14188,13 @@
         <v>32</v>
       </c>
       <c r="H58" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="I58" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="I58" s="22" t="s">
+      <c r="J58" s="26" t="s">
         <v>246</v>
-      </c>
-      <c r="J58" s="26" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="59" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14196,10 +14202,10 @@
         <v>30033</v>
       </c>
       <c r="D59" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E59" s="18" t="s">
         <v>66</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>67</v>
       </c>
       <c r="F59" s="11">
         <v>30033</v>
@@ -14208,13 +14214,13 @@
         <v>32</v>
       </c>
       <c r="H59" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="I59" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="I59" s="12" t="s">
+      <c r="J59" s="25" t="s">
         <v>249</v>
-      </c>
-      <c r="J59" s="25" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="60" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14222,10 +14228,10 @@
         <v>30041</v>
       </c>
       <c r="D60" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="E60" s="18" t="s">
         <v>251</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>252</v>
       </c>
       <c r="F60" s="11">
         <v>30041</v>
@@ -14234,13 +14240,13 @@
         <v>38</v>
       </c>
       <c r="H60" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="I60" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="I60" s="12" t="s">
+      <c r="J60" s="25" t="s">
         <v>254</v>
-      </c>
-      <c r="J60" s="25" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="61" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14248,10 +14254,10 @@
         <v>30042</v>
       </c>
       <c r="D61" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="E61" s="16" t="s">
         <v>256</v>
-      </c>
-      <c r="E61" s="16" t="s">
-        <v>257</v>
       </c>
       <c r="F61" s="11">
         <v>30042</v>
@@ -14260,13 +14266,13 @@
         <v>38</v>
       </c>
       <c r="H61" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="I61" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="I61" s="12" t="s">
-        <v>259</v>
-      </c>
       <c r="J61" s="24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14274,10 +14280,10 @@
         <v>30043</v>
       </c>
       <c r="D62" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E62" s="18" t="s">
         <v>81</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>82</v>
       </c>
       <c r="F62" s="11">
         <v>30043</v>
@@ -14286,13 +14292,13 @@
         <v>38</v>
       </c>
       <c r="H62" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="I62" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="I62" s="12" t="s">
+      <c r="J62" s="25" t="s">
         <v>261</v>
-      </c>
-      <c r="J62" s="25" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="63" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14300,10 +14306,10 @@
         <v>30051</v>
       </c>
       <c r="D63" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E63" s="18" t="s">
         <v>263</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>264</v>
       </c>
       <c r="F63" s="11">
         <v>30051</v>
@@ -14312,13 +14318,13 @@
         <v>42</v>
       </c>
       <c r="H63" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="I63" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="I63" s="12" t="s">
+      <c r="J63" s="25" t="s">
         <v>266</v>
-      </c>
-      <c r="J63" s="25" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="64" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14326,10 +14332,10 @@
         <v>30052</v>
       </c>
       <c r="D64" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="E64" s="21" t="s">
         <v>268</v>
-      </c>
-      <c r="E64" s="21" t="s">
-        <v>269</v>
       </c>
       <c r="F64" s="11">
         <v>30052</v>
@@ -14338,13 +14344,13 @@
         <v>42</v>
       </c>
       <c r="H64" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="I64" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="I64" s="23" t="s">
+      <c r="J64" s="24" t="s">
         <v>271</v>
-      </c>
-      <c r="J64" s="24" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="65" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14352,10 +14358,10 @@
         <v>30053</v>
       </c>
       <c r="D65" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="E65" s="18" t="s">
         <v>96</v>
-      </c>
-      <c r="E65" s="18" t="s">
-        <v>97</v>
       </c>
       <c r="F65" s="11">
         <v>30053</v>
@@ -14364,13 +14370,13 @@
         <v>42</v>
       </c>
       <c r="H65" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="I65" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="I65" s="12" t="s">
+      <c r="J65" s="25" t="s">
         <v>274</v>
-      </c>
-      <c r="J65" s="25" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="66" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14378,10 +14384,10 @@
         <v>30061</v>
       </c>
       <c r="D66" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="E66" s="15" t="s">
         <v>276</v>
-      </c>
-      <c r="E66" s="15" t="s">
-        <v>277</v>
       </c>
       <c r="F66" s="11">
         <v>30061</v>
@@ -14390,13 +14396,13 @@
         <v>52</v>
       </c>
       <c r="H66" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="I66" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="I66" s="13" t="s">
+      <c r="J66" s="26" t="s">
         <v>279</v>
-      </c>
-      <c r="J66" s="26" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="67" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14404,10 +14410,10 @@
         <v>30062</v>
       </c>
       <c r="D67" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="E67" s="28" t="s">
         <v>281</v>
-      </c>
-      <c r="E67" s="28" t="s">
-        <v>282</v>
       </c>
       <c r="F67" s="11">
         <v>30062</v>
@@ -14416,13 +14422,13 @@
         <v>52</v>
       </c>
       <c r="H67" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="I67" s="29" t="s">
         <v>283</v>
       </c>
-      <c r="I67" s="29" t="s">
+      <c r="J67" s="27" t="s">
         <v>284</v>
-      </c>
-      <c r="J67" s="27" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="68" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14430,10 +14436,10 @@
         <v>30063</v>
       </c>
       <c r="D68" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="E68" s="30" t="s">
         <v>286</v>
-      </c>
-      <c r="E68" s="30" t="s">
-        <v>287</v>
       </c>
       <c r="F68" s="11">
         <v>30063</v>
@@ -14442,13 +14448,13 @@
         <v>52</v>
       </c>
       <c r="H68" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="I68" s="31" t="s">
         <v>288</v>
       </c>
-      <c r="I68" s="31" t="s">
+      <c r="J68" s="26" t="s">
         <v>289</v>
-      </c>
-      <c r="J68" s="26" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="69" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14456,10 +14462,10 @@
         <v>40001</v>
       </c>
       <c r="D69" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="E69" s="32" t="s">
         <v>291</v>
-      </c>
-      <c r="E69" s="32" t="s">
-        <v>292</v>
       </c>
       <c r="F69" s="14">
         <v>40001</v>
@@ -14468,13 +14474,13 @@
         <v>15</v>
       </c>
       <c r="H69" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="I69" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="I69" s="33" t="s">
+      <c r="J69" s="26" t="s">
         <v>294</v>
-      </c>
-      <c r="J69" s="26" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="70" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14482,10 +14488,10 @@
         <v>40002</v>
       </c>
       <c r="D70" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="E70" s="32" t="s">
         <v>51</v>
-      </c>
-      <c r="E70" s="32" t="s">
-        <v>52</v>
       </c>
       <c r="F70" s="14">
         <v>40002</v>
@@ -14494,13 +14500,13 @@
         <v>15</v>
       </c>
       <c r="H70" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="I70" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="I70" s="12" t="s">
+      <c r="J70" s="25" t="s">
         <v>297</v>
-      </c>
-      <c r="J70" s="25" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="71" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14508,10 +14514,10 @@
         <v>40003</v>
       </c>
       <c r="D71" s="35" t="s">
+        <v>298</v>
+      </c>
+      <c r="E71" s="35" t="s">
         <v>299</v>
-      </c>
-      <c r="E71" s="35" t="s">
-        <v>300</v>
       </c>
       <c r="F71" s="34">
         <v>40003</v>
@@ -14520,13 +14526,13 @@
         <v>15</v>
       </c>
       <c r="H71" s="36" t="s">
+        <v>300</v>
+      </c>
+      <c r="I71" s="36" t="s">
         <v>301</v>
       </c>
-      <c r="I71" s="36" t="s">
+      <c r="J71" s="26" t="s">
         <v>302</v>
-      </c>
-      <c r="J71" s="26" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="72" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14534,10 +14540,10 @@
         <v>40011</v>
       </c>
       <c r="D72" s="32" t="s">
+        <v>303</v>
+      </c>
+      <c r="E72" s="32" t="s">
         <v>304</v>
-      </c>
-      <c r="E72" s="32" t="s">
-        <v>305</v>
       </c>
       <c r="F72" s="14">
         <v>40011</v>
@@ -14546,13 +14552,13 @@
         <v>22</v>
       </c>
       <c r="H72" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="I72" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="I72" s="33" t="s">
+      <c r="J72" s="26" t="s">
         <v>307</v>
-      </c>
-      <c r="J72" s="26" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="73" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14560,10 +14566,10 @@
         <v>40012</v>
       </c>
       <c r="D73" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="E73" s="32" t="s">
         <v>81</v>
-      </c>
-      <c r="E73" s="32" t="s">
-        <v>82</v>
       </c>
       <c r="F73" s="14">
         <v>40012</v>
@@ -14572,13 +14578,13 @@
         <v>22</v>
       </c>
       <c r="H73" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="I73" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="I73" s="33" t="s">
+      <c r="J73" s="26" t="s">
         <v>310</v>
-      </c>
-      <c r="J73" s="26" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="74" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14586,10 +14592,10 @@
         <v>40013</v>
       </c>
       <c r="D74" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="E74" s="35" t="s">
         <v>312</v>
-      </c>
-      <c r="E74" s="35" t="s">
-        <v>313</v>
       </c>
       <c r="F74" s="34">
         <v>40013</v>
@@ -14598,13 +14604,13 @@
         <v>22</v>
       </c>
       <c r="H74" s="36" t="s">
+        <v>313</v>
+      </c>
+      <c r="I74" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="I74" s="36" t="s">
+      <c r="J74" s="41" t="s">
         <v>315</v>
-      </c>
-      <c r="J74" s="41" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="75" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14612,10 +14618,10 @@
         <v>40021</v>
       </c>
       <c r="D75" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="E75" s="32" t="s">
         <v>317</v>
-      </c>
-      <c r="E75" s="32" t="s">
-        <v>318</v>
       </c>
       <c r="F75" s="14">
         <v>40021</v>
@@ -14624,13 +14630,13 @@
         <v>28</v>
       </c>
       <c r="H75" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="I75" s="33" t="s">
         <v>319</v>
       </c>
-      <c r="I75" s="33" t="s">
+      <c r="J75" s="26" t="s">
         <v>320</v>
-      </c>
-      <c r="J75" s="26" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="76" spans="3:10" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14638,10 +14644,10 @@
         <v>40022</v>
       </c>
       <c r="D76" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="E76" s="32" t="s">
         <v>81</v>
-      </c>
-      <c r="E76" s="32" t="s">
-        <v>82</v>
       </c>
       <c r="F76" s="14">
         <v>40022</v>
@@ -14650,13 +14656,13 @@
         <v>28</v>
       </c>
       <c r="H76" s="33" t="s">
+        <v>321</v>
+      </c>
+      <c r="I76" s="33" t="s">
         <v>322</v>
       </c>
-      <c r="I76" s="33" t="s">
+      <c r="J76" s="25" t="s">
         <v>323</v>
-      </c>
-      <c r="J76" s="25" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="77" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14664,10 +14670,10 @@
         <v>40023</v>
       </c>
       <c r="D77" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E77" s="35" t="s">
         <v>25</v>
-      </c>
-      <c r="E77" s="35" t="s">
-        <v>26</v>
       </c>
       <c r="F77" s="34">
         <v>40023</v>
@@ -14676,13 +14682,13 @@
         <v>28</v>
       </c>
       <c r="H77" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="I77" s="36" t="s">
         <v>325</v>
       </c>
-      <c r="I77" s="36" t="s">
-        <v>326</v>
-      </c>
       <c r="J77" s="25" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="78" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14690,10 +14696,10 @@
         <v>40031</v>
       </c>
       <c r="D78" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="E78" s="37" t="s">
         <v>327</v>
-      </c>
-      <c r="E78" s="37" t="s">
-        <v>328</v>
       </c>
       <c r="F78" s="34">
         <v>40031</v>
@@ -14702,13 +14708,13 @@
         <v>32</v>
       </c>
       <c r="H78" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="I78" s="38" t="s">
         <v>329</v>
       </c>
-      <c r="I78" s="38" t="s">
+      <c r="J78" s="39" t="s">
         <v>330</v>
-      </c>
-      <c r="J78" s="39" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="79" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14716,10 +14722,10 @@
         <v>40032</v>
       </c>
       <c r="D79" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="E79" s="37" t="s">
         <v>81</v>
-      </c>
-      <c r="E79" s="37" t="s">
-        <v>82</v>
       </c>
       <c r="F79" s="34">
         <v>40032</v>
@@ -14728,13 +14734,13 @@
         <v>32</v>
       </c>
       <c r="H79" s="38" t="s">
+        <v>331</v>
+      </c>
+      <c r="I79" s="38" t="s">
         <v>332</v>
       </c>
-      <c r="I79" s="38" t="s">
+      <c r="J79" s="25" t="s">
         <v>333</v>
-      </c>
-      <c r="J79" s="25" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="80" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14742,10 +14748,10 @@
         <v>40033</v>
       </c>
       <c r="D80" s="35" t="s">
+        <v>334</v>
+      </c>
+      <c r="E80" s="35" t="s">
         <v>335</v>
-      </c>
-      <c r="E80" s="35" t="s">
-        <v>336</v>
       </c>
       <c r="F80" s="34">
         <v>40033</v>
@@ -14754,13 +14760,13 @@
         <v>32</v>
       </c>
       <c r="H80" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="I80" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="I80" s="36" t="s">
-        <v>218</v>
-      </c>
       <c r="J80" s="25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="81" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14768,10 +14774,10 @@
         <v>40041</v>
       </c>
       <c r="D81" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="E81" s="37" t="s">
         <v>81</v>
-      </c>
-      <c r="E81" s="37" t="s">
-        <v>82</v>
       </c>
       <c r="F81" s="34">
         <v>40041</v>
@@ -14780,13 +14786,13 @@
         <v>38</v>
       </c>
       <c r="H81" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="I81" s="38" t="s">
         <v>338</v>
       </c>
-      <c r="I81" s="38" t="s">
+      <c r="J81" s="25" t="s">
         <v>339</v>
-      </c>
-      <c r="J81" s="25" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="82" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14794,10 +14800,10 @@
         <v>40042</v>
       </c>
       <c r="D82" s="37" t="s">
+        <v>340</v>
+      </c>
+      <c r="E82" s="37" t="s">
         <v>341</v>
-      </c>
-      <c r="E82" s="37" t="s">
-        <v>342</v>
       </c>
       <c r="F82" s="34">
         <v>40042</v>
@@ -14806,13 +14812,13 @@
         <v>38</v>
       </c>
       <c r="H82" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="I82" s="38" t="s">
         <v>343</v>
       </c>
-      <c r="I82" s="38" t="s">
+      <c r="J82" s="39" t="s">
         <v>344</v>
-      </c>
-      <c r="J82" s="39" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="83" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14820,10 +14826,10 @@
         <v>40043</v>
       </c>
       <c r="D83" s="35" t="s">
+        <v>345</v>
+      </c>
+      <c r="E83" s="35" t="s">
         <v>346</v>
-      </c>
-      <c r="E83" s="35" t="s">
-        <v>347</v>
       </c>
       <c r="F83" s="34">
         <v>40043</v>
@@ -14832,13 +14838,13 @@
         <v>38</v>
       </c>
       <c r="H83" s="36" t="s">
+        <v>347</v>
+      </c>
+      <c r="I83" s="36" t="s">
         <v>348</v>
       </c>
-      <c r="I83" s="36" t="s">
+      <c r="J83" s="25" t="s">
         <v>349</v>
-      </c>
-      <c r="J83" s="25" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="84" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14846,10 +14852,10 @@
         <v>40051</v>
       </c>
       <c r="D84" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="E84" s="37" t="s">
         <v>238</v>
-      </c>
-      <c r="E84" s="37" t="s">
-        <v>239</v>
       </c>
       <c r="F84" s="34">
         <v>40051</v>
@@ -14858,13 +14864,13 @@
         <v>42</v>
       </c>
       <c r="H84" s="38" t="s">
+        <v>350</v>
+      </c>
+      <c r="I84" s="38" t="s">
         <v>351</v>
       </c>
-      <c r="I84" s="38" t="s">
+      <c r="J84" s="39" t="s">
         <v>352</v>
-      </c>
-      <c r="J84" s="39" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="85" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14872,10 +14878,10 @@
         <v>40052</v>
       </c>
       <c r="D85" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E85" s="37" t="s">
         <v>51</v>
-      </c>
-      <c r="E85" s="37" t="s">
-        <v>52</v>
       </c>
       <c r="F85" s="34">
         <v>40052</v>
@@ -14884,13 +14890,13 @@
         <v>42</v>
       </c>
       <c r="H85" s="38" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="I85" s="38" t="s">
+        <v>353</v>
+      </c>
+      <c r="J85" s="25" t="s">
         <v>354</v>
-      </c>
-      <c r="J85" s="25" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="86" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14898,10 +14904,10 @@
         <v>40053</v>
       </c>
       <c r="D86" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="E86" s="35" t="s">
         <v>109</v>
-      </c>
-      <c r="E86" s="35" t="s">
-        <v>110</v>
       </c>
       <c r="F86" s="34">
         <v>40053</v>
@@ -14910,13 +14916,13 @@
         <v>42</v>
       </c>
       <c r="H86" s="36" t="s">
+        <v>355</v>
+      </c>
+      <c r="I86" s="36" t="s">
         <v>356</v>
       </c>
-      <c r="I86" s="36" t="s">
+      <c r="J86" s="27" t="s">
         <v>357</v>
-      </c>
-      <c r="J86" s="27" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="87" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14924,10 +14930,10 @@
         <v>40061</v>
       </c>
       <c r="D87" s="37" t="s">
+        <v>358</v>
+      </c>
+      <c r="E87" s="37" t="s">
         <v>359</v>
-      </c>
-      <c r="E87" s="37" t="s">
-        <v>360</v>
       </c>
       <c r="F87" s="34">
         <v>40061</v>
@@ -14936,13 +14942,13 @@
         <v>52</v>
       </c>
       <c r="H87" s="38" t="s">
+        <v>360</v>
+      </c>
+      <c r="I87" s="38" t="s">
         <v>361</v>
       </c>
-      <c r="I87" s="38" t="s">
+      <c r="J87" s="39" t="s">
         <v>362</v>
-      </c>
-      <c r="J87" s="39" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="88" spans="3:10" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14950,10 +14956,10 @@
         <v>40062</v>
       </c>
       <c r="D88" s="37" t="s">
+        <v>363</v>
+      </c>
+      <c r="E88" s="37" t="s">
         <v>364</v>
-      </c>
-      <c r="E88" s="37" t="s">
-        <v>365</v>
       </c>
       <c r="F88" s="34">
         <v>40062</v>
@@ -14962,13 +14968,13 @@
         <v>52</v>
       </c>
       <c r="H88" s="38" t="s">
+        <v>365</v>
+      </c>
+      <c r="I88" s="38" t="s">
         <v>366</v>
       </c>
-      <c r="I88" s="38" t="s">
+      <c r="J88" s="26" t="s">
         <v>367</v>
-      </c>
-      <c r="J88" s="26" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="89" spans="3:10" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -14976,10 +14982,10 @@
         <v>40063</v>
       </c>
       <c r="D89" s="35" t="s">
+        <v>368</v>
+      </c>
+      <c r="E89" s="35" t="s">
         <v>369</v>
-      </c>
-      <c r="E89" s="35" t="s">
-        <v>370</v>
       </c>
       <c r="F89" s="34">
         <v>40063</v>
@@ -14988,13 +14994,13 @@
         <v>52</v>
       </c>
       <c r="H89" s="36" t="s">
+        <v>370</v>
+      </c>
+      <c r="I89" s="36" t="s">
         <v>371</v>
       </c>
-      <c r="I89" s="36" t="s">
+      <c r="J89" s="27" t="s">
         <v>372</v>
-      </c>
-      <c r="J89" s="27" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="90" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15002,10 +15008,10 @@
         <v>50001</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F90" s="14">
         <v>50001</v>
@@ -15014,11 +15020,11 @@
         <v>15</v>
       </c>
       <c r="H90" s="13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I90" s="13"/>
       <c r="J90" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="91" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15026,10 +15032,10 @@
         <v>50002</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F91" s="14">
         <v>50002</v>
@@ -15038,11 +15044,11 @@
         <v>15</v>
       </c>
       <c r="H91" s="13" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I91" s="13"/>
       <c r="J91" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="92" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15050,10 +15056,10 @@
         <v>50003</v>
       </c>
       <c r="D92" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="E92" s="14" t="s">
         <v>299</v>
-      </c>
-      <c r="E92" s="14" t="s">
-        <v>300</v>
       </c>
       <c r="F92" s="14">
         <v>50003</v>
@@ -15062,11 +15068,11 @@
         <v>15</v>
       </c>
       <c r="H92" s="13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I92" s="13"/>
       <c r="J92" s="27" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="93" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15074,10 +15080,10 @@
         <v>50011</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F93" s="14">
         <v>50011</v>
@@ -15086,11 +15092,11 @@
         <v>22</v>
       </c>
       <c r="H93" s="13" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="I93" s="13"/>
       <c r="J93" s="27" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="94" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15098,10 +15104,10 @@
         <v>50012</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F94" s="14">
         <v>50012</v>
@@ -15110,11 +15116,11 @@
         <v>22</v>
       </c>
       <c r="H94" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I94" s="13"/>
       <c r="J94" s="27" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="95" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15122,10 +15128,10 @@
         <v>50013</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E95" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F95" s="14">
         <v>50013</v>
@@ -15134,11 +15140,11 @@
         <v>22</v>
       </c>
       <c r="H95" s="13" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I95" s="13"/>
       <c r="J95" s="27" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="96" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15146,10 +15152,10 @@
         <v>50021</v>
       </c>
       <c r="D96" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E96" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="E96" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="F96" s="14">
         <v>50021</v>
@@ -15158,11 +15164,11 @@
         <v>28</v>
       </c>
       <c r="H96" s="13" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="I96" s="13"/>
       <c r="J96" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="97" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15170,10 +15176,10 @@
         <v>50022</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F97" s="14">
         <v>50022</v>
@@ -15182,11 +15188,11 @@
         <v>28</v>
       </c>
       <c r="H97" s="13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I97" s="13"/>
       <c r="J97" s="27" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="98" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15194,10 +15200,10 @@
         <v>50023</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F98" s="14">
         <v>50023</v>
@@ -15206,11 +15212,11 @@
         <v>28</v>
       </c>
       <c r="H98" s="13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I98" s="13"/>
       <c r="J98" s="27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="99" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15218,10 +15224,10 @@
         <v>50031</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F99" s="14">
         <v>50031</v>
@@ -15230,11 +15236,11 @@
         <v>32</v>
       </c>
       <c r="H99" s="13" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="I99" s="13"/>
       <c r="J99" s="27" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="100" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15242,10 +15248,10 @@
         <v>50032</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F100" s="14">
         <v>50032</v>
@@ -15254,11 +15260,11 @@
         <v>32</v>
       </c>
       <c r="H100" s="13" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I100" s="13"/>
       <c r="J100" s="27" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="101" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15266,10 +15272,10 @@
         <v>50033</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F101" s="14">
         <v>50033</v>
@@ -15278,11 +15284,11 @@
         <v>32</v>
       </c>
       <c r="H101" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I101" s="13"/>
       <c r="J101" s="27" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="102" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15290,10 +15296,10 @@
         <v>50041</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F102" s="14">
         <v>50041</v>
@@ -15302,11 +15308,11 @@
         <v>38</v>
       </c>
       <c r="H102" s="13" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="I102" s="13"/>
       <c r="J102" s="27" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="103" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15314,10 +15320,10 @@
         <v>50042</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E103" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F103" s="14">
         <v>50042</v>
@@ -15326,11 +15332,11 @@
         <v>38</v>
       </c>
       <c r="H103" s="13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I103" s="13"/>
       <c r="J103" s="27" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="104" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15338,10 +15344,10 @@
         <v>50043</v>
       </c>
       <c r="D104" s="14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F104" s="14">
         <v>50043</v>
@@ -15350,11 +15356,11 @@
         <v>38</v>
       </c>
       <c r="H104" s="13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I104" s="13"/>
       <c r="J104" s="27" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="105" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15362,10 +15368,10 @@
         <v>50051</v>
       </c>
       <c r="D105" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E105" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="E105" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="F105" s="14">
         <v>50051</v>
@@ -15374,11 +15380,11 @@
         <v>42</v>
       </c>
       <c r="H105" s="13" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="I105" s="13"/>
       <c r="J105" s="27" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="106" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15386,10 +15392,10 @@
         <v>50052</v>
       </c>
       <c r="D106" s="14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F106" s="14">
         <v>50052</v>
@@ -15398,11 +15404,11 @@
         <v>42</v>
       </c>
       <c r="H106" s="13" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I106" s="13"/>
       <c r="J106" s="27" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="107" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15410,10 +15416,10 @@
         <v>50053</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E107" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F107" s="14">
         <v>50053</v>
@@ -15422,11 +15428,11 @@
         <v>42</v>
       </c>
       <c r="H107" s="13" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I107" s="13"/>
       <c r="J107" s="27" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="108" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15434,10 +15440,10 @@
         <v>50061</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F108" s="14">
         <v>50061</v>
@@ -15446,11 +15452,11 @@
         <v>52</v>
       </c>
       <c r="H108" s="13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I108" s="13"/>
       <c r="J108" s="27" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="109" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15458,10 +15464,10 @@
         <v>50062</v>
       </c>
       <c r="D109" s="14" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E109" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F109" s="14">
         <v>50062</v>
@@ -15470,11 +15476,11 @@
         <v>52</v>
       </c>
       <c r="H109" s="13" t="s">
-        <v>416</v>
+        <v>486</v>
       </c>
       <c r="I109" s="13"/>
       <c r="J109" s="27" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="110" spans="3:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15482,10 +15488,10 @@
         <v>50063</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F110" s="14">
         <v>50063</v>
@@ -15494,11 +15500,11 @@
         <v>52</v>
       </c>
       <c r="H110" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I110" s="13"/>
       <c r="J110" s="27" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="111" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15506,10 +15512,10 @@
         <v>90001</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F111" s="11">
         <v>60010100</v>
@@ -15518,13 +15524,13 @@
         <v>1</v>
       </c>
       <c r="H111" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="J111" s="25" t="s">
         <v>422</v>
-      </c>
-      <c r="I111" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="J111" s="25" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="112" spans="3:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15532,10 +15538,10 @@
         <v>90002</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F112" s="11">
         <v>60010200</v>
@@ -15544,13 +15550,13 @@
         <v>1</v>
       </c>
       <c r="H112" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="J112" s="25" t="s">
         <v>427</v>
-      </c>
-      <c r="I112" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="J112" s="25" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="113" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15558,10 +15564,10 @@
         <v>90003</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F113" s="11">
         <v>60010300</v>
@@ -15570,13 +15576,13 @@
         <v>1</v>
       </c>
       <c r="H113" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="J113" s="25" t="s">
         <v>432</v>
-      </c>
-      <c r="I113" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="J113" s="25" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="114" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15584,10 +15590,10 @@
         <v>90004</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F114" s="11">
         <v>60010400</v>
@@ -15596,13 +15602,13 @@
         <v>2</v>
       </c>
       <c r="H114" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="J114" s="25" t="s">
         <v>437</v>
-      </c>
-      <c r="I114" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="J114" s="25" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="115" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15610,10 +15616,10 @@
         <v>90005</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F115" s="11">
         <v>60010500</v>
@@ -15622,13 +15628,13 @@
         <v>2</v>
       </c>
       <c r="H115" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="J115" s="25" t="s">
         <v>442</v>
-      </c>
-      <c r="I115" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="J115" s="25" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="116" spans="3:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15636,10 +15642,10 @@
         <v>90006</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F116" s="11">
         <v>60010600</v>
@@ -15648,13 +15654,13 @@
         <v>2</v>
       </c>
       <c r="H116" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="J116" s="25" t="s">
         <v>447</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="J116" s="25" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="117" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15668,7 +15674,7 @@
         <v>1</v>
       </c>
       <c r="J117" s="40" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="118" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15682,7 +15688,7 @@
         <v>1</v>
       </c>
       <c r="J118" s="40" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="119" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15696,7 +15702,7 @@
         <v>1</v>
       </c>
       <c r="J119" s="40" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="120" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15710,7 +15716,7 @@
         <v>1</v>
       </c>
       <c r="J120" s="40" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="121" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15724,7 +15730,7 @@
         <v>1</v>
       </c>
       <c r="J121" s="40" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="122" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15738,7 +15744,7 @@
         <v>1</v>
       </c>
       <c r="J122" s="40" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="123" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15752,7 +15758,7 @@
         <v>1</v>
       </c>
       <c r="J123" s="40" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="124" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15766,7 +15772,7 @@
         <v>1</v>
       </c>
       <c r="J124" s="40" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="125" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15780,7 +15786,7 @@
         <v>1</v>
       </c>
       <c r="J125" s="40" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="126" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15794,7 +15800,7 @@
         <v>1</v>
       </c>
       <c r="J126" s="40" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="127" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -15808,7 +15814,7 @@
         <v>1</v>
       </c>
       <c r="J127" s="40" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="Q127" s="11"/>
     </row>
@@ -15823,7 +15829,7 @@
         <v>1</v>
       </c>
       <c r="J128" s="40" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="Q128" s="11"/>
     </row>
@@ -15838,7 +15844,7 @@
         <v>1</v>
       </c>
       <c r="J129" s="40" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="Q129" s="11"/>
     </row>
@@ -15853,7 +15859,7 @@
         <v>1</v>
       </c>
       <c r="J130" s="40" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="Q130" s="11"/>
     </row>
@@ -15868,7 +15874,7 @@
         <v>1</v>
       </c>
       <c r="J131" s="40" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="Q131" s="11"/>
     </row>
@@ -15883,7 +15889,7 @@
         <v>1</v>
       </c>
       <c r="J132" s="40" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="Q132" s="11"/>
     </row>
@@ -15898,7 +15904,7 @@
         <v>1</v>
       </c>
       <c r="J133" s="40" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="Q133" s="11"/>
     </row>
@@ -15913,7 +15919,7 @@
         <v>1</v>
       </c>
       <c r="J134" s="40" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="Q134" s="11"/>
     </row>
@@ -15928,7 +15934,7 @@
         <v>1</v>
       </c>
       <c r="J135" s="40" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q135" s="11"/>
     </row>
@@ -15943,7 +15949,7 @@
         <v>1</v>
       </c>
       <c r="J136" s="40" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="Q136" s="11"/>
     </row>
@@ -15958,7 +15964,7 @@
         <v>1</v>
       </c>
       <c r="J137" s="40" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="Q137" s="11"/>
     </row>
@@ -15973,7 +15979,7 @@
         <v>1</v>
       </c>
       <c r="J138" s="40" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="Q138" s="11"/>
     </row>
@@ -15988,7 +15994,7 @@
         <v>1</v>
       </c>
       <c r="J139" s="40" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="Q139" s="11"/>
     </row>
@@ -16003,7 +16009,7 @@
         <v>1</v>
       </c>
       <c r="J140" s="40" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Q140" s="11"/>
     </row>
